--- a/research/traditional_assets/database/data/spain/spain_homebuilding.xlsx
+++ b/research/traditional_assets/database/data/spain/spain_homebuilding.xlsx
@@ -650,10 +650,10 @@
         <v>0.1007455365901511</v>
       </c>
       <c r="X2">
-        <v>0.1237443487951502</v>
+        <v>0.1237232600653381</v>
       </c>
       <c r="Y2">
-        <v>-0.02299881220499909</v>
+        <v>-0.02297772347518702</v>
       </c>
       <c r="Z2">
         <v>0.4679917669506168</v>
@@ -662,10 +662,10 @@
         <v>0.06500484174129162</v>
       </c>
       <c r="AB2">
-        <v>0.1093153425432629</v>
+        <v>0.1092995050613013</v>
       </c>
       <c r="AC2">
-        <v>-0.0443105008019713</v>
+        <v>-0.04429466332000964</v>
       </c>
       <c r="AD2">
         <v>432.7</v>
@@ -787,10 +787,10 @@
         <v>0.1007455365901511</v>
       </c>
       <c r="X3">
-        <v>0.1237443487951502</v>
+        <v>0.1237232600653381</v>
       </c>
       <c r="Y3">
-        <v>-0.02299881220499909</v>
+        <v>-0.02297772347518702</v>
       </c>
       <c r="Z3">
         <v>0.4679917669506168</v>
@@ -799,10 +799,10 @@
         <v>0.06500484174129162</v>
       </c>
       <c r="AB3">
-        <v>0.1093153425432629</v>
+        <v>0.1092995050613013</v>
       </c>
       <c r="AC3">
-        <v>-0.0443105008019713</v>
+        <v>-0.04429466332000964</v>
       </c>
       <c r="AD3">
         <v>432.7</v>
@@ -1139,49 +1139,49 @@
         <v>4.57853658536585</v>
       </c>
       <c r="F2">
-        <v>4.6808744135314</v>
+        <v>4.56656102039557</v>
       </c>
       <c r="G2">
         <v>4.21324245374878</v>
       </c>
       <c r="H2">
-        <v>2.70722492697176</v>
+        <v>2.8764264849075</v>
       </c>
       <c r="I2">
         <v>0.24900730851125</v>
       </c>
       <c r="J2">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="K2">
         <v>1305</v>
       </c>
       <c r="L2">
-        <v>1510.14160525537</v>
+        <v>1502.74248485251</v>
       </c>
       <c r="M2">
         <v>1497.5</v>
       </c>
       <c r="N2">
-        <v>1547.97360525537</v>
+        <v>1557.95148485251</v>
       </c>
       <c r="O2">
         <v>432.7</v>
       </c>
       <c r="P2">
-        <v>278.032</v>
+        <v>295.409</v>
       </c>
       <c r="Q2">
-        <v>0.109315342543263</v>
+        <v>0.109299505061301</v>
       </c>
       <c r="R2">
-        <v>0.107244345779297</v>
+        <v>0.106835603325158</v>
       </c>
       <c r="S2">
         <v>0.06579823332506821</v>
       </c>
       <c r="T2">
-        <v>0.0552982333250682</v>
+        <v>0.0533482333250682</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -1194,16 +1194,16 @@
         </is>
       </c>
       <c r="W2">
-        <v>0.12374434879515</v>
+        <v>0.123723260065338</v>
       </c>
       <c r="X2">
-        <v>0.117138843389626</v>
+        <v>0.117790847783007</v>
       </c>
       <c r="Y2">
         <v>1.20544805064439</v>
       </c>
       <c r="Z2">
-        <v>1.10329063015536</v>
+        <v>1.11367551936993</v>
       </c>
       <c r="AA2">
         <v>432.7</v>
@@ -1236,7 +1236,7 @@
         <v>1305</v>
       </c>
       <c r="AK2">
-        <v>0.0646600645739018</v>
+        <v>0.06464257005823121</v>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
@@ -1424,13 +1424,13 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0.1082214879659232</v>
+        <v>0.108204599122607</v>
       </c>
       <c r="C2">
-        <v>1763.941720326508</v>
+        <v>1763.974051371971</v>
       </c>
       <c r="D2">
-        <v>1523.741720326508</v>
+        <v>1523.774051371971</v>
       </c>
       <c r="E2">
         <v>-432.7</v>
@@ -1475,19 +1475,19 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>0.1082214879659232</v>
+        <v>0.108204599122607</v>
       </c>
       <c r="T2">
         <v>0.9653793013859413</v>
       </c>
       <c r="U2">
-        <v>0.06753097776675759</v>
+        <v>0.0661309777667576</v>
       </c>
       <c r="V2">
         <v>0.25</v>
       </c>
       <c r="W2">
-        <v>0.0506482333250682</v>
+        <v>0.0495982333250682</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -1506,13 +1506,13 @@
         <v>0.01</v>
       </c>
       <c r="B3">
-        <v>0.108113916579259</v>
+        <v>0.1080865699580512</v>
       </c>
       <c r="C3">
-        <v>1749.195128087269</v>
+        <v>1749.484508144377</v>
       </c>
       <c r="D3">
-        <v>1526.372128087269</v>
+        <v>1526.661508144377</v>
       </c>
       <c r="E3">
         <v>-415.323</v>
@@ -1539,37 +1539,37 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M3">
-        <v>1.173485800652947</v>
+        <v>1.149158000652947</v>
       </c>
       <c r="N3">
-        <v>94.782432566694</v>
+        <v>94.80676036669399</v>
       </c>
       <c r="O3">
-        <v>23.6956081416735</v>
+        <v>23.7016900916735</v>
       </c>
       <c r="P3">
-        <v>71.0868244250205</v>
+        <v>71.10507027502049</v>
       </c>
       <c r="Q3">
-        <v>79.9268244250205</v>
+        <v>79.9450702750205</v>
       </c>
       <c r="R3">
         <v>0.0101010101010101</v>
       </c>
       <c r="S3">
-        <v>0.1086943780262711</v>
+        <v>0.1086773612371722</v>
       </c>
       <c r="T3">
         <v>0.9726927809418954</v>
       </c>
       <c r="U3">
-        <v>0.06753097776675759</v>
+        <v>0.0661309777667576</v>
       </c>
       <c r="V3">
         <v>0.25</v>
       </c>
       <c r="W3">
-        <v>0.0506482333250682</v>
+        <v>0.0495982333250682</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>81.76998674713872</v>
+        <v>83.50106627010835</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1588,13 +1588,13 @@
         <v>0.02</v>
       </c>
       <c r="B4">
-        <v>0.1080063451925949</v>
+        <v>0.1079685407934953</v>
       </c>
       <c r="C4">
-        <v>1734.457633203275</v>
+        <v>1735.005928793566</v>
       </c>
       <c r="D4">
-        <v>1529.011633203274</v>
+        <v>1529.559928793566</v>
       </c>
       <c r="E4">
         <v>-397.946</v>
@@ -1621,37 +1621,37 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M4">
-        <v>2.346971601305894</v>
+        <v>2.298316001305894</v>
       </c>
       <c r="N4">
-        <v>93.60894676604104</v>
+        <v>93.65760236604105</v>
       </c>
       <c r="O4">
-        <v>23.40223669151026</v>
+        <v>23.41440059151026</v>
       </c>
       <c r="P4">
-        <v>70.20671007453078</v>
+        <v>70.24320177453079</v>
       </c>
       <c r="Q4">
-        <v>79.04671007453078</v>
+        <v>79.08320177453079</v>
       </c>
       <c r="R4">
         <v>0.02040816326530612</v>
       </c>
       <c r="S4">
-        <v>0.1091769189041771</v>
+        <v>0.1091597715581571</v>
       </c>
       <c r="T4">
         <v>0.980155515182665</v>
       </c>
       <c r="U4">
-        <v>0.06753097776675759</v>
+        <v>0.0661309777667576</v>
       </c>
       <c r="V4">
         <v>0.25</v>
       </c>
       <c r="W4">
-        <v>0.0506482333250682</v>
+        <v>0.0495982333250682</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>40.88499337356936</v>
+        <v>41.75053313505418</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1670,13 +1670,13 @@
         <v>0.03</v>
       </c>
       <c r="B5">
-        <v>0.1078987738059308</v>
+        <v>0.1078505116289395</v>
       </c>
       <c r="C5">
-        <v>1719.729282951549</v>
+        <v>1720.538375884239</v>
       </c>
       <c r="D5">
-        <v>1531.660282951549</v>
+        <v>1532.469375884239</v>
       </c>
       <c r="E5">
         <v>-380.569</v>
@@ -1703,37 +1703,37 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M5">
-        <v>3.52045740195884</v>
+        <v>3.44747400195884</v>
       </c>
       <c r="N5">
-        <v>92.4354609653881</v>
+        <v>92.5084443653881</v>
       </c>
       <c r="O5">
-        <v>23.10886524134703</v>
+        <v>23.12711109134703</v>
       </c>
       <c r="P5">
-        <v>69.32659572404108</v>
+        <v>69.38133327404108</v>
       </c>
       <c r="Q5">
-        <v>78.16659572404109</v>
+        <v>78.22133327404109</v>
       </c>
       <c r="R5">
         <v>0.03092783505154639</v>
       </c>
       <c r="S5">
-        <v>0.1096694090785348</v>
+        <v>0.1096521284836984</v>
       </c>
       <c r="T5">
         <v>0.9877721202325224</v>
       </c>
       <c r="U5">
-        <v>0.06753097776675759</v>
+        <v>0.0661309777667576</v>
       </c>
       <c r="V5">
         <v>0.25</v>
       </c>
       <c r="W5">
-        <v>0.0506482333250682</v>
+        <v>0.0495982333250682</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>27.25666224904625</v>
+        <v>27.83368875670279</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1752,13 +1752,13 @@
         <v>0.04</v>
       </c>
       <c r="B6">
-        <v>0.1077912024192667</v>
+        <v>0.1077324824643837</v>
       </c>
       <c r="C6">
-        <v>1705.010124937273</v>
+        <v>1706.081912458032</v>
       </c>
       <c r="D6">
-        <v>1534.318124937273</v>
+        <v>1535.389912458032</v>
       </c>
       <c r="E6">
         <v>-363.192</v>
@@ -1785,37 +1785,37 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M6">
-        <v>4.693943202611788</v>
+        <v>4.596632002611788</v>
       </c>
       <c r="N6">
-        <v>91.26197516473515</v>
+        <v>91.35928636473515</v>
       </c>
       <c r="O6">
-        <v>22.81549379118379</v>
+        <v>22.83982159118379</v>
       </c>
       <c r="P6">
-        <v>68.44648137355136</v>
+        <v>68.51946477355136</v>
       </c>
       <c r="Q6">
-        <v>77.28648137355137</v>
+        <v>77.35946477355137</v>
       </c>
       <c r="R6">
         <v>0.04166666666666667</v>
       </c>
       <c r="S6">
-        <v>0.1101721594648583</v>
+        <v>0.1101547428451885</v>
       </c>
       <c r="T6">
         <v>0.9955474045542519</v>
       </c>
       <c r="U6">
-        <v>0.06753097776675759</v>
+        <v>0.0661309777667576</v>
       </c>
       <c r="V6">
         <v>0.25</v>
       </c>
       <c r="W6">
-        <v>0.0506482333250682</v>
+        <v>0.0495982333250682</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>20.44249668678468</v>
+        <v>20.87526656752709</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1834,13 +1834,13 @@
         <v>0.05</v>
       </c>
       <c r="B7">
-        <v>0.1076836310326025</v>
+        <v>0.1076144532998278</v>
       </c>
       <c r="C7">
-        <v>1690.300207096633</v>
+        <v>1691.636602038071</v>
       </c>
       <c r="D7">
-        <v>1536.985207096633</v>
+        <v>1538.321602038071</v>
       </c>
       <c r="E7">
         <v>-345.815</v>
@@ -1867,37 +1867,37 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M7">
-        <v>5.867429003264734</v>
+        <v>5.745790003264734</v>
       </c>
       <c r="N7">
-        <v>90.08848936408221</v>
+        <v>90.21012836408221</v>
       </c>
       <c r="O7">
-        <v>22.52212234102055</v>
+        <v>22.55253209102055</v>
       </c>
       <c r="P7">
-        <v>67.56636702306166</v>
+        <v>67.65759627306166</v>
       </c>
       <c r="Q7">
-        <v>76.40636702306166</v>
+        <v>76.49759627306166</v>
       </c>
       <c r="R7">
         <v>0.05263157894736843</v>
       </c>
       <c r="S7">
-        <v>0.1106854940698412</v>
+        <v>0.1106679385616573</v>
       </c>
       <c r="T7">
         <v>1.003486379072228</v>
       </c>
       <c r="U7">
-        <v>0.06753097776675759</v>
+        <v>0.0661309777667576</v>
       </c>
       <c r="V7">
         <v>0.25</v>
       </c>
       <c r="W7">
-        <v>0.0506482333250682</v>
+        <v>0.0495982333250682</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>16.35399734942775</v>
+        <v>16.70021325402168</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1916,13 +1916,13 @@
         <v>0.06</v>
       </c>
       <c r="B8">
-        <v>0.1075760596459384</v>
+        <v>0.107496424135272</v>
       </c>
       <c r="C8">
-        <v>1675.599577699699</v>
+        <v>1677.202508633575</v>
       </c>
       <c r="D8">
-        <v>1539.661577699699</v>
+        <v>1541.264508633575</v>
       </c>
       <c r="E8">
         <v>-328.438</v>
@@ -1949,37 +1949,37 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M8">
-        <v>7.04091480391768</v>
+        <v>6.894948003917681</v>
       </c>
       <c r="N8">
-        <v>88.91500356342925</v>
+        <v>89.06097036342926</v>
       </c>
       <c r="O8">
-        <v>22.22875089085731</v>
+        <v>22.26524259085732</v>
       </c>
       <c r="P8">
-        <v>66.68625267257194</v>
+        <v>66.79572777257195</v>
       </c>
       <c r="Q8">
-        <v>75.52625267257194</v>
+        <v>75.63572777257195</v>
       </c>
       <c r="R8">
         <v>0.06382978723404255</v>
       </c>
       <c r="S8">
-        <v>0.1112097506876961</v>
+        <v>0.1111920533359233</v>
       </c>
       <c r="T8">
         <v>1.011594267941651</v>
       </c>
       <c r="U8">
-        <v>0.06753097776675759</v>
+        <v>0.0661309777667576</v>
       </c>
       <c r="V8">
         <v>0.25</v>
       </c>
       <c r="W8">
-        <v>0.0506482333250682</v>
+        <v>0.0495982333250682</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>13.62833112452312</v>
+        <v>13.91684437835139</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1998,13 +1998,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="B9">
-        <v>0.1075262382592743</v>
+        <v>0.1074571449707162</v>
       </c>
       <c r="C9">
-        <v>1659.465291932052</v>
+        <v>1660.807383196328</v>
       </c>
       <c r="D9">
-        <v>1540.904291932052</v>
+        <v>1542.246383196328</v>
       </c>
       <c r="E9">
         <v>-311.061</v>
@@ -2031,37 +2031,37 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M9">
-        <v>8.348203504570627</v>
+        <v>8.226564504570627</v>
       </c>
       <c r="N9">
-        <v>87.60771486277631</v>
+        <v>87.72935386277631</v>
       </c>
       <c r="O9">
-        <v>21.90192871569408</v>
+        <v>21.93233846569408</v>
       </c>
       <c r="P9">
-        <v>65.70578614708222</v>
+        <v>65.79701539708223</v>
       </c>
       <c r="Q9">
-        <v>74.54578614708223</v>
+        <v>74.63701539708224</v>
       </c>
       <c r="R9">
         <v>0.07526881720430109</v>
       </c>
       <c r="S9">
-        <v>0.1117452816414188</v>
+        <v>0.1117274393956574</v>
       </c>
       <c r="T9">
         <v>1.019876520012567</v>
       </c>
       <c r="U9">
-        <v>0.06863097776675758</v>
+        <v>0.06763097776675758</v>
       </c>
       <c r="V9">
         <v>0.25</v>
       </c>
       <c r="W9">
-        <v>0.05147323332506819</v>
+        <v>0.05072323332506819</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>11.4941997179167</v>
+        <v>11.66415437623256</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2080,13 +2080,13 @@
         <v>0.08</v>
       </c>
       <c r="B10">
-        <v>0.1074269168726102</v>
+        <v>0.1073503658061603</v>
       </c>
       <c r="C10">
-        <v>1644.571699487678</v>
+        <v>1646.10591206086</v>
       </c>
       <c r="D10">
-        <v>1543.387699487678</v>
+        <v>1544.92191206086</v>
       </c>
       <c r="E10">
         <v>-293.684</v>
@@ -2113,37 +2113,37 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M10">
-        <v>9.540804005223574</v>
+        <v>9.401788005223574</v>
       </c>
       <c r="N10">
-        <v>86.41511436212336</v>
+        <v>86.55413036212336</v>
       </c>
       <c r="O10">
-        <v>21.60377859053084</v>
+        <v>21.63853259053084</v>
       </c>
       <c r="P10">
-        <v>64.81133577159252</v>
+        <v>64.91559777159252</v>
       </c>
       <c r="Q10">
-        <v>73.65133577159253</v>
+        <v>73.75559777159252</v>
       </c>
       <c r="R10">
         <v>0.08695652173913043</v>
       </c>
       <c r="S10">
-        <v>0.1122924545723964</v>
+        <v>0.112274464282777</v>
       </c>
       <c r="T10">
         <v>1.028338821041546</v>
       </c>
       <c r="U10">
-        <v>0.06863097776675758</v>
+        <v>0.06763097776675758</v>
       </c>
       <c r="V10">
         <v>0.25</v>
       </c>
       <c r="W10">
-        <v>0.05147323332506819</v>
+        <v>0.05072323332506819</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>10.05742475317711</v>
+        <v>10.20613507920349</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2162,13 +2162,13 @@
         <v>0.09</v>
       </c>
       <c r="B11">
-        <v>0.107476095485946</v>
+        <v>0.1073583366416045</v>
       </c>
       <c r="C11">
-        <v>1625.964049812105</v>
+        <v>1628.528868995909</v>
       </c>
       <c r="D11">
-        <v>1542.157049812105</v>
+        <v>1544.721868995909</v>
       </c>
       <c r="E11">
         <v>-276.307</v>
@@ -2195,37 +2195,37 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M11">
-        <v>11.07746910587652</v>
+        <v>10.84287960587652</v>
       </c>
       <c r="N11">
-        <v>84.87844926147042</v>
+        <v>85.11303876147042</v>
       </c>
       <c r="O11">
-        <v>21.21961231536761</v>
+        <v>21.27825969036761</v>
       </c>
       <c r="P11">
-        <v>63.65883694610282</v>
+        <v>63.83477907110282</v>
       </c>
       <c r="Q11">
-        <v>72.49883694610281</v>
+        <v>72.67477907110282</v>
       </c>
       <c r="R11">
         <v>0.0989010989010989</v>
       </c>
       <c r="S11">
-        <v>0.1128516532820768</v>
+        <v>0.1128335116948883</v>
       </c>
       <c r="T11">
         <v>1.036987106708525</v>
       </c>
       <c r="U11">
-        <v>0.07083097776675759</v>
+        <v>0.06933097776675759</v>
       </c>
       <c r="V11">
         <v>0.25</v>
       </c>
       <c r="W11">
-        <v>0.05312323332506819</v>
+        <v>0.05199823332506819</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>8.662260074951867</v>
+        <v>8.849671107234435</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2244,13 +2244,13 @@
         <v>0.1</v>
       </c>
       <c r="B12">
-        <v>0.1073932740992819</v>
+        <v>0.1072643074770487</v>
       </c>
       <c r="C12">
-        <v>1610.660711054945</v>
+        <v>1613.515011326392</v>
       </c>
       <c r="D12">
-        <v>1544.230711054945</v>
+        <v>1547.085011326392</v>
       </c>
       <c r="E12">
         <v>-258.9299999999999</v>
@@ -2277,37 +2277,37 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M12">
-        <v>12.30829900652947</v>
+        <v>12.04764400652947</v>
       </c>
       <c r="N12">
-        <v>83.64761936081747</v>
+        <v>83.90827436081747</v>
       </c>
       <c r="O12">
-        <v>20.91190484020437</v>
+        <v>20.97706859020437</v>
       </c>
       <c r="P12">
-        <v>62.7357145206131</v>
+        <v>62.9312057706131</v>
       </c>
       <c r="Q12">
-        <v>71.5757145206131</v>
+        <v>71.77120577061311</v>
       </c>
       <c r="R12">
         <v>0.1111111111111111</v>
       </c>
       <c r="S12">
-        <v>0.1134232786297501</v>
+        <v>0.1134049823828243</v>
       </c>
       <c r="T12">
         <v>1.045827576501436</v>
       </c>
       <c r="U12">
-        <v>0.07083097776675759</v>
+        <v>0.06933097776675759</v>
       </c>
       <c r="V12">
         <v>0.25</v>
       </c>
       <c r="W12">
-        <v>0.05312323332506819</v>
+        <v>0.05199823332506819</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>7.796034067456681</v>
+        <v>7.964703996510992</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2326,13 +2326,13 @@
         <v>0.11</v>
       </c>
       <c r="B13">
-        <v>0.1074342027126178</v>
+        <v>0.1072362783124928</v>
       </c>
       <c r="C13">
-        <v>1592.258254102596</v>
+        <v>1596.843840220254</v>
       </c>
       <c r="D13">
-        <v>1543.205254102596</v>
+        <v>1547.790840220254</v>
       </c>
       <c r="E13">
         <v>-241.553</v>
@@ -2359,37 +2359,37 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M13">
-        <v>13.82584940718242</v>
+        <v>13.40532600718241</v>
       </c>
       <c r="N13">
-        <v>82.13006896016452</v>
+        <v>82.55059236016453</v>
       </c>
       <c r="O13">
-        <v>20.53251724004113</v>
+        <v>20.63764809004113</v>
       </c>
       <c r="P13">
-        <v>61.59755172012339</v>
+        <v>61.9129442701234</v>
       </c>
       <c r="Q13">
-        <v>70.43755172012339</v>
+        <v>70.75294427012339</v>
       </c>
       <c r="R13">
         <v>0.1235955056179775</v>
       </c>
       <c r="S13">
-        <v>0.1140077494908543</v>
+        <v>0.1139892951086914</v>
       </c>
       <c r="T13">
         <v>1.054866708536885</v>
       </c>
       <c r="U13">
-        <v>0.07233097776675759</v>
+        <v>0.07013097776675759</v>
       </c>
       <c r="V13">
         <v>0.25</v>
       </c>
       <c r="W13">
-        <v>0.05424823332506819</v>
+        <v>0.05259823332506819</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>6.940327175666952</v>
+        <v>7.158044371016036</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2408,13 +2408,13 @@
         <v>0.12</v>
       </c>
       <c r="B14">
-        <v>0.1073626313259537</v>
+        <v>0.107148249147937</v>
       </c>
       <c r="C14">
-        <v>1576.6753512288</v>
+        <v>1581.687779472215</v>
       </c>
       <c r="D14">
-        <v>1544.9993512288</v>
+        <v>1550.011779472215</v>
       </c>
       <c r="E14">
         <v>-224.176</v>
@@ -2441,37 +2441,37 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M14">
-        <v>15.08274480783536</v>
+        <v>14.62399200783536</v>
       </c>
       <c r="N14">
-        <v>80.87317355951159</v>
+        <v>81.33192635951158</v>
       </c>
       <c r="O14">
-        <v>20.2182933898779</v>
+        <v>20.3329815898779</v>
       </c>
       <c r="P14">
-        <v>60.65488016963369</v>
+        <v>60.99894476963369</v>
       </c>
       <c r="Q14">
-        <v>69.49488016963369</v>
+        <v>69.83894476963368</v>
       </c>
       <c r="R14">
         <v>0.1363636363636364</v>
       </c>
       <c r="S14">
-        <v>0.1146055037806199</v>
+        <v>0.1145868876692373</v>
       </c>
       <c r="T14">
         <v>1.064111275391322</v>
       </c>
       <c r="U14">
-        <v>0.07233097776675759</v>
+        <v>0.07013097776675759</v>
       </c>
       <c r="V14">
         <v>0.25</v>
       </c>
       <c r="W14">
-        <v>0.05424823332506819</v>
+        <v>0.05259823332506819</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>6.361966577694708</v>
+        <v>6.561540673431367</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2490,13 +2490,13 @@
         <v>0.13</v>
       </c>
       <c r="B15">
-        <v>0.1074275599392896</v>
+        <v>0.1071577199833812</v>
       </c>
       <c r="C15">
-        <v>1557.670594660489</v>
+        <v>1564.071528298869</v>
       </c>
       <c r="D15">
-        <v>1543.371594660489</v>
+        <v>1549.772528298869</v>
       </c>
       <c r="E15">
         <v>-206.799</v>
@@ -2523,37 +2523,37 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M15">
-        <v>16.65590160848831</v>
+        <v>16.06855900848831</v>
       </c>
       <c r="N15">
-        <v>79.30001675885863</v>
+        <v>79.88735935885863</v>
       </c>
       <c r="O15">
-        <v>19.82500418971466</v>
+        <v>19.97183983971466</v>
       </c>
       <c r="P15">
-        <v>59.47501256914397</v>
+        <v>59.91551951914397</v>
       </c>
       <c r="Q15">
-        <v>68.31501256914397</v>
+        <v>68.75551951914397</v>
       </c>
       <c r="R15">
         <v>0.1494252873563219</v>
       </c>
       <c r="S15">
-        <v>0.1152169995483111</v>
+        <v>0.1151982179897957</v>
       </c>
       <c r="T15">
         <v>1.073568361024021</v>
       </c>
       <c r="U15">
-        <v>0.07373097776675759</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V15">
         <v>0.25</v>
       </c>
       <c r="W15">
-        <v>0.0552982333250682</v>
+        <v>0.05334823332506819</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>5.761076201269414</v>
+        <v>5.971656718978826</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2572,13 +2572,13 @@
         <v>0.14</v>
       </c>
       <c r="B16">
-        <v>0.1073664885526254</v>
+        <v>0.1070771908188253</v>
       </c>
       <c r="C16">
-        <v>1541.824554857178</v>
+        <v>1548.731205980855</v>
       </c>
       <c r="D16">
-        <v>1544.902554857178</v>
+        <v>1551.809205980855</v>
       </c>
       <c r="E16">
         <v>-189.422</v>
@@ -2605,37 +2605,37 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M16">
-        <v>17.93712480914126</v>
+        <v>17.30460200914125</v>
       </c>
       <c r="N16">
-        <v>78.01879355820569</v>
+        <v>78.65131635820569</v>
       </c>
       <c r="O16">
-        <v>19.50469838955142</v>
+        <v>19.66282908955142</v>
       </c>
       <c r="P16">
-        <v>58.51409516865426</v>
+        <v>58.98848726865427</v>
       </c>
       <c r="Q16">
-        <v>67.35409516865427</v>
+        <v>67.82848726865427</v>
       </c>
       <c r="R16">
         <v>0.1627906976744186</v>
       </c>
       <c r="S16">
-        <v>0.1158427161478091</v>
+        <v>0.1158237652945532</v>
       </c>
       <c r="T16">
         <v>1.083245378880736</v>
       </c>
       <c r="U16">
-        <v>0.07373097776675759</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V16">
         <v>0.25</v>
       </c>
       <c r="W16">
-        <v>0.0552982333250682</v>
+        <v>0.05334823332506819</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>5.349570758321598</v>
+        <v>5.545109810480339</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2654,13 +2654,13 @@
         <v>0.15</v>
       </c>
       <c r="B17">
-        <v>0.1073054171659613</v>
+        <v>0.1069966616542695</v>
       </c>
       <c r="C17">
-        <v>1525.981555366946</v>
+        <v>1533.396243822947</v>
       </c>
       <c r="D17">
-        <v>1546.436555366946</v>
+        <v>1553.851243822947</v>
       </c>
       <c r="E17">
         <v>-172.045</v>
@@ -2687,37 +2687,37 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M17">
-        <v>19.2183480097942</v>
+        <v>18.5406450097942</v>
       </c>
       <c r="N17">
-        <v>76.73757035755274</v>
+        <v>77.41527335755273</v>
       </c>
       <c r="O17">
-        <v>19.18439258938819</v>
+        <v>19.35381833938818</v>
       </c>
       <c r="P17">
-        <v>57.55317776816456</v>
+        <v>58.06145501816455</v>
       </c>
       <c r="Q17">
-        <v>66.39317776816456</v>
+        <v>66.90145501816455</v>
       </c>
       <c r="R17">
         <v>0.1764705882352941</v>
       </c>
       <c r="S17">
-        <v>0.1164831554908248</v>
+        <v>0.1164640313594226</v>
       </c>
       <c r="T17">
         <v>1.093150091275257</v>
       </c>
       <c r="U17">
-        <v>0.07373097776675759</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V17">
         <v>0.25</v>
       </c>
       <c r="W17">
-        <v>0.0552982333250682</v>
+        <v>0.05334823332506819</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>4.992932707766826</v>
+        <v>5.175435823114983</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2736,13 +2736,13 @@
         <v>0.16</v>
       </c>
       <c r="B18">
-        <v>0.1072443457792972</v>
+        <v>0.1069161324897136</v>
       </c>
       <c r="C18">
-        <v>1510.14160525537</v>
+        <v>1518.066663013456</v>
       </c>
       <c r="D18">
-        <v>1547.97360525537</v>
+        <v>1555.898663013455</v>
       </c>
       <c r="E18">
         <v>-154.6679999999999</v>
@@ -2769,37 +2769,37 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M18">
-        <v>20.49957121044715</v>
+        <v>19.77668801044715</v>
       </c>
       <c r="N18">
-        <v>75.4563471568998</v>
+        <v>76.17923035689979</v>
       </c>
       <c r="O18">
-        <v>18.86408678922495</v>
+        <v>19.04480758922495</v>
       </c>
       <c r="P18">
-        <v>56.59226036767485</v>
+        <v>57.13442276767485</v>
       </c>
       <c r="Q18">
-        <v>65.43226036767484</v>
+        <v>65.97442276767485</v>
       </c>
       <c r="R18">
         <v>0.1904761904761905</v>
       </c>
       <c r="S18">
-        <v>0.1171388433896265</v>
+        <v>0.117119541854408</v>
       </c>
       <c r="T18">
         <v>1.103290630155361</v>
       </c>
       <c r="U18">
-        <v>0.07373097776675759</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V18">
         <v>0.25</v>
       </c>
       <c r="W18">
-        <v>0.0552982333250682</v>
+        <v>0.05334823332506819</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>4.680874413531399</v>
+        <v>4.851971084170296</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2818,13 +2818,13 @@
         <v>0.17</v>
       </c>
       <c r="B19">
-        <v>0.107514774392633</v>
+        <v>0.1068356033251578</v>
       </c>
       <c r="C19">
-        <v>1485.981523575666</v>
+        <v>1502.742484852513</v>
       </c>
       <c r="D19">
-        <v>1541.190523575666</v>
+        <v>1557.951484852513</v>
       </c>
       <c r="E19">
         <v>-137.2909999999999</v>
@@ -2851,45 +2851,45 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M19">
-        <v>22.5488578111001</v>
+        <v>21.01273101110009</v>
       </c>
       <c r="N19">
-        <v>73.40706055624685</v>
+        <v>74.94318735624685</v>
       </c>
       <c r="O19">
-        <v>18.35176513906171</v>
+        <v>18.73579683906171</v>
       </c>
       <c r="P19">
-        <v>55.05529541718514</v>
+        <v>56.20739051718514</v>
       </c>
       <c r="Q19">
-        <v>63.89529541718514</v>
+        <v>65.04739051718514</v>
       </c>
       <c r="R19">
         <v>0.2048192771084338</v>
       </c>
       <c r="S19">
-        <v>0.1178103309968331</v>
+        <v>0.1177908477830075</v>
       </c>
       <c r="T19">
         <v>1.113675519369926</v>
       </c>
       <c r="U19">
-        <v>0.0763309777667576</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V19">
         <v>0.25</v>
       </c>
       <c r="W19">
-        <v>0.0572482333250682</v>
+        <v>0.05334823332506819</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y19">
-        <v>4.255466914164975</v>
+        <v>4.566561020395573</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2900,13 +2900,13 @@
         <v>0.18</v>
       </c>
       <c r="B20">
-        <v>0.1074732030059689</v>
+        <v>0.107092574160602</v>
       </c>
       <c r="C20">
-        <v>1469.64337714668</v>
+        <v>1478.833729576663</v>
       </c>
       <c r="D20">
-        <v>1542.22937714668</v>
+        <v>1551.419729576663</v>
       </c>
       <c r="E20">
         <v>-119.914</v>
@@ -2933,37 +2933,37 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M20">
-        <v>23.87526121175304</v>
+        <v>23.03073901175304</v>
       </c>
       <c r="N20">
-        <v>72.0806571555939</v>
+        <v>72.9251793555939</v>
       </c>
       <c r="O20">
-        <v>18.02016428889847</v>
+        <v>18.23129483889847</v>
       </c>
       <c r="P20">
-        <v>54.06049286669543</v>
+        <v>54.69388451669542</v>
       </c>
       <c r="Q20">
-        <v>62.90049286669543</v>
+        <v>63.53388451669542</v>
       </c>
       <c r="R20">
         <v>0.2195121951219512</v>
       </c>
       <c r="S20">
-        <v>0.1184981963505569</v>
+        <v>0.1184785270269386</v>
       </c>
       <c r="T20">
         <v>1.124313698565334</v>
       </c>
       <c r="U20">
-        <v>0.0763309777667576</v>
+        <v>0.07363097776675759</v>
       </c>
       <c r="V20">
         <v>0.25</v>
       </c>
       <c r="W20">
-        <v>0.0572482333250682</v>
+        <v>0.05522323332506819</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>4.019052085600255</v>
+        <v>4.1664281080333</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2982,13 +2982,13 @@
         <v>0.19</v>
       </c>
       <c r="B21">
-        <v>0.1078163816193048</v>
+        <v>0.1075295449960462</v>
       </c>
       <c r="C21">
-        <v>1443.732178193507</v>
+        <v>1450.474546322256</v>
       </c>
       <c r="D21">
-        <v>1533.695178193507</v>
+        <v>1540.437546322256</v>
       </c>
       <c r="E21">
         <v>-102.537</v>
@@ -3015,37 +3015,37 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M21">
-        <v>26.09310471240599</v>
+        <v>25.46579501240599</v>
       </c>
       <c r="N21">
-        <v>69.86281365494095</v>
+        <v>70.49012335494095</v>
       </c>
       <c r="O21">
-        <v>17.46570341373524</v>
+        <v>17.62253083873524</v>
       </c>
       <c r="P21">
-        <v>52.39711024120571</v>
+        <v>52.86759251620571</v>
       </c>
       <c r="Q21">
-        <v>61.23711024120571</v>
+        <v>61.70759251620571</v>
       </c>
       <c r="R21">
         <v>0.2345679012345679</v>
       </c>
       <c r="S21">
-        <v>0.1192030460340023</v>
+        <v>0.1191831860052879</v>
       </c>
       <c r="T21">
         <v>1.135214548851987</v>
       </c>
       <c r="U21">
-        <v>0.07903097776675759</v>
+        <v>0.07713097776675759</v>
       </c>
       <c r="V21">
         <v>0.25</v>
       </c>
       <c r="W21">
-        <v>0.05927323332506819</v>
+        <v>0.05784823332506819</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>3.677443501835357</v>
+        <v>3.768031523092084</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3064,13 +3064,13 @@
         <v>0.2</v>
       </c>
       <c r="B22">
-        <v>0.1085000602326407</v>
+        <v>0.1074940158314903</v>
       </c>
       <c r="C22">
-        <v>1409.631835523394</v>
+        <v>1433.984673839142</v>
       </c>
       <c r="D22">
-        <v>1516.971835523394</v>
+        <v>1541.324673839141</v>
       </c>
       <c r="E22">
         <v>-85.15999999999997</v>
@@ -3097,45 +3097,45 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M22">
-        <v>29.09986401305893</v>
+        <v>26.80610001305893</v>
       </c>
       <c r="N22">
-        <v>66.85605435428801</v>
+        <v>69.149818354288</v>
       </c>
       <c r="O22">
-        <v>16.714013588572</v>
+        <v>17.287454588572</v>
       </c>
       <c r="P22">
-        <v>50.142040765716</v>
+        <v>51.862363765716</v>
       </c>
       <c r="Q22">
-        <v>58.98204076571601</v>
+        <v>60.702363765716</v>
       </c>
       <c r="R22">
         <v>0.25</v>
       </c>
       <c r="S22">
-        <v>0.1199255169595338</v>
+        <v>0.1199054614580958</v>
       </c>
       <c r="T22">
         <v>1.146387920395805</v>
       </c>
       <c r="U22">
-        <v>0.08373097776675759</v>
+        <v>0.07713097776675759</v>
       </c>
       <c r="V22">
         <v>0.25</v>
       </c>
       <c r="W22">
-        <v>0.06279823332506819</v>
+        <v>0.05784823332506819</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y22">
-        <v>3.297469648802672</v>
+        <v>3.57962994693748</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3146,13 +3146,13 @@
         <v>0.21</v>
       </c>
       <c r="B23">
-        <v>0.1085139888459765</v>
+        <v>0.1078994866669345</v>
       </c>
       <c r="C23">
-        <v>1391.917920035681</v>
+        <v>1406.543787054631</v>
       </c>
       <c r="D23">
-        <v>1516.634920035681</v>
+        <v>1531.260787054631</v>
       </c>
       <c r="E23">
         <v>-67.78300000000002</v>
@@ -3179,37 +3179,37 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M23">
-        <v>30.55485721371188</v>
+        <v>29.16817261371188</v>
       </c>
       <c r="N23">
-        <v>65.40106115363506</v>
+        <v>66.78774575363506</v>
       </c>
       <c r="O23">
-        <v>16.35026528840876</v>
+        <v>16.69693643840877</v>
       </c>
       <c r="P23">
-        <v>49.05079586522629</v>
+        <v>50.09080931522629</v>
       </c>
       <c r="Q23">
-        <v>57.89079586522629</v>
+        <v>58.9308093152263</v>
       </c>
       <c r="R23">
         <v>0.2658227848101266</v>
       </c>
       <c r="S23">
-        <v>0.1206662782882433</v>
+        <v>0.1206460223654053</v>
       </c>
       <c r="T23">
         <v>1.15784416210529</v>
       </c>
       <c r="U23">
-        <v>0.08373097776675759</v>
+        <v>0.07993097776675759</v>
       </c>
       <c r="V23">
         <v>0.25</v>
       </c>
       <c r="W23">
-        <v>0.06279823332506819</v>
+        <v>0.05994823332506819</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>3.140447284573973</v>
+        <v>3.289747343384766</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3228,13 +3228,13 @@
         <v>0.22</v>
       </c>
       <c r="B24">
-        <v>0.1100624174593124</v>
+        <v>0.1078849575023786</v>
       </c>
       <c r="C24">
-        <v>1337.996995934873</v>
+        <v>1389.525133759663</v>
       </c>
       <c r="D24">
-        <v>1480.090995934873</v>
+        <v>1531.619133759663</v>
       </c>
       <c r="E24">
         <v>-50.40599999999995</v>
@@ -3261,45 +3261,45 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M24">
-        <v>35.56518461436483</v>
+        <v>30.55713321436483</v>
       </c>
       <c r="N24">
-        <v>60.39073375298211</v>
+        <v>65.39878515298211</v>
       </c>
       <c r="O24">
-        <v>15.09768343824553</v>
+        <v>16.34969628824553</v>
       </c>
       <c r="P24">
-        <v>45.29305031473658</v>
+        <v>49.04908886473659</v>
       </c>
       <c r="Q24">
-        <v>54.13305031473658</v>
+        <v>57.88908886473659</v>
       </c>
       <c r="R24">
         <v>0.282051282051282</v>
       </c>
       <c r="S24">
-        <v>0.1214260334971762</v>
+        <v>0.1214055720139277</v>
       </c>
       <c r="T24">
         <v>1.169594153602198</v>
       </c>
       <c r="U24">
-        <v>0.09303097776675759</v>
+        <v>0.07993097776675759</v>
       </c>
       <c r="V24">
         <v>0.25</v>
       </c>
       <c r="W24">
-        <v>0.06977323332506818</v>
+        <v>0.05994823332506819</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y24">
-        <v>2.698029531065338</v>
+        <v>3.140213373230913</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3310,13 +3310,13 @@
         <v>0.23</v>
       </c>
       <c r="B25">
-        <v>0.1101460960726483</v>
+        <v>0.1078704283378228</v>
       </c>
       <c r="C25">
-        <v>1318.695217747694</v>
+        <v>1372.50664822504</v>
       </c>
       <c r="D25">
-        <v>1478.166217747694</v>
+        <v>1531.97764822504</v>
       </c>
       <c r="E25">
         <v>-33.02899999999994</v>
@@ -3343,45 +3343,45 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M25">
-        <v>37.18178391501777</v>
+        <v>31.94609381501778</v>
       </c>
       <c r="N25">
-        <v>58.77413445232916</v>
+        <v>64.00982455232916</v>
       </c>
       <c r="O25">
-        <v>14.69353361308229</v>
+        <v>16.00245613808229</v>
       </c>
       <c r="P25">
-        <v>44.08060083924687</v>
+        <v>48.00736841424687</v>
       </c>
       <c r="Q25">
-        <v>52.92060083924687</v>
+        <v>56.84736841424687</v>
       </c>
       <c r="R25">
         <v>0.2987012987012987</v>
       </c>
       <c r="S25">
-        <v>0.1222055226076397</v>
+        <v>0.1221848502247495</v>
       </c>
       <c r="T25">
         <v>1.181649339683441</v>
       </c>
       <c r="U25">
-        <v>0.09303097776675759</v>
+        <v>0.07993097776675759</v>
       </c>
       <c r="V25">
         <v>0.25</v>
       </c>
       <c r="W25">
-        <v>0.06977323332506818</v>
+        <v>0.05994823332506819</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y25">
-        <v>2.58072389927989</v>
+        <v>3.003682357003482</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3392,13 +3392,13 @@
         <v>0.24</v>
       </c>
       <c r="B26">
-        <v>0.1110757746859842</v>
+        <v>0.109259899173267</v>
       </c>
       <c r="C26">
-        <v>1280.265698245528</v>
+        <v>1321.586603081694</v>
       </c>
       <c r="D26">
-        <v>1457.113698245528</v>
+        <v>1498.434603081694</v>
       </c>
       <c r="E26">
         <v>-15.65199999999999</v>
@@ -3425,45 +3425,45 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M26">
-        <v>40.75850881567072</v>
+        <v>36.58802881567072</v>
       </c>
       <c r="N26">
-        <v>55.19740955167622</v>
+        <v>59.36788955167622</v>
       </c>
       <c r="O26">
-        <v>13.79935238791905</v>
+        <v>14.84197238791906</v>
       </c>
       <c r="P26">
-        <v>41.39805716375716</v>
+        <v>44.52591716375716</v>
       </c>
       <c r="Q26">
-        <v>50.23805716375716</v>
+        <v>53.36591716375716</v>
       </c>
       <c r="R26">
         <v>0.3157894736842105</v>
       </c>
       <c r="S26">
-        <v>0.1230055245894313</v>
+        <v>0.1229846357569087</v>
       </c>
       <c r="T26">
         <v>1.194021767503664</v>
       </c>
       <c r="U26">
-        <v>0.0977309777667576</v>
+        <v>0.08773097776675759</v>
       </c>
       <c r="V26">
         <v>0.25</v>
       </c>
       <c r="W26">
-        <v>0.0732982333250682</v>
+        <v>0.06579823332506819</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y26">
-        <v>2.35425488212302</v>
+        <v>2.622604208900395</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3474,13 +3474,13 @@
         <v>0.25</v>
       </c>
       <c r="B27">
-        <v>0.11119470329932</v>
+        <v>0.1093038700087111</v>
       </c>
       <c r="C27">
-        <v>1260.238751034791</v>
+        <v>1303.172069127514</v>
       </c>
       <c r="D27">
-        <v>1454.463751034791</v>
+        <v>1497.397069127514</v>
       </c>
       <c r="E27">
         <v>1.725000000000023</v>
@@ -3507,45 +3507,45 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M27">
-        <v>42.45678001632367</v>
+        <v>38.11253001632367</v>
       </c>
       <c r="N27">
-        <v>53.49913835102327</v>
+        <v>57.84338835102327</v>
       </c>
       <c r="O27">
-        <v>13.37478458775582</v>
+        <v>14.46084708775582</v>
       </c>
       <c r="P27">
-        <v>40.12435376326745</v>
+        <v>43.38254126326746</v>
       </c>
       <c r="Q27">
-        <v>48.96435376326745</v>
+        <v>52.22254126326746</v>
       </c>
       <c r="R27">
         <v>0.3333333333333333</v>
       </c>
       <c r="S27">
-        <v>0.123826859957404</v>
+        <v>0.1238057489032588</v>
       </c>
       <c r="T27">
         <v>1.206724126732427</v>
       </c>
       <c r="U27">
-        <v>0.0977309777667576</v>
+        <v>0.08773097776675759</v>
       </c>
       <c r="V27">
         <v>0.25</v>
       </c>
       <c r="W27">
-        <v>0.0732982333250682</v>
+        <v>0.06579823332506819</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y27">
-        <v>2.260084686838099</v>
+        <v>2.517700040544379</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3556,13 +3556,13 @@
         <v>0.26</v>
       </c>
       <c r="B28">
-        <v>0.1113136319126559</v>
+        <v>0.1101083408441553</v>
       </c>
       <c r="C28">
-        <v>1240.221424861324</v>
+        <v>1267.063249034193</v>
       </c>
       <c r="D28">
-        <v>1451.823424861324</v>
+        <v>1478.665249034193</v>
       </c>
       <c r="E28">
         <v>19.10200000000003</v>
@@ -3589,37 +3589,37 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M28">
-        <v>44.15505121697662</v>
+        <v>41.39905901697662</v>
       </c>
       <c r="N28">
-        <v>51.80086715037032</v>
+        <v>54.55685935037032</v>
       </c>
       <c r="O28">
-        <v>12.95021678759258</v>
+        <v>13.63921483759258</v>
       </c>
       <c r="P28">
-        <v>38.85065036277774</v>
+        <v>40.91764451277774</v>
       </c>
       <c r="Q28">
-        <v>47.69065036277775</v>
+        <v>49.75764451277774</v>
       </c>
       <c r="R28">
         <v>0.3513513513513514</v>
       </c>
       <c r="S28">
-        <v>0.1246703935785651</v>
+        <v>0.1246490542968075</v>
       </c>
       <c r="T28">
         <v>1.219769792967372</v>
       </c>
       <c r="U28">
-        <v>0.0977309777667576</v>
+        <v>0.09163097776675759</v>
       </c>
       <c r="V28">
         <v>0.25</v>
       </c>
       <c r="W28">
-        <v>0.0732982333250682</v>
+        <v>0.06872323332506819</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>2.173158352728941</v>
+        <v>2.317828488033944</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3638,13 +3638,13 @@
         <v>0.27</v>
       </c>
       <c r="B29">
-        <v>0.1114325605259918</v>
+        <v>0.1101815616795995</v>
       </c>
       <c r="C29">
-        <v>1220.213667424108</v>
+        <v>1248.004570273194</v>
       </c>
       <c r="D29">
-        <v>1449.192667424108</v>
+        <v>1476.983570273194</v>
       </c>
       <c r="E29">
         <v>36.47900000000004</v>
@@ -3671,37 +3671,37 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M29">
-        <v>45.85332241762956</v>
+        <v>42.99133051762956</v>
       </c>
       <c r="N29">
-        <v>50.10259594971738</v>
+        <v>52.96458784971738</v>
       </c>
       <c r="O29">
-        <v>12.52564898742934</v>
+        <v>13.24114696242934</v>
       </c>
       <c r="P29">
-        <v>37.57694696228803</v>
+        <v>39.72344088728804</v>
       </c>
       <c r="Q29">
-        <v>46.41694696228804</v>
+        <v>48.56344088728804</v>
       </c>
       <c r="R29">
         <v>0.3698630136986302</v>
       </c>
       <c r="S29">
-        <v>0.125537037709895</v>
+        <v>0.1255154639477138</v>
       </c>
       <c r="T29">
         <v>1.233172874715603</v>
       </c>
       <c r="U29">
-        <v>0.0977309777667576</v>
+        <v>0.09163097776675759</v>
       </c>
       <c r="V29">
         <v>0.25</v>
       </c>
       <c r="W29">
-        <v>0.0732982333250682</v>
+        <v>0.06872323332506819</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>2.092671006331573</v>
+        <v>2.231982988477132</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3720,13 +3720,13 @@
         <v>0.28</v>
       </c>
       <c r="B30">
-        <v>0.1115514891393277</v>
+        <v>0.1102547825150436</v>
       </c>
       <c r="C30">
-        <v>1200.215426800522</v>
+        <v>1228.949712296907</v>
       </c>
       <c r="D30">
-        <v>1446.571426800522</v>
+        <v>1475.305712296907</v>
       </c>
       <c r="E30">
         <v>53.85600000000005</v>
@@ -3753,37 +3753,37 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M30">
-        <v>47.55159361828252</v>
+        <v>44.58360201828251</v>
       </c>
       <c r="N30">
-        <v>48.40432474906442</v>
+        <v>51.37231634906443</v>
       </c>
       <c r="O30">
-        <v>12.10108118726611</v>
+        <v>12.84307908726611</v>
       </c>
       <c r="P30">
-        <v>36.30324356179832</v>
+        <v>38.52923726179832</v>
       </c>
       <c r="Q30">
-        <v>45.14324356179831</v>
+        <v>47.36923726179832</v>
       </c>
       <c r="R30">
         <v>0.388888888888889</v>
       </c>
       <c r="S30">
-        <v>0.1264277552893174</v>
+        <v>0.1264059405333674</v>
       </c>
       <c r="T30">
         <v>1.246948264290174</v>
       </c>
       <c r="U30">
-        <v>0.0977309777667576</v>
+        <v>0.09163097776675759</v>
       </c>
       <c r="V30">
         <v>0.25</v>
       </c>
       <c r="W30">
-        <v>0.0732982333250682</v>
+        <v>0.06872323332506819</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>2.017932756105445</v>
+        <v>2.152269310317234</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3802,13 +3802,13 @@
         <v>0.29</v>
       </c>
       <c r="B31">
-        <v>0.1152156677526635</v>
+        <v>0.1103280033504878</v>
       </c>
       <c r="C31">
-        <v>1106.479641293602</v>
+        <v>1209.898662098838</v>
       </c>
       <c r="D31">
-        <v>1370.212641293602</v>
+        <v>1473.631662098838</v>
       </c>
       <c r="E31">
         <v>71.233</v>
@@ -3835,45 +3835,45 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M31">
-        <v>57.46397271893546</v>
+        <v>46.17587351893545</v>
       </c>
       <c r="N31">
-        <v>38.49194564841148</v>
+        <v>49.78004484841149</v>
       </c>
       <c r="O31">
-        <v>9.62298641210287</v>
+        <v>12.44501121210287</v>
       </c>
       <c r="P31">
-        <v>28.86895923630861</v>
+        <v>37.33503363630862</v>
       </c>
       <c r="Q31">
-        <v>37.70895923630862</v>
+        <v>46.17503363630861</v>
       </c>
       <c r="R31">
         <v>0.4084507042253521</v>
       </c>
       <c r="S31">
-        <v>0.1273435635047799</v>
+        <v>0.1273215009665042</v>
       </c>
       <c r="T31">
         <v>1.261111693007691</v>
       </c>
       <c r="U31">
-        <v>0.1140309777667576</v>
+        <v>0.09163097776675759</v>
       </c>
       <c r="V31">
         <v>0.25</v>
       </c>
       <c r="W31">
-        <v>0.0855232333250682</v>
+        <v>0.06872323332506819</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y31">
-        <v>1.669844840639214</v>
+        <v>2.078053127202847</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3884,13 +3884,13 @@
         <v>0.3</v>
       </c>
       <c r="B32">
-        <v>0.1154568463659994</v>
+        <v>0.1104012241859319</v>
       </c>
       <c r="C32">
-        <v>1084.358441662943</v>
+        <v>1190.851406731458</v>
       </c>
       <c r="D32">
-        <v>1365.468441662943</v>
+        <v>1471.961406731458</v>
       </c>
       <c r="E32">
         <v>88.60999999999996</v>
@@ -3917,45 +3917,45 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M32">
-        <v>59.4454890195884</v>
+        <v>47.7681450195884</v>
       </c>
       <c r="N32">
-        <v>36.51042934775854</v>
+        <v>48.18777334775854</v>
       </c>
       <c r="O32">
-        <v>9.127607336939635</v>
+        <v>12.04694333693964</v>
       </c>
       <c r="P32">
-        <v>27.38282201081891</v>
+        <v>36.14083001081891</v>
       </c>
       <c r="Q32">
-        <v>36.2228220108189</v>
+        <v>44.98083001081891</v>
       </c>
       <c r="R32">
         <v>0.4285714285714286</v>
       </c>
       <c r="S32">
-        <v>0.1282855376692556</v>
+        <v>0.1282632202691593</v>
       </c>
       <c r="T32">
         <v>1.275679791117137</v>
       </c>
       <c r="U32">
-        <v>0.1140309777667576</v>
+        <v>0.09163097776675759</v>
       </c>
       <c r="V32">
         <v>0.25</v>
       </c>
       <c r="W32">
-        <v>0.0855232333250682</v>
+        <v>0.06872323332506819</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y32">
-        <v>1.614183345951241</v>
+        <v>2.008784689629419</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3966,13 +3966,13 @@
         <v>0.31</v>
       </c>
       <c r="B33">
-        <v>0.1156980249793353</v>
+        <v>0.1137759450213761</v>
       </c>
       <c r="C33">
-        <v>1062.269981140109</v>
+        <v>1100.397690744586</v>
       </c>
       <c r="D33">
-        <v>1360.756981140109</v>
+        <v>1398.884690744586</v>
       </c>
       <c r="E33">
         <v>105.987</v>
@@ -3999,37 +3999,37 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M33">
-        <v>61.42700532024136</v>
+        <v>57.00977192024135</v>
       </c>
       <c r="N33">
-        <v>34.52891304710558</v>
+        <v>38.94614644710559</v>
       </c>
       <c r="O33">
-        <v>8.632228261776396</v>
+        <v>9.736536611776398</v>
       </c>
       <c r="P33">
-        <v>25.89668478532919</v>
+        <v>29.20960983532919</v>
       </c>
       <c r="Q33">
-        <v>34.73668478532919</v>
+        <v>38.04960983532919</v>
       </c>
       <c r="R33">
         <v>0.4492753623188406</v>
       </c>
       <c r="S33">
-        <v>0.1292548154327016</v>
+        <v>0.1292322357834854</v>
       </c>
       <c r="T33">
         <v>1.2906701529399</v>
       </c>
       <c r="U33">
-        <v>0.1140309777667576</v>
+        <v>0.1058309777667576</v>
       </c>
       <c r="V33">
         <v>0.25</v>
       </c>
       <c r="W33">
-        <v>0.0855232333250682</v>
+        <v>0.0793732333250682</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>1.562112915436684</v>
+        <v>1.683148610059212</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4048,13 +4048,13 @@
         <v>0.32</v>
       </c>
       <c r="B34">
-        <v>0.1159392035926711</v>
+        <v>0.1139556658568203</v>
       </c>
       <c r="C34">
-        <v>1040.213921997887</v>
+        <v>1079.331947891734</v>
       </c>
       <c r="D34">
-        <v>1356.077921997887</v>
+        <v>1395.195947891734</v>
       </c>
       <c r="E34">
         <v>123.3640000000001</v>
@@ -4081,37 +4081,37 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M34">
-        <v>63.40852162089431</v>
+        <v>58.8487968208943</v>
       </c>
       <c r="N34">
-        <v>32.54739674645263</v>
+        <v>37.10712154645264</v>
       </c>
       <c r="O34">
-        <v>8.136849186613157</v>
+        <v>9.27678038661316</v>
       </c>
       <c r="P34">
-        <v>24.41054755983947</v>
+        <v>27.83034115983948</v>
       </c>
       <c r="Q34">
-        <v>33.25054755983948</v>
+        <v>36.67034115983948</v>
       </c>
       <c r="R34">
         <v>0.4705882352941177</v>
       </c>
       <c r="S34">
-        <v>0.1302526013656608</v>
+        <v>0.1302297517541154</v>
       </c>
       <c r="T34">
         <v>1.30610140775745</v>
       </c>
       <c r="U34">
-        <v>0.1140309777667576</v>
+        <v>0.1058309777667576</v>
       </c>
       <c r="V34">
         <v>0.25</v>
       </c>
       <c r="W34">
-        <v>0.0855232333250682</v>
+        <v>0.0793732333250682</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>1.513296886829288</v>
+        <v>1.630550215994862</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4130,13 +4130,13 @@
         <v>0.33</v>
       </c>
       <c r="B35">
-        <v>0.1337121231412983</v>
+        <v>0.1141353866922644</v>
       </c>
       <c r="C35">
-        <v>748.6828810290383</v>
+        <v>1058.28560769333</v>
       </c>
       <c r="D35">
-        <v>1081.923881029038</v>
+        <v>1391.52660769333</v>
       </c>
       <c r="E35">
         <v>140.741</v>
@@ -4163,45 +4163,45 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M35">
-        <v>102.8930793215472</v>
+        <v>60.68782172154724</v>
       </c>
       <c r="N35">
-        <v>-6.937160954200309</v>
+        <v>35.26809664579969</v>
       </c>
       <c r="O35">
-        <v>-1.734290238550077</v>
+        <v>8.817024161449924</v>
       </c>
       <c r="P35">
-        <v>-5.202870715650231</v>
+        <v>26.45107248434977</v>
       </c>
       <c r="Q35">
-        <v>3.637129284349768</v>
+        <v>35.29107248434977</v>
       </c>
       <c r="R35">
         <v>0.4925373134328359</v>
       </c>
       <c r="S35">
-        <v>0.1317983856280463</v>
+        <v>0.1312570443208835</v>
       </c>
       <c r="T35">
-        <v>1.330007728800771</v>
+        <v>1.321993297047166</v>
       </c>
       <c r="U35">
-        <v>0.1794309777667576</v>
+        <v>0.1058309777667576</v>
       </c>
       <c r="V35">
-        <v>0.2331447338345244</v>
+        <v>0.25</v>
       </c>
       <c r="W35">
-        <v>0.1375975902136584</v>
+        <v>0.0793732333250682</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y35">
-        <v>0.9325789353380974</v>
+        <v>1.581139603388957</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4212,13 +4212,13 @@
         <v>0.34</v>
       </c>
       <c r="B36">
-        <v>0.1350484329189659</v>
+        <v>0.1143151075277086</v>
       </c>
       <c r="C36">
-        <v>715.1063197188261</v>
+        <v>1037.258517465035</v>
       </c>
       <c r="D36">
-        <v>1065.724319718826</v>
+        <v>1387.876517465035</v>
       </c>
       <c r="E36">
         <v>158.1180000000001</v>
@@ -4245,45 +4245,45 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M36">
-        <v>106.0110514222002</v>
+        <v>62.5268466222002</v>
       </c>
       <c r="N36">
-        <v>-10.05513305485327</v>
+        <v>33.42907174514674</v>
       </c>
       <c r="O36">
-        <v>-2.513783263713318</v>
+        <v>8.357267936286686</v>
       </c>
       <c r="P36">
-        <v>-7.541349791139954</v>
+        <v>25.07180380886006</v>
       </c>
       <c r="Q36">
-        <v>1.298650208860046</v>
+        <v>33.91180380886006</v>
       </c>
       <c r="R36">
         <v>0.5151515151515152</v>
       </c>
       <c r="S36">
-        <v>0.1331013914708955</v>
+        <v>0.1323154669654324</v>
       </c>
       <c r="T36">
-        <v>1.350159361055328</v>
+        <v>1.338366758739601</v>
       </c>
       <c r="U36">
-        <v>0.1794309777667576</v>
+        <v>0.1058309777667576</v>
       </c>
       <c r="V36">
-        <v>0.2262875357805677</v>
+        <v>0.25</v>
       </c>
       <c r="W36">
-        <v>0.1388279839652202</v>
+        <v>0.0793732333250682</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y36">
-        <v>0.9051501431222708</v>
+        <v>1.534635497406929</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4294,13 +4294,13 @@
         <v>0.35</v>
       </c>
       <c r="B37">
-        <v>0.1363847426966335</v>
+        <v>0.1299931755360693</v>
       </c>
       <c r="C37">
-        <v>682.0077115722114</v>
+        <v>761.4375011955486</v>
       </c>
       <c r="D37">
-        <v>1050.002711572211</v>
+        <v>1129.432501195549</v>
       </c>
       <c r="E37">
         <v>175.4950000000001</v>
@@ -4327,37 +4327,37 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M37">
-        <v>109.1290235228531</v>
+        <v>98.91134752285315</v>
       </c>
       <c r="N37">
-        <v>-13.17310515550621</v>
+        <v>-2.955429155506209</v>
       </c>
       <c r="O37">
-        <v>-3.293276288876552</v>
+        <v>-0.7388572888765523</v>
       </c>
       <c r="P37">
-        <v>-9.879828866629655</v>
+        <v>-2.216571866629657</v>
       </c>
       <c r="Q37">
-        <v>-1.039828866629655</v>
+        <v>6.623428133370343</v>
       </c>
       <c r="R37">
         <v>0.5384615384615385</v>
       </c>
       <c r="S37">
-        <v>0.134444489801217</v>
+        <v>0.133657463400349</v>
       </c>
       <c r="T37">
-        <v>1.370931043533102</v>
+        <v>1.35912701678175</v>
       </c>
       <c r="U37">
-        <v>0.1794309777667576</v>
+        <v>0.1626309777667576</v>
       </c>
       <c r="V37">
-        <v>0.2198221776154087</v>
+        <v>0.2425301059243395</v>
       </c>
       <c r="W37">
-        <v>0.139988069502407</v>
+        <v>0.123188069502407</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.8792887104616347</v>
+        <v>0.9701204236973582</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4376,13 +4376,13 @@
         <v>0.36</v>
       </c>
       <c r="B38">
-        <v>0.1377210524743011</v>
+        <v>0.1311614853137369</v>
       </c>
       <c r="C38">
-        <v>649.3662117402095</v>
+        <v>728.6023934844126</v>
       </c>
       <c r="D38">
-        <v>1034.738211740209</v>
+        <v>1113.974393484413</v>
       </c>
       <c r="E38">
         <v>192.872</v>
@@ -4409,37 +4409,37 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M38">
-        <v>112.2469956235061</v>
+        <v>101.7373860235061</v>
       </c>
       <c r="N38">
-        <v>-16.29107725615914</v>
+        <v>-5.781467656159151</v>
       </c>
       <c r="O38">
-        <v>-4.072769314039785</v>
+        <v>-1.445366914039788</v>
       </c>
       <c r="P38">
-        <v>-12.21830794211936</v>
+        <v>-4.336100742119363</v>
       </c>
       <c r="Q38">
-        <v>-3.378307942119356</v>
+        <v>4.503899257880636</v>
       </c>
       <c r="R38">
         <v>0.5625</v>
       </c>
       <c r="S38">
-        <v>0.135829559954361</v>
+        <v>0.1350302362659795</v>
       </c>
       <c r="T38">
-        <v>1.392351841088307</v>
+        <v>1.380363376418964</v>
       </c>
       <c r="U38">
-        <v>0.1794309777667576</v>
+        <v>0.1626309777667576</v>
       </c>
       <c r="V38">
-        <v>0.2137160060149807</v>
+        <v>0.2357931585375524</v>
       </c>
       <c r="W38">
-        <v>0.1410837058430834</v>
+        <v>0.1242837058430834</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.8548640240599227</v>
+        <v>0.9431726341502095</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4458,13 +4458,13 @@
         <v>0.37</v>
       </c>
       <c r="B39">
-        <v>0.1390573622519686</v>
+        <v>0.1323297950914045</v>
       </c>
       <c r="C39">
-        <v>617.1621701395821</v>
+        <v>696.1847109703216</v>
       </c>
       <c r="D39">
-        <v>1019.911170139582</v>
+        <v>1098.933710970321</v>
       </c>
       <c r="E39">
         <v>210.249</v>
@@ -4491,37 +4491,37 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M39">
-        <v>115.364967724159</v>
+        <v>104.563424524159</v>
       </c>
       <c r="N39">
-        <v>-19.40904935681208</v>
+        <v>-8.607506156812093</v>
       </c>
       <c r="O39">
-        <v>-4.852262339203019</v>
+        <v>-2.151876539203023</v>
       </c>
       <c r="P39">
-        <v>-14.55678701760906</v>
+        <v>-6.45562961760907</v>
       </c>
       <c r="Q39">
-        <v>-5.716787017609057</v>
+        <v>2.38437038239093</v>
       </c>
       <c r="R39">
         <v>0.5873015873015873</v>
       </c>
       <c r="S39">
-        <v>0.1372586005885572</v>
+        <v>0.1364465892225823</v>
       </c>
       <c r="T39">
-        <v>1.414452663962725</v>
+        <v>1.402273906203392</v>
       </c>
       <c r="U39">
-        <v>0.1794309777667576</v>
+        <v>0.1626309777667576</v>
       </c>
       <c r="V39">
-        <v>0.2079398977443055</v>
+        <v>0.2294203704689699</v>
       </c>
       <c r="W39">
-        <v>0.1421201185977773</v>
+        <v>0.1253201185977773</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.8317595909772222</v>
+        <v>0.9176814818758795</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4540,13 +4540,13 @@
         <v>0.38</v>
       </c>
       <c r="B40">
-        <v>0.1403936720296362</v>
+        <v>0.133498104869072</v>
       </c>
       <c r="C40">
-        <v>585.3770470615088</v>
+        <v>664.1677709003293</v>
       </c>
       <c r="D40">
-        <v>1005.503047061509</v>
+        <v>1084.293770900329</v>
       </c>
       <c r="E40">
         <v>227.626</v>
@@ -4573,37 +4573,37 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M40">
-        <v>118.482939824812</v>
+        <v>107.389463024812</v>
       </c>
       <c r="N40">
-        <v>-22.52702145746504</v>
+        <v>-11.43354465746505</v>
       </c>
       <c r="O40">
-        <v>-5.63175536436626</v>
+        <v>-2.858386164366262</v>
       </c>
       <c r="P40">
-        <v>-16.89526609309878</v>
+        <v>-8.575158493098787</v>
       </c>
       <c r="Q40">
-        <v>-8.05526609309878</v>
+        <v>0.2648415069012131</v>
       </c>
       <c r="R40">
         <v>0.6129032258064516</v>
       </c>
       <c r="S40">
-        <v>0.1387337393077275</v>
+        <v>0.1379086309842369</v>
       </c>
       <c r="T40">
-        <v>1.437266416607285</v>
+        <v>1.424891227271189</v>
       </c>
       <c r="U40">
-        <v>0.1794309777667576</v>
+        <v>0.1626309777667576</v>
       </c>
       <c r="V40">
-        <v>0.2024677951720869</v>
+        <v>0.2233829922987338</v>
       </c>
       <c r="W40">
-        <v>0.1431019833127504</v>
+        <v>0.1263019833127504</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.8098711806883478</v>
+        <v>0.8935319691949353</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4622,13 +4622,13 @@
         <v>0.39</v>
       </c>
       <c r="B41">
-        <v>0.1631702814862281</v>
+        <v>0.1346664146467396</v>
       </c>
       <c r="C41">
-        <v>372.874416277191</v>
+        <v>632.5357678213524</v>
       </c>
       <c r="D41">
-        <v>810.3774162771912</v>
+        <v>1070.038767821352</v>
       </c>
       <c r="E41">
         <v>245.0030000000001</v>
@@ -4655,45 +4655,45 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M41">
-        <v>156.977008525465</v>
+        <v>110.2155015254649</v>
       </c>
       <c r="N41">
-        <v>-61.02109015811801</v>
+        <v>-14.25958315811801</v>
       </c>
       <c r="O41">
-        <v>-15.2552725395295</v>
+        <v>-3.564895789529501</v>
       </c>
       <c r="P41">
-        <v>-45.76581761858851</v>
+        <v>-10.6946873685885</v>
       </c>
       <c r="Q41">
-        <v>-36.92581761858851</v>
+        <v>-1.854687368588504</v>
       </c>
       <c r="R41">
         <v>0.639344262295082</v>
       </c>
       <c r="S41">
-        <v>0.1420315049995334</v>
+        <v>0.1394186085413555</v>
       </c>
       <c r="T41">
-        <v>1.488268000251496</v>
+        <v>1.448250099849405</v>
       </c>
       <c r="U41">
-        <v>0.2316309777667576</v>
+        <v>0.1626309777667576</v>
       </c>
       <c r="V41">
-        <v>0.1528184274701936</v>
+        <v>0.2176552232654329</v>
       </c>
       <c r="W41">
-        <v>0.1962334959910584</v>
+        <v>0.1272334959910583</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y41">
-        <v>0.6112737098807746</v>
+        <v>0.8706208930617316</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4704,13 +4704,13 @@
         <v>0.4</v>
       </c>
       <c r="B42">
-        <v>0.1650285912638957</v>
+        <v>0.1358347244244072</v>
       </c>
       <c r="C42">
-        <v>342.8667858193027</v>
+        <v>601.2737166600233</v>
       </c>
       <c r="D42">
-        <v>797.7467858193027</v>
+        <v>1056.153716660023</v>
       </c>
       <c r="E42">
         <v>262.3800000000001</v>
@@ -4737,45 +4737,45 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M42">
-        <v>161.0020600261179</v>
+        <v>113.0415400261179</v>
       </c>
       <c r="N42">
-        <v>-65.04614165877096</v>
+        <v>-17.08562165877095</v>
       </c>
       <c r="O42">
-        <v>-16.26153541469274</v>
+        <v>-4.271405414692737</v>
       </c>
       <c r="P42">
-        <v>-48.78460624407822</v>
+        <v>-12.81421624407821</v>
       </c>
       <c r="Q42">
-        <v>-39.94460624407822</v>
+        <v>-3.97421624407821</v>
       </c>
       <c r="R42">
         <v>0.6666666666666667</v>
       </c>
       <c r="S42">
-        <v>0.1436353634161923</v>
+        <v>0.1409789186837115</v>
       </c>
       <c r="T42">
-        <v>1.513072466922354</v>
+        <v>1.472387601513562</v>
       </c>
       <c r="U42">
-        <v>0.2316309777667576</v>
+        <v>0.1626309777667576</v>
       </c>
       <c r="V42">
-        <v>0.1489979667834388</v>
+        <v>0.2122138426837971</v>
       </c>
       <c r="W42">
-        <v>0.1971184330354508</v>
+        <v>0.1281184330354508</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y42">
-        <v>0.5959918671337552</v>
+        <v>0.8488553707351885</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4786,13 +4786,13 @@
         <v>0.41</v>
       </c>
       <c r="B43">
-        <v>0.1668869010415633</v>
+        <v>0.1370030342020748</v>
       </c>
       <c r="C43">
-        <v>313.2468376602608</v>
+        <v>570.3674001774168</v>
       </c>
       <c r="D43">
-        <v>785.5038376602608</v>
+        <v>1042.624400177417</v>
       </c>
       <c r="E43">
         <v>279.7570000000001</v>
@@ -4819,45 +4819,45 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M43">
-        <v>165.0271115267709</v>
+        <v>115.8675785267708</v>
       </c>
       <c r="N43">
-        <v>-69.07119315942391</v>
+        <v>-19.9116601594239</v>
       </c>
       <c r="O43">
-        <v>-17.26779828985598</v>
+        <v>-4.977915039855976</v>
       </c>
       <c r="P43">
-        <v>-51.80339486956794</v>
+        <v>-14.93374511956793</v>
       </c>
       <c r="Q43">
-        <v>-42.96339486956794</v>
+        <v>-6.093745119567927</v>
       </c>
       <c r="R43">
         <v>0.6949152542372882</v>
       </c>
       <c r="S43">
-        <v>0.1452935899147719</v>
+        <v>0.1425921206952998</v>
       </c>
       <c r="T43">
-        <v>1.538717762971886</v>
+        <v>1.497343323573114</v>
       </c>
       <c r="U43">
-        <v>0.2316309777667576</v>
+        <v>0.1626309777667576</v>
       </c>
       <c r="V43">
-        <v>0.1453638700326232</v>
+        <v>0.2070378953012655</v>
       </c>
       <c r="W43">
-        <v>0.1979602024191412</v>
+        <v>0.1289602024191412</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y43">
-        <v>0.5814554801304929</v>
+        <v>0.8281515812050618</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4868,13 +4868,13 @@
         <v>0.42</v>
       </c>
       <c r="B44">
-        <v>0.1687452108192309</v>
+        <v>0.1381713439797423</v>
       </c>
       <c r="C44">
-        <v>283.9969924132369</v>
+        <v>539.8033204113241</v>
       </c>
       <c r="D44">
-        <v>773.6309924132368</v>
+        <v>1029.437320411324</v>
       </c>
       <c r="E44">
         <v>297.134</v>
@@ -4901,45 +4901,45 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M44">
-        <v>169.0521630274238</v>
+        <v>118.6936170274238</v>
       </c>
       <c r="N44">
-        <v>-73.09624466007683</v>
+        <v>-22.73769866007683</v>
       </c>
       <c r="O44">
-        <v>-18.27406116501921</v>
+        <v>-5.684424665019208</v>
       </c>
       <c r="P44">
-        <v>-54.82218349505763</v>
+        <v>-17.05327399505762</v>
       </c>
       <c r="Q44">
-        <v>-45.98218349505763</v>
+        <v>-8.213273995057623</v>
       </c>
       <c r="R44">
         <v>0.7241379310344827</v>
       </c>
       <c r="S44">
-        <v>0.1470089966374403</v>
+        <v>0.1442609503624601</v>
       </c>
       <c r="T44">
-        <v>1.565247379574849</v>
+        <v>1.52315958777265</v>
       </c>
       <c r="U44">
-        <v>0.2316309777667576</v>
+        <v>0.1626309777667576</v>
       </c>
       <c r="V44">
-        <v>0.141902825508037</v>
+        <v>0.2021084216036163</v>
       </c>
       <c r="W44">
-        <v>0.1987618875464654</v>
+        <v>0.1297618875464654</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y44">
-        <v>0.5676113020321478</v>
+        <v>0.8084336864144652</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4950,13 +4950,13 @@
         <v>0.43</v>
       </c>
       <c r="B45">
-        <v>0.1706035205968985</v>
+        <v>0.1638801084320711</v>
       </c>
       <c r="C45">
-        <v>255.1007177114307</v>
+        <v>298.2940601998907</v>
       </c>
       <c r="D45">
-        <v>762.1117177114307</v>
+        <v>805.3050601998908</v>
       </c>
       <c r="E45">
         <v>314.511</v>
@@ -4983,37 +4983,37 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M45">
-        <v>173.0772145280767</v>
+        <v>161.8690495280767</v>
       </c>
       <c r="N45">
-        <v>-77.12129616072978</v>
+        <v>-65.91313116072978</v>
       </c>
       <c r="O45">
-        <v>-19.28032404018245</v>
+        <v>-16.47828279018244</v>
       </c>
       <c r="P45">
-        <v>-57.84097212054733</v>
+        <v>-49.43484837054733</v>
       </c>
       <c r="Q45">
-        <v>-49.00097212054733</v>
+        <v>-40.59484837054733</v>
       </c>
       <c r="R45">
         <v>0.7543859649122806</v>
       </c>
       <c r="S45">
-        <v>0.1487845930696761</v>
+        <v>0.1483049226050667</v>
       </c>
       <c r="T45">
-        <v>1.592707859918267</v>
+        <v>1.585718552228483</v>
       </c>
       <c r="U45">
-        <v>0.2316309777667576</v>
+        <v>0.2166309777667576</v>
       </c>
       <c r="V45">
-        <v>0.1386027597985477</v>
+        <v>0.1481999163013295</v>
       </c>
       <c r="W45">
-        <v>0.199526284993449</v>
+        <v>0.1845262849934489</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.554411039194191</v>
+        <v>0.5927996652053181</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5032,13 +5032,13 @@
         <v>0.44</v>
       </c>
       <c r="B46">
-        <v>0.1724618303745661</v>
+        <v>0.1655884182097386</v>
       </c>
       <c r="C46">
-        <v>226.5424514016823</v>
+        <v>269.4325566985932</v>
       </c>
       <c r="D46">
-        <v>750.9304514016824</v>
+        <v>793.8205566985932</v>
       </c>
       <c r="E46">
         <v>331.8880000000001</v>
@@ -5065,37 +5065,37 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M46">
-        <v>177.1022660287297</v>
+        <v>165.6334460287297</v>
       </c>
       <c r="N46">
-        <v>-81.14634766138276</v>
+        <v>-69.67752766138274</v>
       </c>
       <c r="O46">
-        <v>-20.28658691534569</v>
+        <v>-17.41938191534569</v>
       </c>
       <c r="P46">
-        <v>-60.85976074603707</v>
+        <v>-52.25814574603706</v>
       </c>
       <c r="Q46">
-        <v>-52.01976074603706</v>
+        <v>-43.41814574603706</v>
       </c>
       <c r="R46">
         <v>0.7857142857142857</v>
       </c>
       <c r="S46">
-        <v>0.1506236036602061</v>
+        <v>0.1501353676515857</v>
       </c>
       <c r="T46">
-        <v>1.621149071702523</v>
+        <v>1.614034954946849</v>
       </c>
       <c r="U46">
-        <v>0.2316309777667576</v>
+        <v>0.2166309777667576</v>
       </c>
       <c r="V46">
-        <v>0.1354526970758534</v>
+        <v>0.1448317363853902</v>
       </c>
       <c r="W46">
-        <v>0.2002559371019333</v>
+        <v>0.1852559371019332</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.5418107883034138</v>
+        <v>0.5793269455415608</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5114,13 +5114,13 @@
         <v>0.45</v>
       </c>
       <c r="B47">
-        <v>0.1743201401522336</v>
+        <v>0.1672967279874062</v>
       </c>
       <c r="C47">
-        <v>198.3075314014776</v>
+        <v>240.8940098718975</v>
       </c>
       <c r="D47">
-        <v>740.0725314014777</v>
+        <v>782.6590098718976</v>
       </c>
       <c r="E47">
         <v>349.265</v>
@@ -5147,37 +5147,37 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M47">
-        <v>181.1273175293826</v>
+        <v>169.3978425293826</v>
       </c>
       <c r="N47">
-        <v>-85.17139916203568</v>
+        <v>-73.44192416203568</v>
       </c>
       <c r="O47">
-        <v>-21.29284979050892</v>
+        <v>-18.36048104050892</v>
       </c>
       <c r="P47">
-        <v>-63.87854937152676</v>
+        <v>-55.08144312152676</v>
       </c>
       <c r="Q47">
-        <v>-55.03854937152676</v>
+        <v>-46.24144312152676</v>
       </c>
       <c r="R47">
         <v>0.8181818181818181</v>
       </c>
       <c r="S47">
-        <v>0.1525294873631189</v>
+        <v>0.15203237433616</v>
       </c>
       <c r="T47">
-        <v>1.650624509369841</v>
+        <v>1.643381045036792</v>
       </c>
       <c r="U47">
-        <v>0.2316309777667576</v>
+        <v>0.2166309777667576</v>
       </c>
       <c r="V47">
-        <v>0.1324426371408345</v>
+        <v>0.1416132533546038</v>
       </c>
       <c r="W47">
-        <v>0.2009531602278182</v>
+        <v>0.1859531602278182</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.5297705485633379</v>
+        <v>0.5664530134184151</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5196,13 +5196,13 @@
         <v>0.46</v>
       </c>
       <c r="B48">
-        <v>0.1761784499299012</v>
+        <v>0.1690050377650738</v>
       </c>
       <c r="C48">
-        <v>170.3821315545244</v>
+        <v>212.6649857712823</v>
       </c>
       <c r="D48">
-        <v>729.5241315545245</v>
+        <v>771.8069857712824</v>
       </c>
       <c r="E48">
         <v>366.6420000000001</v>
@@ -5229,37 +5229,37 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M48">
-        <v>185.1523690300356</v>
+        <v>173.1622390300356</v>
       </c>
       <c r="N48">
-        <v>-89.19645066268866</v>
+        <v>-77.20632066268864</v>
       </c>
       <c r="O48">
-        <v>-22.29911266567217</v>
+        <v>-19.30158016567216</v>
       </c>
       <c r="P48">
-        <v>-66.89733799701649</v>
+        <v>-57.90474049701648</v>
       </c>
       <c r="Q48">
-        <v>-58.05733799701649</v>
+        <v>-49.06474049701647</v>
       </c>
       <c r="R48">
         <v>0.8518518518518519</v>
       </c>
       <c r="S48">
-        <v>0.1545059593513248</v>
+        <v>0.1539996405275704</v>
       </c>
       <c r="T48">
-        <v>1.681191629913727</v>
+        <v>1.673814027352288</v>
       </c>
       <c r="U48">
-        <v>0.2316309777667576</v>
+        <v>0.2166309777667576</v>
       </c>
       <c r="V48">
-        <v>0.1295634493769033</v>
+        <v>0.1385347043686341</v>
       </c>
       <c r="W48">
-        <v>0.2016200693047517</v>
+        <v>0.1866200693047517</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.5182537975076131</v>
+        <v>0.5541388174745365</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5278,13 +5278,13 @@
         <v>0.47</v>
       </c>
       <c r="B49">
-        <v>0.1780367597075688</v>
+        <v>0.1707133475427414</v>
       </c>
       <c r="C49">
-        <v>142.7532028948219</v>
+        <v>184.7327853367246</v>
       </c>
       <c r="D49">
-        <v>719.2722028948219</v>
+        <v>761.2517853367247</v>
       </c>
       <c r="E49">
         <v>384.0190000000001</v>
@@ -5311,37 +5311,37 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M49">
-        <v>189.1774205306885</v>
+        <v>176.9266355306885</v>
       </c>
       <c r="N49">
-        <v>-93.22150216334158</v>
+        <v>-80.97071716334158</v>
       </c>
       <c r="O49">
-        <v>-23.3053755408354</v>
+        <v>-20.24267929083539</v>
       </c>
       <c r="P49">
-        <v>-69.91612662250618</v>
+        <v>-60.72803787250618</v>
       </c>
       <c r="Q49">
-        <v>-61.07612662250618</v>
+        <v>-51.88803787250617</v>
       </c>
       <c r="R49">
         <v>0.8867924528301887</v>
       </c>
       <c r="S49">
-        <v>0.1565570151881423</v>
+        <v>0.156041143179034</v>
       </c>
       <c r="T49">
-        <v>1.712912226704552</v>
+        <v>1.705395424094784</v>
       </c>
       <c r="U49">
-        <v>0.2316309777667576</v>
+        <v>0.2166309777667576</v>
       </c>
       <c r="V49">
-        <v>0.1268067802412245</v>
+        <v>0.1355871574671738</v>
       </c>
       <c r="W49">
-        <v>0.2022585992720284</v>
+        <v>0.1872585992720284</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.5072271209648981</v>
+        <v>0.5423486298686953</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5360,13 +5360,13 @@
         <v>0.48</v>
       </c>
       <c r="B50">
-        <v>0.1947216554286857</v>
+        <v>0.1724216573204089</v>
       </c>
       <c r="C50">
-        <v>44.7903292967062</v>
+        <v>157.0853948231422</v>
       </c>
       <c r="D50">
-        <v>638.6863292967063</v>
+        <v>750.9813948231423</v>
       </c>
       <c r="E50">
         <v>401.396</v>
@@ -5393,45 +5393,45 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M50">
-        <v>218.2253520313414</v>
+        <v>180.6910320313415</v>
       </c>
       <c r="N50">
-        <v>-122.2694336639945</v>
+        <v>-84.73511366399451</v>
       </c>
       <c r="O50">
-        <v>-30.56735841599862</v>
+        <v>-21.18377841599863</v>
       </c>
       <c r="P50">
-        <v>-91.70207524799586</v>
+        <v>-63.55133524799588</v>
       </c>
       <c r="Q50">
-        <v>-82.86207524799586</v>
+        <v>-54.71133524799588</v>
       </c>
       <c r="R50">
         <v>0.923076923076923</v>
       </c>
       <c r="S50">
-        <v>0.1595073153714708</v>
+        <v>0.1581611651632462</v>
       </c>
       <c r="T50">
-        <v>1.758540083756204</v>
+        <v>1.73819148994276</v>
       </c>
       <c r="U50">
-        <v>0.2616309777667576</v>
+        <v>0.2166309777667576</v>
       </c>
       <c r="V50">
-        <v>0.1099275559348918</v>
+        <v>0.132762425019941</v>
       </c>
       <c r="W50">
-        <v>0.2328705238240019</v>
+        <v>0.1878705238240019</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y50">
-        <v>0.4397102237395671</v>
+        <v>0.5310497000797642</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5442,13 +5442,13 @@
         <v>0.49</v>
       </c>
       <c r="B51">
-        <v>0.1968799652063533</v>
+        <v>0.1741299670980765</v>
       </c>
       <c r="C51">
-        <v>18.28913504963384</v>
+        <v>129.7114401863321</v>
       </c>
       <c r="D51">
-        <v>629.5621350496339</v>
+        <v>740.984440186332</v>
       </c>
       <c r="E51">
         <v>418.773</v>
@@ -5475,45 +5475,45 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M51">
-        <v>222.7717135319944</v>
+        <v>184.4554285319944</v>
       </c>
       <c r="N51">
-        <v>-126.8157951646474</v>
+        <v>-88.49951016464745</v>
       </c>
       <c r="O51">
-        <v>-31.70394879116186</v>
+        <v>-22.12487754116186</v>
       </c>
       <c r="P51">
-        <v>-95.11184637348558</v>
+        <v>-66.37463262348558</v>
       </c>
       <c r="Q51">
-        <v>-86.27184637348557</v>
+        <v>-57.53463262348558</v>
       </c>
       <c r="R51">
         <v>0.9607843137254901</v>
       </c>
       <c r="S51">
-        <v>0.161736870574833</v>
+        <v>0.1603643252644863</v>
       </c>
       <c r="T51">
-        <v>1.793021261869071</v>
+        <v>1.772273676020069</v>
       </c>
       <c r="U51">
-        <v>0.2616309777667576</v>
+        <v>0.2166309777667576</v>
       </c>
       <c r="V51">
-        <v>0.1076841364260164</v>
+        <v>0.1300529877746361</v>
       </c>
       <c r="W51">
-        <v>0.23345747186365</v>
+        <v>0.18845747186365</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y51">
-        <v>0.4307365457040657</v>
+        <v>0.5202119510985446</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5524,13 +5524,13 @@
         <v>0.5</v>
       </c>
       <c r="B52">
-        <v>0.1990382749840209</v>
+        <v>0.1758382768757441</v>
       </c>
       <c r="C52">
-        <v>-7.955036757596304</v>
+        <v>102.6001450642935</v>
       </c>
       <c r="D52">
-        <v>620.6949632424037</v>
+        <v>731.2501450642936</v>
       </c>
       <c r="E52">
         <v>436.15</v>
@@ -5557,45 +5557,45 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M52">
-        <v>227.3180750326473</v>
+        <v>188.2198250326473</v>
       </c>
       <c r="N52">
-        <v>-131.3621566653004</v>
+        <v>-92.26390666530041</v>
       </c>
       <c r="O52">
-        <v>-32.8405391663251</v>
+        <v>-23.0659766663251</v>
       </c>
       <c r="P52">
-        <v>-98.5216174989753</v>
+        <v>-69.19792999897531</v>
       </c>
       <c r="Q52">
-        <v>-89.6816174989753</v>
+        <v>-60.35792999897531</v>
       </c>
       <c r="R52">
         <v>1</v>
       </c>
       <c r="S52">
-        <v>0.1640556079863297</v>
+        <v>0.162655611769776</v>
       </c>
       <c r="T52">
-        <v>1.828881687106452</v>
+        <v>1.807719149540471</v>
       </c>
       <c r="U52">
-        <v>0.2616309777667576</v>
+        <v>0.2166309777667576</v>
       </c>
       <c r="V52">
-        <v>0.1055304536974961</v>
+        <v>0.1274519280191434</v>
       </c>
       <c r="W52">
-        <v>0.2340209419817121</v>
+        <v>0.1890209419817122</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y52">
-        <v>0.4221218147899843</v>
+        <v>0.5098077120765736</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5606,13 +5606,13 @@
         <v>0.51</v>
       </c>
       <c r="B53">
-        <v>0.2011965847616885</v>
+        <v>0.1959497290548579</v>
       </c>
       <c r="C53">
-        <v>-33.95289551179326</v>
+        <v>-12.72243509760915</v>
       </c>
       <c r="D53">
-        <v>612.0741044882068</v>
+        <v>633.3045649023909</v>
       </c>
       <c r="E53">
         <v>453.5270000000001</v>
@@ -5639,37 +5639,37 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M53">
-        <v>231.8644365333003</v>
+        <v>223.0021665333003</v>
       </c>
       <c r="N53">
-        <v>-135.9085181659534</v>
+        <v>-127.0462481659533</v>
       </c>
       <c r="O53">
-        <v>-33.97712954148834</v>
+        <v>-31.76156204148834</v>
       </c>
       <c r="P53">
-        <v>-101.931388624465</v>
+        <v>-95.28468612446501</v>
       </c>
       <c r="Q53">
-        <v>-93.09138862446501</v>
+        <v>-86.44468612446501</v>
       </c>
       <c r="R53">
         <v>1.040816326530612</v>
       </c>
       <c r="S53">
-        <v>0.1664689877411527</v>
+        <v>0.1661692822170086</v>
       </c>
       <c r="T53">
-        <v>1.866205803169849</v>
+        <v>1.862074513878049</v>
       </c>
       <c r="U53">
-        <v>0.2616309777667576</v>
+        <v>0.2516309777667576</v>
       </c>
       <c r="V53">
-        <v>0.1034612291151922</v>
+        <v>0.1075728544020873</v>
       </c>
       <c r="W53">
-        <v>0.2345623152323993</v>
+        <v>0.2245623152323993</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.413844916460769</v>
+        <v>0.4302914176083492</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5688,13 +5688,13 @@
         <v>0.52</v>
       </c>
       <c r="B54">
-        <v>0.2033548945393561</v>
+        <v>0.1980080388325254</v>
       </c>
       <c r="C54">
-        <v>-59.71456377764662</v>
+        <v>-38.663614678258</v>
       </c>
       <c r="D54">
-        <v>603.6894362223534</v>
+        <v>624.7403853217421</v>
       </c>
       <c r="E54">
         <v>470.9040000000001</v>
@@ -5721,37 +5721,37 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M54">
-        <v>236.4107980339532</v>
+        <v>227.3747580339532</v>
       </c>
       <c r="N54">
-        <v>-140.4548796666063</v>
+        <v>-131.4188396666063</v>
       </c>
       <c r="O54">
-        <v>-35.11371991665158</v>
+        <v>-32.85470991665157</v>
       </c>
       <c r="P54">
-        <v>-105.3411597499547</v>
+        <v>-98.56412974995472</v>
       </c>
       <c r="Q54">
-        <v>-96.50115974995472</v>
+        <v>-89.72412974995471</v>
       </c>
       <c r="R54">
         <v>1.083333333333333</v>
       </c>
       <c r="S54">
-        <v>0.1689829249857601</v>
+        <v>0.1686769755965296</v>
       </c>
       <c r="T54">
-        <v>1.905085090735888</v>
+        <v>1.900867732917175</v>
       </c>
       <c r="U54">
-        <v>0.2616309777667576</v>
+        <v>0.2516309777667576</v>
       </c>
       <c r="V54">
-        <v>0.1014715900937463</v>
+        <v>0.1055041456635856</v>
       </c>
       <c r="W54">
-        <v>0.2350828664349831</v>
+        <v>0.2250828664349831</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.4058863603749849</v>
+        <v>0.4220165826543424</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5770,13 +5770,13 @@
         <v>0.53</v>
       </c>
       <c r="B55">
-        <v>0.2055132043170236</v>
+        <v>0.200066348610193</v>
       </c>
       <c r="C55">
-        <v>-85.24961694829778</v>
+        <v>-64.37625790308641</v>
       </c>
       <c r="D55">
-        <v>595.5313830517024</v>
+        <v>616.4047420969137</v>
       </c>
       <c r="E55">
         <v>488.2810000000001</v>
@@ -5803,37 +5803,37 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M55">
-        <v>240.9571595346062</v>
+        <v>231.7473495346062</v>
       </c>
       <c r="N55">
-        <v>-145.0012411672593</v>
+        <v>-135.7914311672592</v>
       </c>
       <c r="O55">
-        <v>-36.25031029181481</v>
+        <v>-33.94785779181481</v>
       </c>
       <c r="P55">
-        <v>-108.7509308754444</v>
+        <v>-101.8435733754444</v>
       </c>
       <c r="Q55">
-        <v>-99.91093087544444</v>
+        <v>-93.00357337544443</v>
       </c>
       <c r="R55">
         <v>1.127659574468085</v>
       </c>
       <c r="S55">
-        <v>0.1716038382833295</v>
+        <v>0.171291379332626</v>
       </c>
       <c r="T55">
-        <v>1.945618816070694</v>
+        <v>1.941311727234562</v>
       </c>
       <c r="U55">
-        <v>0.2616309777667576</v>
+        <v>0.2516309777667576</v>
       </c>
       <c r="V55">
-        <v>0.09955703179009065</v>
+        <v>0.1035135014057821</v>
       </c>
       <c r="W55">
-        <v>0.23558377419596</v>
+        <v>0.22558377419596</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5841,7 +5841,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.3982281271603627</v>
+        <v>0.4140540056231284</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5852,13 +5852,13 @@
         <v>0.54</v>
       </c>
       <c r="B56">
-        <v>0.2076715140946912</v>
+        <v>0.2021246583878606</v>
       </c>
       <c r="C56">
-        <v>-110.567119723829</v>
+        <v>-89.86939211212973</v>
       </c>
       <c r="D56">
-        <v>587.590880276171</v>
+        <v>608.2886078878703</v>
       </c>
       <c r="E56">
         <v>505.6580000000001</v>
@@ -5885,37 +5885,37 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M56">
-        <v>245.5035210352591</v>
+        <v>236.1199410352591</v>
       </c>
       <c r="N56">
-        <v>-149.5476026679122</v>
+        <v>-140.1640226679122</v>
       </c>
       <c r="O56">
-        <v>-37.38690066697805</v>
+        <v>-35.04100566697805</v>
       </c>
       <c r="P56">
-        <v>-112.1607020009342</v>
+        <v>-105.1230170009342</v>
       </c>
       <c r="Q56">
-        <v>-103.3207020009341</v>
+        <v>-96.28301700093415</v>
       </c>
       <c r="R56">
         <v>1.173913043478261</v>
       </c>
       <c r="S56">
-        <v>0.1743387043329671</v>
+        <v>0.1740194527963788</v>
       </c>
       <c r="T56">
-        <v>1.987914877289622</v>
+        <v>1.983514156087488</v>
       </c>
       <c r="U56">
-        <v>0.2616309777667576</v>
+        <v>0.2516309777667576</v>
       </c>
       <c r="V56">
-        <v>0.09771338305323714</v>
+        <v>0.1015965847130824</v>
       </c>
       <c r="W56">
-        <v>0.2360661298176414</v>
+        <v>0.2260661298176414</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.3908535322129485</v>
+        <v>0.4063863388523297</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5934,13 +5934,13 @@
         <v>0.55</v>
       </c>
       <c r="B57">
-        <v>0.2098298238723588</v>
+        <v>0.2041829681655282</v>
       </c>
       <c r="C57">
-        <v>-135.6756597098458</v>
+        <v>-115.1515753762221</v>
       </c>
       <c r="D57">
-        <v>579.8593402901544</v>
+        <v>600.3834246237781</v>
       </c>
       <c r="E57">
         <v>523.0350000000001</v>
@@ -5967,37 +5967,37 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M57">
-        <v>250.0498825359121</v>
+        <v>240.4925325359121</v>
       </c>
       <c r="N57">
-        <v>-154.0939641685652</v>
+        <v>-144.5366141685652</v>
       </c>
       <c r="O57">
-        <v>-38.52349104214129</v>
+        <v>-36.13415354214129</v>
       </c>
       <c r="P57">
-        <v>-115.5704731264239</v>
+        <v>-108.4024606264239</v>
       </c>
       <c r="Q57">
-        <v>-106.7304731264239</v>
+        <v>-99.56246062642387</v>
       </c>
       <c r="R57">
         <v>1.222222222222223</v>
       </c>
       <c r="S57">
-        <v>0.1771951199848108</v>
+        <v>0.1768687739696316</v>
       </c>
       <c r="T57">
-        <v>2.032090763451614</v>
+        <v>2.027592248444987</v>
       </c>
       <c r="U57">
-        <v>0.2616309777667576</v>
+        <v>0.2516309777667576</v>
       </c>
       <c r="V57">
-        <v>0.09593677608863281</v>
+        <v>0.09974937408193547</v>
       </c>
       <c r="W57">
-        <v>0.2365309452348981</v>
+        <v>0.2265309452348981</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.3837471043545313</v>
+        <v>0.3989974963277418</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6016,13 +6016,13 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="B58">
-        <v>0.2119881336500264</v>
+        <v>0.2062412779431957</v>
       </c>
       <c r="C58">
-        <v>-160.583378397954</v>
+        <v>-140.2309265983943</v>
       </c>
       <c r="D58">
-        <v>572.328621602046</v>
+        <v>592.6810734016058</v>
       </c>
       <c r="E58">
         <v>540.412</v>
@@ -6049,37 +6049,37 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M58">
-        <v>254.596244036565</v>
+        <v>244.865124036565</v>
       </c>
       <c r="N58">
-        <v>-158.6403256692181</v>
+        <v>-148.9092056692181</v>
       </c>
       <c r="O58">
-        <v>-39.66008141730453</v>
+        <v>-37.22730141730452</v>
       </c>
       <c r="P58">
-        <v>-118.9802442519136</v>
+        <v>-111.6819042519136</v>
       </c>
       <c r="Q58">
-        <v>-110.1402442519136</v>
+        <v>-102.8419042519135</v>
       </c>
       <c r="R58">
         <v>1.272727272727273</v>
       </c>
       <c r="S58">
-        <v>0.1801813727117383</v>
+        <v>0.1798476097416687</v>
       </c>
       <c r="T58">
-        <v>2.078274644439151</v>
+        <v>2.073673890455101</v>
       </c>
       <c r="U58">
-        <v>0.2616309777667576</v>
+        <v>0.2516309777667576</v>
       </c>
       <c r="V58">
-        <v>0.09422361937276437</v>
+        <v>0.09796813525904378</v>
       </c>
       <c r="W58">
-        <v>0.2369791601015384</v>
+        <v>0.2269791601015384</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.3768944774910574</v>
+        <v>0.3918725410361752</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6098,13 +6098,13 @@
         <v>0.5700000000000001</v>
       </c>
       <c r="B59">
-        <v>0.214146443427694</v>
+        <v>0.2082995877208633</v>
       </c>
       <c r="C59">
-        <v>-185.2979997631079</v>
+        <v>-165.1151533275882</v>
       </c>
       <c r="D59">
-        <v>564.9910002368922</v>
+        <v>585.1738466724119</v>
       </c>
       <c r="E59">
         <v>557.7890000000002</v>
@@ -6131,37 +6131,37 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M59">
-        <v>259.142605537218</v>
+        <v>249.237715537218</v>
       </c>
       <c r="N59">
-        <v>-163.186687169871</v>
+        <v>-153.281797169871</v>
       </c>
       <c r="O59">
-        <v>-40.79667179246776</v>
+        <v>-38.32044929246776</v>
       </c>
       <c r="P59">
-        <v>-122.3900153774033</v>
+        <v>-114.9613478774033</v>
       </c>
       <c r="Q59">
-        <v>-113.5500153774033</v>
+        <v>-106.1213478774033</v>
       </c>
       <c r="R59">
         <v>1.325581395348838</v>
       </c>
       <c r="S59">
-        <v>0.1833065209143369</v>
+        <v>0.1829649960147308</v>
       </c>
       <c r="T59">
-        <v>2.12660661291448</v>
+        <v>2.121898864651731</v>
       </c>
       <c r="U59">
-        <v>0.2616309777667576</v>
+        <v>0.2516309777667576</v>
       </c>
       <c r="V59">
-        <v>0.09257057341885622</v>
+        <v>0.09624939604397284</v>
       </c>
       <c r="W59">
-        <v>0.2374116481307528</v>
+        <v>0.2274116481307528</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.3702822936754249</v>
+        <v>0.3849975841758914</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6180,13 +6180,13 @@
         <v>0.58</v>
       </c>
       <c r="B60">
-        <v>0.2163047532053615</v>
+        <v>0.2103578974985309</v>
       </c>
       <c r="C60">
-        <v>-209.8268566889774</v>
+        <v>-189.8115774849848</v>
       </c>
       <c r="D60">
-        <v>557.8391433110227</v>
+        <v>577.8544225150151</v>
       </c>
       <c r="E60">
         <v>575.1659999999999</v>
@@ -6213,37 +6213,37 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M60">
-        <v>263.6889670378709</v>
+        <v>253.6103070378709</v>
       </c>
       <c r="N60">
-        <v>-167.7330486705239</v>
+        <v>-157.6543886705239</v>
       </c>
       <c r="O60">
-        <v>-41.93326216763099</v>
+        <v>-39.41359716763098</v>
       </c>
       <c r="P60">
-        <v>-125.799786502893</v>
+        <v>-118.2407915028929</v>
       </c>
       <c r="Q60">
-        <v>-116.959786502893</v>
+        <v>-109.4007915028929</v>
       </c>
       <c r="R60">
         <v>1.380952380952381</v>
       </c>
       <c r="S60">
-        <v>0.1865804856980115</v>
+        <v>0.1862308292531767</v>
       </c>
       <c r="T60">
-        <v>2.177240103698157</v>
+        <v>2.172420266191057</v>
       </c>
       <c r="U60">
-        <v>0.2616309777667576</v>
+        <v>0.2516309777667576</v>
       </c>
       <c r="V60">
-        <v>0.09097452904956561</v>
+        <v>0.09458992369838712</v>
       </c>
       <c r="W60">
-        <v>0.2378292227796494</v>
+        <v>0.2278292227796494</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.3638981161982625</v>
+        <v>0.3783596947935485</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6262,13 +6262,13 @@
         <v>0.59</v>
       </c>
       <c r="B61">
-        <v>0.2184630629830291</v>
+        <v>0.2124162072761985</v>
       </c>
       <c r="C61">
-        <v>-234.1769154113992</v>
+        <v>-214.3271591834593</v>
       </c>
       <c r="D61">
-        <v>550.8660845886008</v>
+        <v>570.7158408165407</v>
       </c>
       <c r="E61">
         <v>592.5429999999999</v>
@@ -6295,37 +6295,37 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M61">
-        <v>268.2353285385238</v>
+        <v>257.9828985385238</v>
       </c>
       <c r="N61">
-        <v>-172.2794101711769</v>
+        <v>-162.0269801711769</v>
       </c>
       <c r="O61">
-        <v>-43.06985254279422</v>
+        <v>-40.50674504279422</v>
       </c>
       <c r="P61">
-        <v>-129.2095576283827</v>
+        <v>-121.5202351283827</v>
       </c>
       <c r="Q61">
-        <v>-120.3695576283827</v>
+        <v>-112.6802351283827</v>
       </c>
       <c r="R61">
         <v>1.439024390243902</v>
       </c>
       <c r="S61">
-        <v>0.1900141560808899</v>
+        <v>0.1896559714300835</v>
       </c>
       <c r="T61">
-        <v>2.230343520861527</v>
+        <v>2.225406126342059</v>
       </c>
       <c r="U61">
-        <v>0.2616309777667576</v>
+        <v>0.2516309777667576</v>
       </c>
       <c r="V61">
-        <v>0.08943258787923399</v>
+        <v>0.09298670465265173</v>
       </c>
       <c r="W61">
-        <v>0.2382326423557021</v>
+        <v>0.2282326423557021</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.357730351516936</v>
+        <v>0.371946818610607</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6344,13 +6344,13 @@
         <v>0.6</v>
       </c>
       <c r="B62">
-        <v>0.2206213727606967</v>
+        <v>0.2144745170538661</v>
       </c>
       <c r="C62">
-        <v>-258.3547981511799</v>
+        <v>-238.6685188030413</v>
       </c>
       <c r="D62">
-        <v>544.0652018488199</v>
+        <v>563.7514811969586</v>
       </c>
       <c r="E62">
         <v>609.9199999999998</v>
@@ -6377,37 +6377,37 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M62">
-        <v>272.7816900391768</v>
+        <v>262.3554900391767</v>
       </c>
       <c r="N62">
-        <v>-176.8257716718298</v>
+        <v>-166.3995716718298</v>
       </c>
       <c r="O62">
-        <v>-44.20644291795746</v>
+        <v>-41.59989291795745</v>
       </c>
       <c r="P62">
-        <v>-132.6193287538724</v>
+        <v>-124.7996787538723</v>
       </c>
       <c r="Q62">
-        <v>-123.7793287538724</v>
+        <v>-115.9596787538723</v>
       </c>
       <c r="R62">
         <v>1.5</v>
       </c>
       <c r="S62">
-        <v>0.1936195099829121</v>
+        <v>0.1932523707158356</v>
       </c>
       <c r="T62">
-        <v>2.286102108883065</v>
+        <v>2.28104127950061</v>
       </c>
       <c r="U62">
-        <v>0.2616309777667576</v>
+        <v>0.2516309777667576</v>
       </c>
       <c r="V62">
-        <v>0.08794204474791342</v>
+        <v>0.09143692624177421</v>
       </c>
       <c r="W62">
-        <v>0.238622614612553</v>
+        <v>0.228622614612553</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.3517681789916537</v>
+        <v>0.365747704967097</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6426,13 +6426,13 @@
         <v>0.61</v>
       </c>
       <c r="B63">
-        <v>0.2227796825383643</v>
+        <v>0.2165328268315336</v>
       </c>
       <c r="C63">
-        <v>-282.3668040908281</v>
+        <v>-262.8419574695624</v>
       </c>
       <c r="D63">
-        <v>537.4301959091721</v>
+        <v>556.9550425304376</v>
       </c>
       <c r="E63">
         <v>627.297</v>
@@ -6459,37 +6459,37 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M63">
-        <v>277.3280515398297</v>
+        <v>266.7280815398298</v>
       </c>
       <c r="N63">
-        <v>-181.3721331724828</v>
+        <v>-170.7721631724828</v>
       </c>
       <c r="O63">
-        <v>-45.3430332931207</v>
+        <v>-42.6930407931207</v>
       </c>
       <c r="P63">
-        <v>-136.0290998793621</v>
+        <v>-128.0791223793621</v>
       </c>
       <c r="Q63">
-        <v>-127.1890998793621</v>
+        <v>-119.2391223793621</v>
       </c>
       <c r="R63">
         <v>1.564102564102564</v>
       </c>
       <c r="S63">
-        <v>0.1974097538286278</v>
+        <v>0.1970332007341903</v>
       </c>
       <c r="T63">
-        <v>2.344720111674939</v>
+        <v>2.339529517436524</v>
       </c>
       <c r="U63">
-        <v>0.2616309777667576</v>
+        <v>0.2516309777667576</v>
       </c>
       <c r="V63">
-        <v>0.08650037188319352</v>
+        <v>0.08993796023781069</v>
       </c>
       <c r="W63">
-        <v>0.2389998008937695</v>
+        <v>0.2289998008937695</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.3460014875327742</v>
+        <v>0.3597518409512428</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6508,13 +6508,13 @@
         <v>0.62</v>
       </c>
       <c r="B64">
-        <v>0.2249379923160318</v>
+        <v>0.2185911366092012</v>
       </c>
       <c r="C64">
-        <v>-306.2189288348754</v>
+        <v>-286.8534760696366</v>
       </c>
       <c r="D64">
-        <v>530.9550711651247</v>
+        <v>550.3205239303635</v>
       </c>
       <c r="E64">
         <v>644.674</v>
@@ -6541,37 +6541,37 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M64">
-        <v>281.8744130404827</v>
+        <v>271.1006730404827</v>
       </c>
       <c r="N64">
-        <v>-185.9184946731357</v>
+        <v>-175.1447546731357</v>
       </c>
       <c r="O64">
-        <v>-46.47962366828393</v>
+        <v>-43.78618866828393</v>
       </c>
       <c r="P64">
-        <v>-139.4388710048518</v>
+        <v>-131.3585660048518</v>
       </c>
       <c r="Q64">
-        <v>-130.5988710048518</v>
+        <v>-122.5185660048518</v>
       </c>
       <c r="R64">
         <v>1.631578947368421</v>
       </c>
       <c r="S64">
-        <v>0.2013994841925391</v>
+        <v>0.2010130218061427</v>
       </c>
       <c r="T64">
-        <v>2.40642327250849</v>
+        <v>2.401096083684853</v>
       </c>
       <c r="U64">
-        <v>0.2616309777667576</v>
+        <v>0.2516309777667576</v>
       </c>
       <c r="V64">
-        <v>0.08510520459475493</v>
+        <v>0.08848734797591053</v>
       </c>
       <c r="W64">
-        <v>0.2393648198755919</v>
+        <v>0.2293648198755919</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.3404208183790197</v>
+        <v>0.3539493919036422</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6590,13 +6590,13 @@
         <v>0.63</v>
       </c>
       <c r="B65">
-        <v>0.2270963020936994</v>
+        <v>0.2206494463868688</v>
       </c>
       <c r="C65">
-        <v>-329.9168824801716</v>
+        <v>-310.7087929225863</v>
       </c>
       <c r="D65">
-        <v>524.6341175198285</v>
+        <v>543.8422070774136</v>
       </c>
       <c r="E65">
         <v>662.0509999999999</v>
@@ -6623,37 +6623,37 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M65">
-        <v>286.4207745411356</v>
+        <v>275.4732645411356</v>
       </c>
       <c r="N65">
-        <v>-190.4648561737887</v>
+        <v>-179.5173461737887</v>
       </c>
       <c r="O65">
-        <v>-47.61621404344717</v>
+        <v>-44.87933654344717</v>
       </c>
       <c r="P65">
-        <v>-142.8486421303415</v>
+        <v>-134.6380096303415</v>
       </c>
       <c r="Q65">
-        <v>-134.0086421303415</v>
+        <v>-125.7980096303415</v>
       </c>
       <c r="R65">
         <v>1.702702702702703</v>
       </c>
       <c r="S65">
-        <v>0.2056048756572023</v>
+        <v>0.2052079683414439</v>
       </c>
       <c r="T65">
-        <v>2.471461739333044</v>
+        <v>2.465990572433093</v>
       </c>
       <c r="U65">
-        <v>0.2616309777667576</v>
+        <v>0.2516309777667576</v>
       </c>
       <c r="V65">
-        <v>0.08375432833134612</v>
+        <v>0.08708278689692782</v>
       </c>
       <c r="W65">
-        <v>0.2397182509532295</v>
+        <v>0.2297182509532295</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.3350173133253845</v>
+        <v>0.3483311475877113</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6672,13 +6672,13 @@
         <v>0.64</v>
       </c>
       <c r="B66">
-        <v>0.229254611871367</v>
+        <v>0.2227077561645364</v>
       </c>
       <c r="C66">
-        <v>-353.4661064106062</v>
+        <v>-334.4133602187012</v>
       </c>
       <c r="D66">
-        <v>518.4618935893939</v>
+        <v>537.514639781299</v>
       </c>
       <c r="E66">
         <v>679.4280000000001</v>
@@ -6705,37 +6705,37 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M66">
-        <v>290.9671360417886</v>
+        <v>279.8458560417886</v>
       </c>
       <c r="N66">
-        <v>-195.0112176744417</v>
+        <v>-183.8899376744417</v>
       </c>
       <c r="O66">
-        <v>-48.75280441861042</v>
+        <v>-45.97248441861042</v>
       </c>
       <c r="P66">
-        <v>-146.2584132558313</v>
+        <v>-137.9174532558313</v>
       </c>
       <c r="Q66">
-        <v>-137.4184132558313</v>
+        <v>-129.0774532558313</v>
       </c>
       <c r="R66">
         <v>1.777777777777778</v>
       </c>
       <c r="S66">
-        <v>0.2100438999810134</v>
+        <v>0.2096359674620395</v>
       </c>
       <c r="T66">
-        <v>2.540113454314517</v>
+        <v>2.534490310556234</v>
       </c>
       <c r="U66">
-        <v>0.2616309777667576</v>
+        <v>0.2516309777667576</v>
       </c>
       <c r="V66">
-        <v>0.08244566695116881</v>
+        <v>0.0857221183516633</v>
       </c>
       <c r="W66">
-        <v>0.2400606373096908</v>
+        <v>0.2300606373096908</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.3297826678046754</v>
+        <v>0.3428884734066533</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6754,13 +6754,13 @@
         <v>0.65</v>
       </c>
       <c r="B67">
-        <v>0.2314129216490345</v>
+        <v>0.2247660659422039</v>
       </c>
       <c r="C67">
-        <v>-376.8717889201025</v>
+        <v>-357.9723793231419</v>
       </c>
       <c r="D67">
-        <v>512.4332110798977</v>
+        <v>531.3326206768583</v>
       </c>
       <c r="E67">
         <v>696.8050000000001</v>
@@ -6787,37 +6787,37 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M67">
-        <v>295.5134975424415</v>
+        <v>284.2184475424415</v>
       </c>
       <c r="N67">
-        <v>-199.5575791750946</v>
+        <v>-188.2625291750946</v>
       </c>
       <c r="O67">
-        <v>-49.88939479377365</v>
+        <v>-47.06563229377365</v>
       </c>
       <c r="P67">
-        <v>-149.6681843813209</v>
+        <v>-141.1968968813209</v>
       </c>
       <c r="Q67">
-        <v>-140.8281843813209</v>
+        <v>-132.3568968813209</v>
       </c>
       <c r="R67">
         <v>1.857142857142857</v>
       </c>
       <c r="S67">
-        <v>0.2147365828376138</v>
+        <v>0.2143169951038121</v>
       </c>
       <c r="T67">
-        <v>2.612688124437789</v>
+        <v>2.606904319429269</v>
       </c>
       <c r="U67">
-        <v>0.2616309777667576</v>
+        <v>0.2516309777667576</v>
       </c>
       <c r="V67">
-        <v>0.081177272074997</v>
+        <v>0.08440331653086849</v>
       </c>
       <c r="W67">
-        <v>0.240392488701338</v>
+        <v>0.230392488701338</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.324709088299988</v>
+        <v>0.337613266123474</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6836,13 +6836,13 @@
         <v>0.66</v>
       </c>
       <c r="B68">
-        <v>0.2335712314267022</v>
+        <v>0.2268243757198715</v>
       </c>
       <c r="C68">
-        <v>-400.1388797581502</v>
+        <v>-381.390815035785</v>
       </c>
       <c r="D68">
-        <v>506.5431202418499</v>
+        <v>525.2911849642152</v>
       </c>
       <c r="E68">
         <v>714.182</v>
@@ -6869,37 +6869,37 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M68">
-        <v>300.0598590430945</v>
+        <v>288.5910390430945</v>
       </c>
       <c r="N68">
-        <v>-204.1039406757475</v>
+        <v>-192.6351206757475</v>
       </c>
       <c r="O68">
-        <v>-51.02598516893688</v>
+        <v>-48.15878016893689</v>
       </c>
       <c r="P68">
-        <v>-153.0779555068107</v>
+        <v>-144.4763405068107</v>
       </c>
       <c r="Q68">
-        <v>-144.2379555068107</v>
+        <v>-135.6363405068107</v>
       </c>
       <c r="R68">
         <v>1.941176470588236</v>
       </c>
       <c r="S68">
-        <v>0.2197053058622496</v>
+        <v>0.2192733773127477</v>
       </c>
       <c r="T68">
-        <v>2.689531892803607</v>
+        <v>2.683577975883071</v>
       </c>
       <c r="U68">
-        <v>0.2616309777667576</v>
+        <v>0.2516309777667576</v>
       </c>
       <c r="V68">
-        <v>0.07994731340719402</v>
+        <v>0.0831244784016129</v>
       </c>
       <c r="W68">
-        <v>0.240714283990208</v>
+        <v>0.230714283990208</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.3197892536287761</v>
+        <v>0.3324979136064516</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6918,13 +6918,13 @@
         <v>0.67</v>
       </c>
       <c r="B69">
-        <v>0.2357295412043697</v>
+        <v>0.2288826854975391</v>
       </c>
       <c r="C69">
-        <v>-423.2721036835891</v>
+        <v>-404.673408889164</v>
       </c>
       <c r="D69">
-        <v>500.7868963164109</v>
+        <v>519.3855911108361</v>
       </c>
       <c r="E69">
         <v>731.559</v>
@@ -6951,37 +6951,37 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M69">
-        <v>304.6062205437474</v>
+        <v>292.9636305437474</v>
       </c>
       <c r="N69">
-        <v>-208.6503021764005</v>
+        <v>-197.0077121764004</v>
       </c>
       <c r="O69">
-        <v>-52.16257554410012</v>
+        <v>-49.25192804410011</v>
       </c>
       <c r="P69">
-        <v>-156.4877266323004</v>
+        <v>-147.7557841323003</v>
       </c>
       <c r="Q69">
-        <v>-147.6477266323004</v>
+        <v>-138.9157841323003</v>
       </c>
       <c r="R69">
         <v>2.030303030303031</v>
       </c>
       <c r="S69">
-        <v>0.2249751636156511</v>
+        <v>0.224530146322225</v>
       </c>
       <c r="T69">
-        <v>2.771032859252201</v>
+        <v>2.764898520606801</v>
       </c>
       <c r="U69">
-        <v>0.2616309777667576</v>
+        <v>0.2516309777667576</v>
       </c>
       <c r="V69">
-        <v>0.07875406992350455</v>
+        <v>0.08188381454487242</v>
       </c>
       <c r="W69">
-        <v>0.2410264734495595</v>
+        <v>0.2310264734495595</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.3150162796940182</v>
+        <v>0.3275352581794897</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7000,13 +7000,13 @@
         <v>0.68</v>
       </c>
       <c r="B70">
-        <v>0.2378878509820373</v>
+        <v>0.2309409952752067</v>
       </c>
       <c r="C70">
-        <v>-446.2759731046468</v>
+        <v>-427.8246915593743</v>
       </c>
       <c r="D70">
-        <v>495.1600268953534</v>
+        <v>513.611308440626</v>
       </c>
       <c r="E70">
         <v>748.9360000000001</v>
@@ -7033,37 +7033,37 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M70">
-        <v>309.1525820444004</v>
+        <v>297.3362220444004</v>
       </c>
       <c r="N70">
-        <v>-213.1966636770535</v>
+        <v>-201.3803036770535</v>
       </c>
       <c r="O70">
-        <v>-53.29916591926337</v>
+        <v>-50.34507591926337</v>
       </c>
       <c r="P70">
-        <v>-159.8974977577901</v>
+        <v>-151.0352277577901</v>
       </c>
       <c r="Q70">
-        <v>-151.0574977577901</v>
+        <v>-142.1952277577901</v>
       </c>
       <c r="R70">
         <v>2.125</v>
       </c>
       <c r="S70">
-        <v>0.2305743874786402</v>
+        <v>0.2301154633947945</v>
       </c>
       <c r="T70">
-        <v>2.857627636103832</v>
+        <v>2.851301599375764</v>
       </c>
       <c r="U70">
-        <v>0.2616309777667576</v>
+        <v>0.2516309777667576</v>
       </c>
       <c r="V70">
-        <v>0.07759592183639417</v>
+        <v>0.08067964080156546</v>
       </c>
       <c r="W70">
-        <v>0.2413294808659889</v>
+        <v>0.2313294808659889</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.3103836873455768</v>
+        <v>0.3227185632062619</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7082,13 +7082,13 @@
         <v>0.6900000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2400461607597049</v>
+        <v>0.2329993050528743</v>
       </c>
       <c r="C71">
-        <v>-469.154799876299</v>
+        <v>-450.8489944582038</v>
       </c>
       <c r="D71">
-        <v>489.6582001237012</v>
+        <v>507.9640055417963</v>
       </c>
       <c r="E71">
         <v>766.3130000000001</v>
@@ -7115,37 +7115,37 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M71">
-        <v>313.6989435450533</v>
+        <v>301.7088135450533</v>
       </c>
       <c r="N71">
-        <v>-217.7430251777064</v>
+        <v>-205.7528951777064</v>
       </c>
       <c r="O71">
-        <v>-54.4357562944266</v>
+        <v>-51.43822379442659</v>
       </c>
       <c r="P71">
-        <v>-163.3072688832798</v>
+        <v>-154.3146713832798</v>
       </c>
       <c r="Q71">
-        <v>-154.4672688832798</v>
+        <v>-145.4746713832798</v>
       </c>
       <c r="R71">
         <v>2.225806451612904</v>
       </c>
       <c r="S71">
-        <v>0.2365348515908544</v>
+        <v>0.236061123504304</v>
       </c>
       <c r="T71">
-        <v>2.949809172752343</v>
+        <v>2.943279070323369</v>
       </c>
       <c r="U71">
-        <v>0.2616309777667576</v>
+        <v>0.2516309777667576</v>
       </c>
       <c r="V71">
-        <v>0.07647134325905515</v>
+        <v>0.07951037064502105</v>
       </c>
       <c r="W71">
-        <v>0.2416237054587536</v>
+        <v>0.2316237054587536</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.3058853730362207</v>
+        <v>0.3180414825800842</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7164,13 +7164,13 @@
         <v>0.7000000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2422044705373724</v>
+        <v>0.2350576148305418</v>
       </c>
       <c r="C72">
-        <v>-491.912706319775</v>
+        <v>-473.7504605688332</v>
       </c>
       <c r="D72">
-        <v>484.2772936802251</v>
+        <v>502.439539431167</v>
       </c>
       <c r="E72">
         <v>783.6900000000001</v>
@@ -7197,37 +7197,37 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M72">
-        <v>318.2453050457063</v>
+        <v>306.0814050457063</v>
       </c>
       <c r="N72">
-        <v>-222.2893866783593</v>
+        <v>-210.1254866783593</v>
       </c>
       <c r="O72">
-        <v>-55.57234666958983</v>
+        <v>-52.53137166958983</v>
       </c>
       <c r="P72">
-        <v>-166.7170400087695</v>
+        <v>-157.5941150087695</v>
       </c>
       <c r="Q72">
-        <v>-157.8770400087695</v>
+        <v>-148.7541150087695</v>
       </c>
       <c r="R72">
         <v>2.333333333333334</v>
       </c>
       <c r="S72">
-        <v>0.2428926799772162</v>
+        <v>0.2424031609544475</v>
       </c>
       <c r="T72">
-        <v>3.048136145177421</v>
+        <v>3.041388372667481</v>
       </c>
       <c r="U72">
-        <v>0.2616309777667576</v>
+        <v>0.2516309777667576</v>
       </c>
       <c r="V72">
-        <v>0.0753788954982115</v>
+        <v>0.07837450820723503</v>
       </c>
       <c r="W72">
-        <v>0.2419095236345823</v>
+        <v>0.2319095236345823</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.301515581992846</v>
+        <v>0.3134980328289402</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7246,13 +7246,13 @@
         <v>0.71</v>
       </c>
       <c r="B73">
-        <v>0.24436278031504</v>
+        <v>0.2371159246082094</v>
       </c>
       <c r="C73">
-        <v>-514.5536355233955</v>
+        <v>-496.5330545820644</v>
       </c>
       <c r="D73">
-        <v>479.0133644766045</v>
+        <v>497.0339454179356</v>
       </c>
       <c r="E73">
         <v>801.067</v>
@@ -7279,37 +7279,37 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M73">
-        <v>322.7916665463592</v>
+        <v>310.4539965463592</v>
       </c>
       <c r="N73">
-        <v>-226.8357481790123</v>
+        <v>-214.4980781790123</v>
       </c>
       <c r="O73">
-        <v>-56.70893704475307</v>
+        <v>-53.62451954475307</v>
       </c>
       <c r="P73">
-        <v>-170.1268111342592</v>
+        <v>-160.8735586342592</v>
       </c>
       <c r="Q73">
-        <v>-161.2868111342592</v>
+        <v>-152.0335586342592</v>
       </c>
       <c r="R73">
         <v>2.448275862068965</v>
       </c>
       <c r="S73">
-        <v>0.2496889792867753</v>
+        <v>0.2491825802977042</v>
       </c>
       <c r="T73">
-        <v>3.153244288114573</v>
+        <v>3.146263833793945</v>
       </c>
       <c r="U73">
-        <v>0.2616309777667576</v>
+        <v>0.2516309777667576</v>
       </c>
       <c r="V73">
-        <v>0.07431722091372965</v>
+        <v>0.07727064189445706</v>
       </c>
       <c r="W73">
-        <v>0.2421872905941904</v>
+        <v>0.2321872905941904</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.2972688836549187</v>
+        <v>0.3090825675778283</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7328,13 +7328,13 @@
         <v>0.72</v>
       </c>
       <c r="B74">
-        <v>0.2465210900927076</v>
+        <v>0.2391742343858769</v>
       </c>
       <c r="C74">
-        <v>-537.0813609788313</v>
+        <v>-519.200572385201</v>
       </c>
       <c r="D74">
-        <v>473.8626390211688</v>
+        <v>491.743427614799</v>
       </c>
       <c r="E74">
         <v>818.444</v>
@@ -7361,37 +7361,37 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M74">
-        <v>327.3380280470121</v>
+        <v>314.8265880470121</v>
       </c>
       <c r="N74">
-        <v>-231.3821096796652</v>
+        <v>-218.8706696796652</v>
       </c>
       <c r="O74">
-        <v>-57.84552741991629</v>
+        <v>-54.7176674199163</v>
       </c>
       <c r="P74">
-        <v>-173.5365822597489</v>
+        <v>-164.1530022597489</v>
       </c>
       <c r="Q74">
-        <v>-164.6965822597489</v>
+        <v>-155.3130022597489</v>
       </c>
       <c r="R74">
         <v>2.571428571428571</v>
       </c>
       <c r="S74">
-        <v>0.2569707285470173</v>
+        <v>0.2564462438797651</v>
       </c>
       <c r="T74">
-        <v>3.265860155547236</v>
+        <v>3.258630399286586</v>
       </c>
       <c r="U74">
-        <v>0.2616309777667576</v>
+        <v>0.2516309777667576</v>
       </c>
       <c r="V74">
-        <v>0.07328503728992786</v>
+        <v>0.07619743853481184</v>
       </c>
       <c r="W74">
-        <v>0.2424573418049205</v>
+        <v>0.2324573418049204</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.2931401491597114</v>
+        <v>0.3047897541392474</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7410,13 +7410,13 @@
         <v>0.73</v>
       </c>
       <c r="B75">
-        <v>0.2486793998703751</v>
+        <v>0.2412325441635445</v>
       </c>
       <c r="C75">
-        <v>-559.4994956022783</v>
+        <v>-541.7566499513014</v>
       </c>
       <c r="D75">
-        <v>468.8215043977217</v>
+        <v>486.5643500486987</v>
       </c>
       <c r="E75">
         <v>835.8209999999999</v>
@@ -7443,37 +7443,37 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M75">
-        <v>331.8843895476651</v>
+        <v>319.1991795476651</v>
       </c>
       <c r="N75">
-        <v>-235.9284711803181</v>
+        <v>-223.2432611803181</v>
       </c>
       <c r="O75">
-        <v>-58.98211779507953</v>
+        <v>-55.81081529507954</v>
       </c>
       <c r="P75">
-        <v>-176.9463533852386</v>
+        <v>-167.4324458852386</v>
       </c>
       <c r="Q75">
-        <v>-168.1063533852386</v>
+        <v>-158.5924458852386</v>
       </c>
       <c r="R75">
         <v>2.703703703703703</v>
       </c>
       <c r="S75">
-        <v>0.2647918666413512</v>
+        <v>0.2642479566160527</v>
       </c>
       <c r="T75">
-        <v>3.386817939086022</v>
+        <v>3.379320414074978</v>
       </c>
       <c r="U75">
-        <v>0.2616309777667576</v>
+        <v>0.2516309777667576</v>
       </c>
       <c r="V75">
-        <v>0.07228113266951788</v>
+        <v>0.0751536380069377</v>
       </c>
       <c r="W75">
-        <v>0.2427199943523429</v>
+        <v>0.2327199943523429</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.2891245306780715</v>
+        <v>0.3006145520277509</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7492,13 +7492,13 @@
         <v>0.74</v>
       </c>
       <c r="B76">
-        <v>0.2508377096480428</v>
+        <v>0.2432908539412121</v>
       </c>
       <c r="C76">
-        <v>-581.811500185871</v>
+        <v>-564.2047716725524</v>
       </c>
       <c r="D76">
-        <v>463.886499814129</v>
+        <v>481.4932283274475</v>
       </c>
       <c r="E76">
         <v>853.1979999999999</v>
@@ -7525,37 +7525,37 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M76">
-        <v>336.430751048318</v>
+        <v>323.571771048318</v>
       </c>
       <c r="N76">
-        <v>-240.4748326809711</v>
+        <v>-227.615852680971</v>
       </c>
       <c r="O76">
-        <v>-60.11870817024277</v>
+        <v>-56.90396317024276</v>
       </c>
       <c r="P76">
-        <v>-180.3561245107283</v>
+        <v>-170.7118895107283</v>
       </c>
       <c r="Q76">
-        <v>-171.5161245107283</v>
+        <v>-161.8718895107283</v>
       </c>
       <c r="R76">
         <v>2.846153846153846</v>
       </c>
       <c r="S76">
-        <v>0.2732146307429417</v>
+        <v>0.2726498011012854</v>
       </c>
       <c r="T76">
-        <v>3.517080167512408</v>
+        <v>3.509294276154785</v>
       </c>
       <c r="U76">
-        <v>0.2616309777667576</v>
+        <v>0.2516309777667576</v>
       </c>
       <c r="V76">
-        <v>0.07130436060641629</v>
+        <v>0.07413804830414125</v>
       </c>
       <c r="W76">
-        <v>0.2429755481822674</v>
+        <v>0.2329755481822674</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.2852174424256652</v>
+        <v>0.2965521932165651</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7574,13 +7574,13 @@
         <v>0.75</v>
       </c>
       <c r="B77">
-        <v>0.2529960194257103</v>
+        <v>0.2453491637188797</v>
       </c>
       <c r="C77">
-        <v>-604.0206913208742</v>
+        <v>-586.5482781779034</v>
       </c>
       <c r="D77">
-        <v>459.0543086791259</v>
+        <v>476.5267218220967</v>
       </c>
       <c r="E77">
         <v>870.575</v>
@@ -7607,37 +7607,37 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M77">
-        <v>340.977112548971</v>
+        <v>327.944362548971</v>
       </c>
       <c r="N77">
-        <v>-245.0211941816241</v>
+        <v>-231.9884441816241</v>
       </c>
       <c r="O77">
-        <v>-61.25529854540602</v>
+        <v>-57.99711104540602</v>
       </c>
       <c r="P77">
-        <v>-183.7658956362181</v>
+        <v>-173.991333136218</v>
       </c>
       <c r="Q77">
-        <v>-174.9258956362181</v>
+        <v>-165.151333136218</v>
       </c>
       <c r="R77">
         <v>3</v>
       </c>
       <c r="S77">
-        <v>0.2823112159726593</v>
+        <v>0.2817237931453369</v>
       </c>
       <c r="T77">
-        <v>3.657763374212905</v>
+        <v>3.649666047200977</v>
       </c>
       <c r="U77">
-        <v>0.2616309777667576</v>
+        <v>0.2516309777667576</v>
       </c>
       <c r="V77">
-        <v>0.07035363579833073</v>
+        <v>0.07314954099341936</v>
       </c>
       <c r="W77">
-        <v>0.243224287243394</v>
+        <v>0.233224287243394</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.2814145431933229</v>
+        <v>0.2925981639736774</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7656,13 +7656,13 @@
         <v>0.76</v>
       </c>
       <c r="B78">
-        <v>0.2551543292033779</v>
+        <v>0.2474074734965473</v>
       </c>
       <c r="C78">
-        <v>-626.1302488307792</v>
+        <v>-608.7903736718117</v>
       </c>
       <c r="D78">
-        <v>454.3217511692209</v>
+        <v>471.6616263281883</v>
       </c>
       <c r="E78">
         <v>887.952</v>
@@ -7689,37 +7689,37 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M78">
-        <v>345.5234740496239</v>
+        <v>332.3169540496239</v>
       </c>
       <c r="N78">
-        <v>-249.567555682277</v>
+        <v>-236.361035682277</v>
       </c>
       <c r="O78">
-        <v>-62.39188892056924</v>
+        <v>-59.09025892056924</v>
       </c>
       <c r="P78">
-        <v>-187.1756667617077</v>
+        <v>-177.2707767617077</v>
       </c>
       <c r="Q78">
-        <v>-178.3356667617077</v>
+        <v>-168.4307767617077</v>
       </c>
       <c r="R78">
         <v>3.166666666666667</v>
       </c>
       <c r="S78">
-        <v>0.2921658499715202</v>
+        <v>0.2915539511930593</v>
       </c>
       <c r="T78">
-        <v>3.810170181471776</v>
+        <v>3.801735465834351</v>
       </c>
       <c r="U78">
-        <v>0.2616309777667576</v>
+        <v>0.2516309777667576</v>
       </c>
       <c r="V78">
-        <v>0.06942793006414218</v>
+        <v>0.07218704703297964</v>
       </c>
       <c r="W78">
-        <v>0.243466480539754</v>
+        <v>0.233466480539754</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.2777117202565688</v>
+        <v>0.2887481881319186</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7738,13 +7738,13 @@
         <v>0.77</v>
       </c>
       <c r="B79">
-        <v>0.2573126389810454</v>
+        <v>0.2494657832742148</v>
       </c>
       <c r="C79">
-        <v>-648.1432227493091</v>
+        <v>-630.9341328279864</v>
       </c>
       <c r="D79">
-        <v>449.6857772506909</v>
+        <v>466.8948671720136</v>
       </c>
       <c r="E79">
         <v>905.329</v>
@@ -7771,37 +7771,37 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M79">
-        <v>350.0698355502769</v>
+        <v>336.6895455502769</v>
       </c>
       <c r="N79">
-        <v>-254.1139171829299</v>
+        <v>-240.7336271829299</v>
       </c>
       <c r="O79">
-        <v>-63.52847929573248</v>
+        <v>-60.18340679573248</v>
       </c>
       <c r="P79">
-        <v>-190.5854378871974</v>
+        <v>-180.5502203871974</v>
       </c>
       <c r="Q79">
-        <v>-181.7454378871974</v>
+        <v>-171.7102203871974</v>
       </c>
       <c r="R79">
         <v>3.347826086956522</v>
       </c>
       <c r="S79">
-        <v>0.3028774086659341</v>
+        <v>0.3022389055927575</v>
       </c>
       <c r="T79">
-        <v>3.975829754579244</v>
+        <v>3.967028312174975</v>
       </c>
       <c r="U79">
-        <v>0.2616309777667576</v>
+        <v>0.2516309777667576</v>
       </c>
       <c r="V79">
-        <v>0.06852626863473774</v>
+        <v>0.07124955291566822</v>
       </c>
       <c r="W79">
-        <v>0.2437023831011436</v>
+        <v>0.2337023831011436</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.2741050745389509</v>
+        <v>0.2849982116626729</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7820,13 +7820,13 @@
         <v>0.78</v>
       </c>
       <c r="B80">
-        <v>0.2594709487587131</v>
+        <v>0.2515240930518824</v>
       </c>
       <c r="C80">
-        <v>-670.0625398755099</v>
+        <v>-652.9825072692904</v>
       </c>
       <c r="D80">
-        <v>445.1434601244903</v>
+        <v>462.2234927307097</v>
       </c>
       <c r="E80">
         <v>922.7060000000001</v>
@@ -7853,37 +7853,37 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M80">
-        <v>354.6161970509299</v>
+        <v>341.0621370509299</v>
       </c>
       <c r="N80">
-        <v>-258.6602786835829</v>
+        <v>-245.1062186835829</v>
       </c>
       <c r="O80">
-        <v>-64.66506967089573</v>
+        <v>-61.27655467089573</v>
       </c>
       <c r="P80">
-        <v>-193.9952090126872</v>
+        <v>-183.8296640126872</v>
       </c>
       <c r="Q80">
-        <v>-185.1552090126872</v>
+        <v>-174.9896640126872</v>
       </c>
       <c r="R80">
         <v>3.545454545454546</v>
       </c>
       <c r="S80">
-        <v>0.3145627454234766</v>
+        <v>0.3138952194833374</v>
       </c>
       <c r="T80">
-        <v>4.156549288878302</v>
+        <v>4.147347780910201</v>
       </c>
       <c r="U80">
-        <v>0.2616309777667576</v>
+        <v>0.2516309777667576</v>
       </c>
       <c r="V80">
-        <v>0.06764772672916416</v>
+        <v>0.07033609710905707</v>
       </c>
       <c r="W80">
-        <v>0.2439322368789079</v>
+        <v>0.2339322368789079</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.2705909069166567</v>
+        <v>0.2813443884362283</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7902,13 +7902,13 @@
         <v>0.79</v>
       </c>
       <c r="B81">
-        <v>0.2616292585363806</v>
+        <v>0.25358240282955</v>
       </c>
       <c r="C81">
-        <v>-691.8910099355319</v>
+        <v>-674.9383316624983</v>
       </c>
       <c r="D81">
-        <v>440.6919900644683</v>
+        <v>457.6446683375018</v>
       </c>
       <c r="E81">
         <v>940.0830000000001</v>
@@ -7935,37 +7935,37 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M81">
-        <v>359.1625585515828</v>
+        <v>345.4347285515828</v>
       </c>
       <c r="N81">
-        <v>-263.2066401842359</v>
+        <v>-249.4788101842358</v>
       </c>
       <c r="O81">
-        <v>-65.80166004605897</v>
+        <v>-62.36970254605896</v>
       </c>
       <c r="P81">
-        <v>-197.4049801381769</v>
+        <v>-187.1091076381769</v>
       </c>
       <c r="Q81">
-        <v>-188.5649801381769</v>
+        <v>-178.2691076381769</v>
       </c>
       <c r="R81">
         <v>3.761904761904763</v>
       </c>
       <c r="S81">
-        <v>0.3273609713960232</v>
+        <v>0.3266616585063535</v>
       </c>
       <c r="T81">
-        <v>4.354480207396317</v>
+        <v>4.344840532382117</v>
       </c>
       <c r="U81">
-        <v>0.2616309777667576</v>
+        <v>0.2516309777667576</v>
       </c>
       <c r="V81">
-        <v>0.06679142639082031</v>
+        <v>0.06944576676590446</v>
       </c>
       <c r="W81">
-        <v>0.2441562715736909</v>
+        <v>0.2341562715736908</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.2671657055632812</v>
+        <v>0.2777830670636179</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7984,13 +7984,13 @@
         <v>0.8</v>
       </c>
       <c r="B82">
-        <v>0.2637875683140481</v>
+        <v>0.2556407126072175</v>
       </c>
       <c r="C82">
-        <v>-713.6313313783658</v>
+        <v>-696.80432945436</v>
       </c>
       <c r="D82">
-        <v>436.3286686216343</v>
+        <v>453.1556705456402</v>
       </c>
       <c r="E82">
         <v>957.46</v>
@@ -8017,37 +8017,37 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M82">
-        <v>363.7089200522357</v>
+        <v>349.8073200522358</v>
       </c>
       <c r="N82">
-        <v>-267.7530016848888</v>
+        <v>-253.8514016848888</v>
       </c>
       <c r="O82">
-        <v>-66.93825042122219</v>
+        <v>-63.4628504212222</v>
       </c>
       <c r="P82">
-        <v>-200.8147512636666</v>
+        <v>-190.3885512636666</v>
       </c>
       <c r="Q82">
-        <v>-191.9747512636666</v>
+        <v>-181.5485512636666</v>
       </c>
       <c r="R82">
         <v>4.000000000000001</v>
       </c>
       <c r="S82">
-        <v>0.3414390199658243</v>
+        <v>0.3407047414316712</v>
       </c>
       <c r="T82">
-        <v>4.572204217766132</v>
+        <v>4.562082559001222</v>
       </c>
       <c r="U82">
-        <v>0.2616309777667576</v>
+        <v>0.2516309777667576</v>
       </c>
       <c r="V82">
-        <v>0.06595653356093506</v>
+        <v>0.06857769468133064</v>
       </c>
       <c r="W82">
-        <v>0.2443747054011042</v>
+        <v>0.2343747054011042</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.2638261342437404</v>
+        <v>0.2743107787253226</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8066,13 +8066,13 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2659458780917158</v>
+        <v>0.2576990223848851</v>
       </c>
       <c r="C83">
-        <v>-735.2860968306466</v>
+        <v>-718.5831182733541</v>
       </c>
       <c r="D83">
-        <v>432.0509031693535</v>
+        <v>448.7538817266459</v>
       </c>
       <c r="E83">
         <v>974.837</v>
@@ -8099,37 +8099,37 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M83">
-        <v>368.2552815528887</v>
+        <v>354.1799115528887</v>
       </c>
       <c r="N83">
-        <v>-272.2993631855417</v>
+        <v>-258.2239931855417</v>
       </c>
       <c r="O83">
-        <v>-68.07484079638543</v>
+        <v>-64.55599829638543</v>
       </c>
       <c r="P83">
-        <v>-204.2245223891563</v>
+        <v>-193.6679948891563</v>
       </c>
       <c r="Q83">
-        <v>-195.3845223891563</v>
+        <v>-184.8279948891563</v>
       </c>
       <c r="R83">
         <v>4.263157894736843</v>
       </c>
       <c r="S83">
-        <v>0.3569989683850782</v>
+        <v>0.3562260436122855</v>
       </c>
       <c r="T83">
-        <v>4.81284654501698</v>
+        <v>4.802192167369707</v>
       </c>
       <c r="U83">
-        <v>0.2616309777667576</v>
+        <v>0.2516309777667576</v>
       </c>
       <c r="V83">
-        <v>0.06514225536882476</v>
+        <v>0.0677310564753883</v>
       </c>
       <c r="W83">
-        <v>0.2445877458006802</v>
+        <v>0.2345877458006801</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.260569021475299</v>
+        <v>0.2709242259015533</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8148,13 +8148,13 @@
         <v>0.8200000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2681041878693834</v>
+        <v>0.2597573321625527</v>
       </c>
       <c r="C84">
-        <v>-756.857798233701</v>
+        <v>-740.2772150196461</v>
       </c>
       <c r="D84">
-        <v>427.8562017662993</v>
+        <v>444.4367849803541</v>
       </c>
       <c r="E84">
         <v>992.2140000000002</v>
@@ -8181,37 +8181,37 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M84">
-        <v>372.8016430535417</v>
+        <v>358.5525030535417</v>
       </c>
       <c r="N84">
-        <v>-276.8457246861947</v>
+        <v>-262.5965846861947</v>
       </c>
       <c r="O84">
-        <v>-69.21143117154868</v>
+        <v>-65.64914617154868</v>
       </c>
       <c r="P84">
-        <v>-207.6342935146461</v>
+        <v>-196.947438514646</v>
       </c>
       <c r="Q84">
-        <v>-198.7942935146461</v>
+        <v>-188.107438514646</v>
       </c>
       <c r="R84">
         <v>4.555555555555557</v>
       </c>
       <c r="S84">
-        <v>0.374287799962027</v>
+        <v>0.3734719349240791</v>
       </c>
       <c r="T84">
-        <v>5.080226908629036</v>
+        <v>5.068980621112469</v>
       </c>
       <c r="U84">
-        <v>0.2616309777667576</v>
+        <v>0.2516309777667576</v>
       </c>
       <c r="V84">
-        <v>0.06434783762042444</v>
+        <v>0.066905067981786</v>
       </c>
       <c r="W84">
-        <v>0.2447955900929494</v>
+        <v>0.2347955900929494</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.2573913504816978</v>
+        <v>0.267620271927144</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8230,13 +8230,13 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2702624976470509</v>
+        <v>0.2618156419402203</v>
       </c>
       <c r="C85">
-        <v>-778.3488316842238</v>
+        <v>-761.8890406640473</v>
       </c>
       <c r="D85">
-        <v>423.7421683157764</v>
+        <v>440.2019593359528</v>
       </c>
       <c r="E85">
         <v>1009.591</v>
@@ -8263,37 +8263,37 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M85">
-        <v>377.3480045541946</v>
+        <v>362.9250945541946</v>
       </c>
       <c r="N85">
-        <v>-281.3920861868477</v>
+        <v>-266.9691761868476</v>
       </c>
       <c r="O85">
-        <v>-70.34802154671192</v>
+        <v>-66.7422940467119</v>
       </c>
       <c r="P85">
-        <v>-211.0440646401358</v>
+        <v>-200.2268821401357</v>
       </c>
       <c r="Q85">
-        <v>-202.2040646401358</v>
+        <v>-191.3868821401357</v>
       </c>
       <c r="R85">
         <v>4.882352941176473</v>
       </c>
       <c r="S85">
-        <v>0.3936106117244992</v>
+        <v>0.3927467546254956</v>
       </c>
       <c r="T85">
-        <v>5.379063785607215</v>
+        <v>5.367155951766144</v>
       </c>
       <c r="U85">
-        <v>0.2616309777667576</v>
+        <v>0.2516309777667576</v>
       </c>
       <c r="V85">
-        <v>0.06357256246837113</v>
+        <v>0.06609898282537895</v>
       </c>
       <c r="W85">
-        <v>0.2449984260890194</v>
+        <v>0.2349984260890194</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.2542902498734846</v>
+        <v>0.2643959313015158</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8312,13 +8312,13 @@
         <v>0.84</v>
       </c>
       <c r="B86">
-        <v>0.2724208074247185</v>
+        <v>0.2638739517178879</v>
       </c>
       <c r="C86">
-        <v>-799.7615019983443</v>
+        <v>-783.4209247752026</v>
       </c>
       <c r="D86">
-        <v>419.7064980016556</v>
+        <v>436.0470752247973</v>
       </c>
       <c r="E86">
         <v>1026.968</v>
@@ -8345,37 +8345,37 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M86">
-        <v>381.8943660548475</v>
+        <v>367.2976860548475</v>
       </c>
       <c r="N86">
-        <v>-285.9384476875005</v>
+        <v>-271.3417676875005</v>
       </c>
       <c r="O86">
-        <v>-71.48461192187513</v>
+        <v>-67.83544192187513</v>
       </c>
       <c r="P86">
-        <v>-214.4538357656254</v>
+        <v>-203.5063257656254</v>
       </c>
       <c r="Q86">
-        <v>-205.6138357656254</v>
+        <v>-194.6663257656254</v>
       </c>
       <c r="R86">
         <v>5.249999999999999</v>
       </c>
       <c r="S86">
-        <v>0.4153487749572802</v>
+        <v>0.4144309267895889</v>
       </c>
       <c r="T86">
-        <v>5.715255272207663</v>
+        <v>5.702603198751525</v>
       </c>
       <c r="U86">
-        <v>0.2616309777667576</v>
+        <v>0.2516309777667576</v>
       </c>
       <c r="V86">
-        <v>0.06281574624850959</v>
+        <v>0.06531209017269586</v>
       </c>
       <c r="W86">
-        <v>0.2451964326566115</v>
+        <v>0.2351964326566115</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.2512629849940384</v>
+        <v>0.2612483606907835</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8394,13 +8394,13 @@
         <v>0.85</v>
       </c>
       <c r="B87">
-        <v>0.2745791172023861</v>
+        <v>0.2659322614955555</v>
       </c>
       <c r="C87">
-        <v>-821.0980270173445</v>
+        <v>-804.875109792796</v>
       </c>
       <c r="D87">
-        <v>415.7469729826555</v>
+        <v>431.9698902072041</v>
       </c>
       <c r="E87">
         <v>1044.345</v>
@@ -8427,37 +8427,37 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M87">
-        <v>386.4407275555005</v>
+        <v>371.6702775555005</v>
       </c>
       <c r="N87">
-        <v>-290.4848091881535</v>
+        <v>-275.7143591881535</v>
       </c>
       <c r="O87">
-        <v>-72.62120229703838</v>
+        <v>-68.92858979703838</v>
       </c>
       <c r="P87">
-        <v>-217.8636068911151</v>
+        <v>-206.7857693911151</v>
       </c>
       <c r="Q87">
-        <v>-209.0236068911151</v>
+        <v>-197.9457693911151</v>
       </c>
       <c r="R87">
         <v>5.666666666666666</v>
       </c>
       <c r="S87">
-        <v>0.4399853599544323</v>
+        <v>0.4390063219088948</v>
       </c>
       <c r="T87">
-        <v>6.096272290354841</v>
+        <v>6.082776745334961</v>
       </c>
       <c r="U87">
-        <v>0.2616309777667576</v>
+        <v>0.2516309777667576</v>
       </c>
       <c r="V87">
-        <v>0.06207673746911536</v>
+        <v>0.06454371264125237</v>
       </c>
       <c r="W87">
-        <v>0.2453897802461426</v>
+        <v>0.2353897802461426</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.2483069498764614</v>
+        <v>0.2581748505650096</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8476,13 +8476,13 @@
         <v>0.86</v>
       </c>
       <c r="B88">
-        <v>0.2767374269800537</v>
+        <v>0.267990571273223</v>
       </c>
       <c r="C88">
-        <v>-842.3605416719338</v>
+        <v>-826.2537550632343</v>
       </c>
       <c r="D88">
-        <v>411.8614583280662</v>
+        <v>427.9682449367658</v>
       </c>
       <c r="E88">
         <v>1061.722</v>
@@ -8509,37 +8509,37 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M88">
-        <v>390.9870890561534</v>
+        <v>376.0428690561534</v>
       </c>
       <c r="N88">
-        <v>-295.0311706888065</v>
+        <v>-280.0869506888064</v>
       </c>
       <c r="O88">
-        <v>-73.75779267220162</v>
+        <v>-70.02173767220161</v>
       </c>
       <c r="P88">
-        <v>-221.2733780166049</v>
+        <v>-210.0652130166048</v>
       </c>
       <c r="Q88">
-        <v>-212.4333780166048</v>
+        <v>-201.2252130166048</v>
       </c>
       <c r="R88">
         <v>6.142857142857142</v>
       </c>
       <c r="S88">
-        <v>0.4681414570940346</v>
+        <v>0.4670924877595302</v>
       </c>
       <c r="T88">
-        <v>6.531720311094473</v>
+        <v>6.517260798573172</v>
       </c>
       <c r="U88">
-        <v>0.2616309777667576</v>
+        <v>0.2516309777667576</v>
       </c>
       <c r="V88">
-        <v>0.06135491494040471</v>
+        <v>0.06379320435472619</v>
       </c>
       <c r="W88">
-        <v>0.2455786313801033</v>
+        <v>0.2355786313801032</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.2454196597616188</v>
+        <v>0.2551728174189047</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8558,13 +8558,13 @@
         <v>0.87</v>
       </c>
       <c r="B89">
-        <v>0.2788957367577212</v>
+        <v>0.2700488810508906</v>
       </c>
       <c r="C89">
-        <v>-863.5511018207313</v>
+        <v>-847.5589406530862</v>
       </c>
       <c r="D89">
-        <v>408.0478981792687</v>
+        <v>424.0400593469137</v>
       </c>
       <c r="E89">
         <v>1079.099</v>
@@ -8591,37 +8591,37 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M89">
-        <v>395.5334505568064</v>
+        <v>380.4154605568064</v>
       </c>
       <c r="N89">
-        <v>-299.5775321894594</v>
+        <v>-284.4595421894594</v>
       </c>
       <c r="O89">
-        <v>-74.89438304736485</v>
+        <v>-71.11488554736485</v>
       </c>
       <c r="P89">
-        <v>-224.6831491420946</v>
+        <v>-213.3446566420945</v>
       </c>
       <c r="Q89">
-        <v>-215.8431491420946</v>
+        <v>-204.5046566420945</v>
       </c>
       <c r="R89">
         <v>6.692307692307692</v>
       </c>
       <c r="S89">
-        <v>0.5006292614858833</v>
+        <v>0.4994996022025709</v>
       </c>
       <c r="T89">
-        <v>7.034160335024816</v>
+        <v>7.01858855230957</v>
       </c>
       <c r="U89">
-        <v>0.2616309777667576</v>
+        <v>0.2516309777667576</v>
       </c>
       <c r="V89">
-        <v>0.06064968603304374</v>
+        <v>0.06305994913225807</v>
       </c>
       <c r="W89">
-        <v>0.2457631411086855</v>
+        <v>0.2357631411086855</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.242598744132175</v>
+        <v>0.2522397965290323</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8640,13 +8640,13 @@
         <v>0.88</v>
       </c>
       <c r="B90">
-        <v>0.2810540465353888</v>
+        <v>0.2721071908285582</v>
       </c>
       <c r="C90">
-        <v>-884.6716878774523</v>
+        <v>-868.7926709544126</v>
       </c>
       <c r="D90">
-        <v>404.3043121225478</v>
+        <v>420.1833290455876</v>
       </c>
       <c r="E90">
         <v>1096.476</v>
@@ -8673,37 +8673,37 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M90">
-        <v>400.0798120574593</v>
+        <v>384.7880520574593</v>
       </c>
       <c r="N90">
-        <v>-304.1238936901124</v>
+        <v>-288.8321336901124</v>
       </c>
       <c r="O90">
-        <v>-76.03097342252809</v>
+        <v>-72.20803342252809</v>
       </c>
       <c r="P90">
-        <v>-228.0929202675843</v>
+        <v>-216.6241002675843</v>
       </c>
       <c r="Q90">
-        <v>-219.2529202675843</v>
+        <v>-207.7841002675843</v>
       </c>
       <c r="R90">
         <v>7.333333333333334</v>
       </c>
       <c r="S90">
-        <v>0.5385316999430404</v>
+        <v>0.5373079023861186</v>
       </c>
       <c r="T90">
-        <v>7.620340362943552</v>
+        <v>7.603470931668703</v>
       </c>
       <c r="U90">
-        <v>0.2616309777667576</v>
+        <v>0.2516309777667576</v>
       </c>
       <c r="V90">
-        <v>0.05996048505539551</v>
+        <v>0.06234335880120968</v>
       </c>
       <c r="W90">
-        <v>0.2459434574343454</v>
+        <v>0.2359434574343454</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.2398419402215821</v>
+        <v>0.2493734352048388</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8722,13 +8722,13 @@
         <v>0.89</v>
       </c>
       <c r="B91">
-        <v>0.2832123563130564</v>
+        <v>0.2741655006062257</v>
       </c>
       <c r="C91">
-        <v>-905.7242082402452</v>
+        <v>-889.9568780951214</v>
       </c>
       <c r="D91">
-        <v>400.628791759755</v>
+        <v>416.3961219048787</v>
       </c>
       <c r="E91">
         <v>1113.853</v>
@@ -8755,37 +8755,37 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M91">
-        <v>404.6261735581123</v>
+        <v>389.1606435581123</v>
       </c>
       <c r="N91">
-        <v>-308.6702551907653</v>
+        <v>-293.2047251907653</v>
       </c>
       <c r="O91">
-        <v>-77.16756379769133</v>
+        <v>-73.30118129769133</v>
       </c>
       <c r="P91">
-        <v>-231.502691393074</v>
+        <v>-219.903543893074</v>
       </c>
       <c r="Q91">
-        <v>-222.662691393074</v>
+        <v>-211.063543893074</v>
       </c>
       <c r="R91">
         <v>8.090909090909092</v>
       </c>
       <c r="S91">
-        <v>0.5833254908469532</v>
+        <v>0.5819904389666748</v>
       </c>
       <c r="T91">
-        <v>8.313098577756604</v>
+        <v>8.294695561820403</v>
       </c>
       <c r="U91">
-        <v>0.2616309777667576</v>
+        <v>0.2516309777667576</v>
       </c>
       <c r="V91">
-        <v>0.05928677174016635</v>
+        <v>0.06164287162366799</v>
       </c>
       <c r="W91">
-        <v>0.2461197217077433</v>
+        <v>0.2361197217077433</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.2371470869606654</v>
+        <v>0.246571486494672</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8804,13 +8804,13 @@
         <v>0.9</v>
       </c>
       <c r="B92">
-        <v>0.2853706660907239</v>
+        <v>0.2762238103838933</v>
       </c>
       <c r="C92">
-        <v>-926.7105025356609</v>
+        <v>-911.0534251665449</v>
       </c>
       <c r="D92">
-        <v>397.0194974643392</v>
+        <v>412.6765748334552</v>
       </c>
       <c r="E92">
         <v>1131.23</v>
@@ -8837,37 +8837,37 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M92">
-        <v>409.1725350587652</v>
+        <v>393.5332350587652</v>
       </c>
       <c r="N92">
-        <v>-313.2166166914183</v>
+        <v>-297.5773166914182</v>
       </c>
       <c r="O92">
-        <v>-78.30415417285457</v>
+        <v>-74.39432917285455</v>
       </c>
       <c r="P92">
-        <v>-234.9124625185637</v>
+        <v>-223.1829875185637</v>
       </c>
       <c r="Q92">
-        <v>-226.0724625185637</v>
+        <v>-214.3429875185637</v>
       </c>
       <c r="R92">
         <v>9.000000000000002</v>
       </c>
       <c r="S92">
-        <v>0.6370780399316485</v>
+        <v>0.6356094828633423</v>
       </c>
       <c r="T92">
-        <v>9.144408435532263</v>
+        <v>9.124165118002443</v>
       </c>
       <c r="U92">
-        <v>0.2616309777667576</v>
+        <v>0.2516309777667576</v>
       </c>
       <c r="V92">
-        <v>0.05862802983194228</v>
+        <v>0.06095795082784947</v>
       </c>
       <c r="W92">
-        <v>0.2462920689972879</v>
+        <v>0.2362920689972879</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.2345121193277692</v>
+        <v>0.2438318033113979</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8886,13 +8886,13 @@
         <v>0.91</v>
       </c>
       <c r="B93">
-        <v>0.2875289758683915</v>
+        <v>0.2782821201615609</v>
       </c>
       <c r="C93">
-        <v>-947.6323446888354</v>
+        <v>-932.0841092795588</v>
       </c>
       <c r="D93">
-        <v>393.4746553111647</v>
+        <v>409.0228907204413</v>
       </c>
       <c r="E93">
         <v>1148.607</v>
@@ -8919,37 +8919,37 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M93">
-        <v>413.7188965594182</v>
+        <v>397.9058265594181</v>
       </c>
       <c r="N93">
-        <v>-317.7629781920712</v>
+        <v>-301.9499081920712</v>
       </c>
       <c r="O93">
-        <v>-79.4407445480178</v>
+        <v>-75.48747704801779</v>
       </c>
       <c r="P93">
-        <v>-238.3222336440534</v>
+        <v>-226.4624311440534</v>
       </c>
       <c r="Q93">
-        <v>-229.4822336440534</v>
+        <v>-217.6224311440534</v>
       </c>
       <c r="R93">
         <v>10.11111111111111</v>
       </c>
       <c r="S93">
-        <v>0.7027755999240539</v>
+        <v>0.7011438698481581</v>
       </c>
       <c r="T93">
-        <v>10.16045381725807</v>
+        <v>10.13796124222494</v>
       </c>
       <c r="U93">
-        <v>0.2616309777667576</v>
+        <v>0.2516309777667576</v>
       </c>
       <c r="V93">
-        <v>0.057983765767855</v>
+        <v>0.06028808323633464</v>
       </c>
       <c r="W93">
-        <v>0.246460628434315</v>
+        <v>0.236460628434315</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.23193506307142</v>
+        <v>0.2411523329453386</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8968,13 +8968,13 @@
         <v>0.92</v>
       </c>
       <c r="B94">
-        <v>0.2896872856460591</v>
+        <v>0.2803404299392285</v>
       </c>
       <c r="C94">
-        <v>-968.4914458306512</v>
+        <v>-953.0506644597804</v>
       </c>
       <c r="D94">
-        <v>389.992554169349</v>
+        <v>405.4333355402198</v>
       </c>
       <c r="E94">
         <v>1165.984</v>
@@ -9001,37 +9001,37 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M94">
-        <v>418.2652580600711</v>
+        <v>402.2784180600711</v>
       </c>
       <c r="N94">
-        <v>-322.3093396927242</v>
+        <v>-306.3224996927242</v>
       </c>
       <c r="O94">
-        <v>-80.57733492318104</v>
+        <v>-76.58062492318105</v>
       </c>
       <c r="P94">
-        <v>-241.7320047695431</v>
+        <v>-229.7418747695431</v>
       </c>
       <c r="Q94">
-        <v>-232.8920047695431</v>
+        <v>-220.9018747695431</v>
       </c>
       <c r="R94">
         <v>11.50000000000001</v>
       </c>
       <c r="S94">
-        <v>0.784897549914561</v>
+        <v>0.7830618535791781</v>
       </c>
       <c r="T94">
-        <v>11.43051054441533</v>
+        <v>11.40520639750306</v>
       </c>
       <c r="U94">
-        <v>0.2616309777667576</v>
+        <v>0.2516309777667576</v>
       </c>
       <c r="V94">
-        <v>0.05735350744429136</v>
+        <v>0.05963277798376578</v>
       </c>
       <c r="W94">
-        <v>0.2466255235357546</v>
+        <v>0.2366255235357546</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.2294140297771655</v>
+        <v>0.2385311119350632</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9050,13 +9050,13 @@
         <v>0.93</v>
       </c>
       <c r="B95">
-        <v>0.2918455954237267</v>
+        <v>0.2823987397168961</v>
       </c>
       <c r="C95">
-        <v>-989.2894570518912</v>
+        <v>-973.9547643916453</v>
       </c>
       <c r="D95">
-        <v>386.571542948109</v>
+        <v>401.9062356083548</v>
       </c>
       <c r="E95">
         <v>1183.361</v>
@@ -9083,37 +9083,37 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M95">
-        <v>422.8116195607241</v>
+        <v>406.651009560724</v>
       </c>
       <c r="N95">
-        <v>-326.8557011933771</v>
+        <v>-310.6950911933771</v>
       </c>
       <c r="O95">
-        <v>-81.71392529834428</v>
+        <v>-77.67377279834427</v>
       </c>
       <c r="P95">
-        <v>-245.1417758950328</v>
+        <v>-233.0213183950328</v>
       </c>
       <c r="Q95">
-        <v>-236.3017758950328</v>
+        <v>-224.1813183950328</v>
       </c>
       <c r="R95">
         <v>13.2857142857143</v>
       </c>
       <c r="S95">
-        <v>0.8904829141880696</v>
+        <v>0.8883849755190609</v>
       </c>
       <c r="T95">
-        <v>13.06344062218895</v>
+        <v>13.03452159714636</v>
       </c>
       <c r="U95">
-        <v>0.2616309777667576</v>
+        <v>0.2516309777667576</v>
       </c>
       <c r="V95">
-        <v>0.05673680306316994</v>
+        <v>0.05899156531727368</v>
       </c>
       <c r="W95">
-        <v>0.2467868725059805</v>
+        <v>0.2367868725059805</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.2269472122526798</v>
+        <v>0.2359662612690947</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9132,13 +9132,13 @@
         <v>0.9400000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2940039052013943</v>
+        <v>0.2844570494945636</v>
       </c>
       <c r="C96">
-        <v>-1010.027972013696</v>
+        <v>-994.7980250204859</v>
       </c>
       <c r="D96">
-        <v>383.2100279863038</v>
+        <v>398.4399749795143</v>
       </c>
       <c r="E96">
         <v>1200.738</v>
@@ -9165,37 +9165,37 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M96">
-        <v>427.357981061377</v>
+        <v>411.023601061377</v>
       </c>
       <c r="N96">
-        <v>-331.4020626940301</v>
+        <v>-315.0676826940301</v>
       </c>
       <c r="O96">
-        <v>-82.85051567350752</v>
+        <v>-78.76692067350751</v>
       </c>
       <c r="P96">
-        <v>-248.5515470205225</v>
+        <v>-236.3007620205225</v>
       </c>
       <c r="Q96">
-        <v>-239.7115470205225</v>
+        <v>-227.4607620205225</v>
       </c>
       <c r="R96">
         <v>15.66666666666668</v>
       </c>
       <c r="S96">
-        <v>1.031263399886082</v>
+        <v>1.028815804772238</v>
       </c>
       <c r="T96">
-        <v>15.24068072588712</v>
+        <v>15.20694186333742</v>
       </c>
       <c r="U96">
-        <v>0.2616309777667576</v>
+        <v>0.2516309777667576</v>
       </c>
       <c r="V96">
-        <v>0.05613322005185963</v>
+        <v>0.05836399547347289</v>
       </c>
       <c r="W96">
-        <v>0.246944788519393</v>
+        <v>0.236944788519393</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.2245328802074386</v>
+        <v>0.2334559818938916</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9214,13 +9214,13 @@
         <v>0.9500000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2961622149790618</v>
+        <v>0.2865153592722312</v>
       </c>
       <c r="C97">
-        <v>-1030.708529422997</v>
+        <v>-1015.582007021109</v>
       </c>
       <c r="D97">
-        <v>379.9064705770028</v>
+        <v>395.0329929788913</v>
       </c>
       <c r="E97">
         <v>1218.115</v>
@@ -9247,37 +9247,37 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M97">
-        <v>431.90434256203</v>
+        <v>415.3961925620299</v>
       </c>
       <c r="N97">
-        <v>-335.948424194683</v>
+        <v>-319.440274194683</v>
       </c>
       <c r="O97">
-        <v>-83.98710604867075</v>
+        <v>-79.86006854867074</v>
       </c>
       <c r="P97">
-        <v>-251.9613181460123</v>
+        <v>-239.5802056460122</v>
       </c>
       <c r="Q97">
-        <v>-243.1213181460123</v>
+        <v>-230.7402056460122</v>
       </c>
       <c r="R97">
         <v>19.00000000000003</v>
       </c>
       <c r="S97">
-        <v>1.228356079863299</v>
+        <v>1.225418965726686</v>
       </c>
       <c r="T97">
-        <v>18.28881687106455</v>
+        <v>18.24833023600491</v>
       </c>
       <c r="U97">
-        <v>0.2616309777667576</v>
+        <v>0.2516309777667576</v>
       </c>
       <c r="V97">
-        <v>0.05554234405131374</v>
+        <v>0.05774963762638371</v>
       </c>
       <c r="W97">
-        <v>0.2470993799851547</v>
+        <v>0.2370993799851547</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.222169376205255</v>
+        <v>0.2309985505055349</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9296,13 +9296,13 @@
         <v>0.96</v>
       </c>
       <c r="B98">
-        <v>0.2983205247567294</v>
+        <v>0.2885736690498988</v>
       </c>
       <c r="C98">
-        <v>-1051.332615381002</v>
+        <v>-1036.308218140798</v>
       </c>
       <c r="D98">
-        <v>376.6593846189982</v>
+        <v>391.6837818592019</v>
       </c>
       <c r="E98">
         <v>1235.492</v>
@@ -9329,37 +9329,37 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M98">
-        <v>436.4507040626829</v>
+        <v>419.7687840626829</v>
       </c>
       <c r="N98">
-        <v>-340.4947856953359</v>
+        <v>-323.8128656953359</v>
       </c>
       <c r="O98">
-        <v>-85.12369642383398</v>
+        <v>-80.95321642383398</v>
       </c>
       <c r="P98">
-        <v>-255.3710892715019</v>
+        <v>-242.859649271502</v>
       </c>
       <c r="Q98">
-        <v>-246.5310892715019</v>
+        <v>-234.0196492715019</v>
       </c>
       <c r="R98">
         <v>23.99999999999998</v>
       </c>
       <c r="S98">
-        <v>1.52399509982912</v>
+        <v>1.520323707158355</v>
       </c>
       <c r="T98">
-        <v>22.86102108883063</v>
+        <v>22.81041279500609</v>
       </c>
       <c r="U98">
-        <v>0.2616309777667576</v>
+        <v>0.2516309777667576</v>
       </c>
       <c r="V98">
-        <v>0.05496377796744589</v>
+        <v>0.05714807890110887</v>
       </c>
       <c r="W98">
-        <v>0.2472507507953798</v>
+        <v>0.2372507507953797</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2198551118697836</v>
+        <v>0.2285923156044355</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9378,13 +9378,13 @@
         <v>0.97</v>
       </c>
       <c r="B99">
-        <v>0.300478834534397</v>
+        <v>0.2906319788275664</v>
       </c>
       <c r="C99">
-        <v>-1071.901665612265</v>
+        <v>-1056.978115424132</v>
       </c>
       <c r="D99">
-        <v>373.4673343877347</v>
+        <v>388.3908845758679</v>
       </c>
       <c r="E99">
         <v>1252.869</v>
@@ -9411,37 +9411,37 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M99">
-        <v>440.9970655633358</v>
+        <v>424.1413755633358</v>
       </c>
       <c r="N99">
-        <v>-345.0411471959889</v>
+        <v>-328.1854571959888</v>
       </c>
       <c r="O99">
-        <v>-86.26028679899721</v>
+        <v>-82.0463642989972</v>
       </c>
       <c r="P99">
-        <v>-258.7808603969917</v>
+        <v>-246.1390928969916</v>
       </c>
       <c r="Q99">
-        <v>-249.9408603969917</v>
+        <v>-237.2990928969916</v>
       </c>
       <c r="R99">
         <v>32.33333333333331</v>
       </c>
       <c r="S99">
-        <v>2.01672679977216</v>
+        <v>2.011831609544473</v>
       </c>
       <c r="T99">
-        <v>30.48136145177418</v>
+        <v>30.41388372667478</v>
       </c>
       <c r="U99">
-        <v>0.2616309777667576</v>
+        <v>0.2516309777667576</v>
       </c>
       <c r="V99">
-        <v>0.05439714108118356</v>
+        <v>0.05655892344852013</v>
       </c>
       <c r="W99">
-        <v>0.2473990005579713</v>
+        <v>0.2373990005579713</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2175885643247343</v>
+        <v>0.2262356937940806</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9460,13 +9460,13 @@
         <v>0.98</v>
       </c>
       <c r="B100">
-        <v>0.3026371443120646</v>
+        <v>0.2926902886052339</v>
       </c>
       <c r="C100">
-        <v>-1092.417067581371</v>
+        <v>-1077.59310732651</v>
       </c>
       <c r="D100">
-        <v>370.328932418629</v>
+        <v>385.1528926734899</v>
       </c>
       <c r="E100">
         <v>1270.246</v>
@@ -9493,37 +9493,37 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M100">
-        <v>445.5434270639888</v>
+        <v>428.5139670639887</v>
       </c>
       <c r="N100">
-        <v>-349.5875086966418</v>
+        <v>-332.5580486966418</v>
       </c>
       <c r="O100">
-        <v>-87.39687717416045</v>
+        <v>-83.13951217416044</v>
       </c>
       <c r="P100">
-        <v>-262.1906315224813</v>
+        <v>-249.4185365224813</v>
       </c>
       <c r="Q100">
-        <v>-253.3506315224813</v>
+        <v>-240.5785365224813</v>
       </c>
       <c r="R100">
         <v>48.99999999999996</v>
       </c>
       <c r="S100">
-        <v>3.002190199658239</v>
+        <v>2.994847414316709</v>
       </c>
       <c r="T100">
-        <v>45.72204217766127</v>
+        <v>45.62082559001217</v>
       </c>
       <c r="U100">
-        <v>0.2616309777667576</v>
+        <v>0.2516309777667576</v>
       </c>
       <c r="V100">
-        <v>0.05384206821300822</v>
+        <v>0.05598179157659645</v>
       </c>
       <c r="W100">
-        <v>0.2475442248152038</v>
+        <v>0.2375442248152038</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9531,7 +9531,7 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2153682728520329</v>
+        <v>0.2239271663063859</v>
       </c>
       <c r="Z100">
         <v>0</v>
@@ -9542,13 +9542,13 @@
         <v>0.99</v>
       </c>
       <c r="B101">
-        <v>0.3047954540897321</v>
+        <v>0.2947485983829015</v>
       </c>
       <c r="C101">
-        <v>-1112.880162503776</v>
+        <v>-1098.154555722831</v>
       </c>
       <c r="D101">
-        <v>367.2428374962238</v>
+        <v>381.9684442771691</v>
       </c>
       <c r="E101">
         <v>1287.623</v>
@@ -9575,37 +9575,37 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M101">
-        <v>450.0897885646418</v>
+        <v>432.8865585646417</v>
       </c>
       <c r="N101">
-        <v>-354.1338701972948</v>
+        <v>-336.9306401972948</v>
       </c>
       <c r="O101">
-        <v>-88.5334675493237</v>
+        <v>-84.2326600493237</v>
       </c>
       <c r="P101">
-        <v>-265.6004026479711</v>
+        <v>-252.6979801479711</v>
       </c>
       <c r="Q101">
-        <v>-256.7604026479711</v>
+        <v>-243.8579801479711</v>
       </c>
       <c r="R101">
         <v>98.99999999999991</v>
       </c>
       <c r="S101">
-        <v>5.958580399316479</v>
+        <v>5.943894828633418</v>
       </c>
       <c r="T101">
-        <v>91.44408435532254</v>
+        <v>91.24165118002435</v>
       </c>
       <c r="U101">
-        <v>0.2616309777667576</v>
+        <v>0.2516309777667576</v>
       </c>
       <c r="V101">
-        <v>0.05329820893812934</v>
+        <v>0.05541631893440861</v>
       </c>
       <c r="W101">
-        <v>0.2476865152490579</v>
+        <v>0.2376865152490579</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
@@ -9613,7 +9613,7 @@
         </is>
       </c>
       <c r="Y101">
-        <v>0.2131928357525174</v>
+        <v>0.2216652757376344</v>
       </c>
       <c r="Z101">
         <v>0</v>

--- a/research/traditional_assets/database/data/spain/spain_homebuilding.xlsx
+++ b/research/traditional_assets/database/data/spain/spain_homebuilding.xlsx
@@ -1284,7 +1284,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1421,22 +1421,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.108204599122607</v>
+        <v>0.1080865699580512</v>
       </c>
       <c r="C2">
-        <v>1763.974051371971</v>
+        <v>1749.484508144377</v>
       </c>
       <c r="D2">
-        <v>1523.774051371971</v>
+        <v>1526.661508144377</v>
       </c>
       <c r="E2">
-        <v>-432.7</v>
+        <v>-415.323</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>17.377</v>
       </c>
       <c r="G2">
         <v>240.2</v>
@@ -1457,28 +1457,28 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>1.149158000652947</v>
       </c>
       <c r="N2">
-        <v>95.95591836734694</v>
+        <v>94.80676036669399</v>
       </c>
       <c r="O2">
-        <v>23.98897959183673</v>
+        <v>23.7016900916735</v>
       </c>
       <c r="P2">
-        <v>71.9669387755102</v>
+        <v>71.10507027502049</v>
       </c>
       <c r="Q2">
-        <v>80.8069387755102</v>
+        <v>79.9450702750205</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.108204599122607</v>
+        <v>0.1086773612371722</v>
       </c>
       <c r="T2">
-        <v>0.9653793013859413</v>
+        <v>0.9726927809418954</v>
       </c>
       <c r="U2">
         <v>0.0661309777667576</v>
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>83.50106627010835</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1503,22 +1503,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1080865699580512</v>
+        <v>0.1079685407934953</v>
       </c>
       <c r="C3">
-        <v>1749.484508144377</v>
+        <v>1735.005928793566</v>
       </c>
       <c r="D3">
-        <v>1526.661508144377</v>
+        <v>1529.559928793566</v>
       </c>
       <c r="E3">
-        <v>-415.323</v>
+        <v>-397.946</v>
       </c>
       <c r="F3">
-        <v>17.377</v>
+        <v>34.754</v>
       </c>
       <c r="G3">
         <v>240.2</v>
@@ -1539,28 +1539,28 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M3">
-        <v>1.149158000652947</v>
+        <v>2.298316001305894</v>
       </c>
       <c r="N3">
-        <v>94.80676036669399</v>
+        <v>93.65760236604105</v>
       </c>
       <c r="O3">
-        <v>23.7016900916735</v>
+        <v>23.41440059151026</v>
       </c>
       <c r="P3">
-        <v>71.10507027502049</v>
+        <v>70.24320177453079</v>
       </c>
       <c r="Q3">
-        <v>79.9450702750205</v>
+        <v>79.08320177453079</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1086773612371722</v>
+        <v>0.1091597715581571</v>
       </c>
       <c r="T3">
-        <v>0.9726927809418954</v>
+        <v>0.980155515182665</v>
       </c>
       <c r="U3">
         <v>0.0661309777667576</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>83.50106627010835</v>
+        <v>41.75053313505418</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1585,22 +1585,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1079685407934953</v>
+        <v>0.1078505116289395</v>
       </c>
       <c r="C4">
-        <v>1735.005928793566</v>
+        <v>1720.538375884239</v>
       </c>
       <c r="D4">
-        <v>1529.559928793566</v>
+        <v>1532.469375884239</v>
       </c>
       <c r="E4">
-        <v>-397.946</v>
+        <v>-380.569</v>
       </c>
       <c r="F4">
-        <v>34.754</v>
+        <v>52.131</v>
       </c>
       <c r="G4">
         <v>240.2</v>
@@ -1621,28 +1621,28 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M4">
-        <v>2.298316001305894</v>
+        <v>3.44747400195884</v>
       </c>
       <c r="N4">
-        <v>93.65760236604105</v>
+        <v>92.5084443653881</v>
       </c>
       <c r="O4">
-        <v>23.41440059151026</v>
+        <v>23.12711109134703</v>
       </c>
       <c r="P4">
-        <v>70.24320177453079</v>
+        <v>69.38133327404108</v>
       </c>
       <c r="Q4">
-        <v>79.08320177453079</v>
+        <v>78.22133327404109</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1091597715581571</v>
+        <v>0.1096521284836984</v>
       </c>
       <c r="T4">
-        <v>0.980155515182665</v>
+        <v>0.9877721202325224</v>
       </c>
       <c r="U4">
         <v>0.0661309777667576</v>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>41.75053313505418</v>
+        <v>27.83368875670279</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1667,22 +1667,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1078505116289395</v>
+        <v>0.1077324824643837</v>
       </c>
       <c r="C5">
-        <v>1720.538375884239</v>
+        <v>1706.081912458032</v>
       </c>
       <c r="D5">
-        <v>1532.469375884239</v>
+        <v>1535.389912458032</v>
       </c>
       <c r="E5">
-        <v>-380.569</v>
+        <v>-363.192</v>
       </c>
       <c r="F5">
-        <v>52.131</v>
+        <v>69.50800000000001</v>
       </c>
       <c r="G5">
         <v>240.2</v>
@@ -1703,28 +1703,28 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M5">
-        <v>3.44747400195884</v>
+        <v>4.596632002611788</v>
       </c>
       <c r="N5">
-        <v>92.5084443653881</v>
+        <v>91.35928636473515</v>
       </c>
       <c r="O5">
-        <v>23.12711109134703</v>
+        <v>22.83982159118379</v>
       </c>
       <c r="P5">
-        <v>69.38133327404108</v>
+        <v>68.51946477355136</v>
       </c>
       <c r="Q5">
-        <v>78.22133327404109</v>
+        <v>77.35946477355137</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1096521284836984</v>
+        <v>0.1101547428451885</v>
       </c>
       <c r="T5">
-        <v>0.9877721202325224</v>
+        <v>0.9955474045542519</v>
       </c>
       <c r="U5">
         <v>0.0661309777667576</v>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>27.83368875670279</v>
+        <v>20.87526656752709</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1749,22 +1749,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1077324824643837</v>
+        <v>0.1076144532998278</v>
       </c>
       <c r="C6">
-        <v>1706.081912458032</v>
+        <v>1691.636602038071</v>
       </c>
       <c r="D6">
-        <v>1535.389912458032</v>
+        <v>1538.321602038071</v>
       </c>
       <c r="E6">
-        <v>-363.192</v>
+        <v>-345.815</v>
       </c>
       <c r="F6">
-        <v>69.50800000000001</v>
+        <v>86.88500000000001</v>
       </c>
       <c r="G6">
         <v>240.2</v>
@@ -1785,28 +1785,28 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M6">
-        <v>4.596632002611788</v>
+        <v>5.745790003264734</v>
       </c>
       <c r="N6">
-        <v>91.35928636473515</v>
+        <v>90.21012836408221</v>
       </c>
       <c r="O6">
-        <v>22.83982159118379</v>
+        <v>22.55253209102055</v>
       </c>
       <c r="P6">
-        <v>68.51946477355136</v>
+        <v>67.65759627306166</v>
       </c>
       <c r="Q6">
-        <v>77.35946477355137</v>
+        <v>76.49759627306166</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1101547428451885</v>
+        <v>0.1106679385616573</v>
       </c>
       <c r="T6">
-        <v>0.9955474045542519</v>
+        <v>1.003486379072228</v>
       </c>
       <c r="U6">
         <v>0.0661309777667576</v>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>20.87526656752709</v>
+        <v>16.70021325402168</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1831,22 +1831,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1076144532998278</v>
+        <v>0.107496424135272</v>
       </c>
       <c r="C7">
-        <v>1691.636602038071</v>
+        <v>1677.202508633575</v>
       </c>
       <c r="D7">
-        <v>1538.321602038071</v>
+        <v>1541.264508633575</v>
       </c>
       <c r="E7">
-        <v>-345.815</v>
+        <v>-328.438</v>
       </c>
       <c r="F7">
-        <v>86.88500000000001</v>
+        <v>104.262</v>
       </c>
       <c r="G7">
         <v>240.2</v>
@@ -1867,28 +1867,28 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M7">
-        <v>5.745790003264734</v>
+        <v>6.894948003917682</v>
       </c>
       <c r="N7">
-        <v>90.21012836408221</v>
+        <v>89.06097036342926</v>
       </c>
       <c r="O7">
-        <v>22.55253209102055</v>
+        <v>22.26524259085732</v>
       </c>
       <c r="P7">
-        <v>67.65759627306166</v>
+        <v>66.79572777257195</v>
       </c>
       <c r="Q7">
-        <v>76.49759627306166</v>
+        <v>75.63572777257195</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1106679385616573</v>
+        <v>0.1111920533359233</v>
       </c>
       <c r="T7">
-        <v>1.003486379072228</v>
+        <v>1.011594267941651</v>
       </c>
       <c r="U7">
         <v>0.0661309777667576</v>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>16.70021325402168</v>
+        <v>13.91684437835139</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1913,22 +1913,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.107496424135272</v>
+        <v>0.1074571449707162</v>
       </c>
       <c r="C8">
-        <v>1677.202508633575</v>
+        <v>1660.807383196328</v>
       </c>
       <c r="D8">
-        <v>1541.264508633575</v>
+        <v>1542.246383196328</v>
       </c>
       <c r="E8">
-        <v>-328.438</v>
+        <v>-311.061</v>
       </c>
       <c r="F8">
-        <v>104.262</v>
+        <v>121.639</v>
       </c>
       <c r="G8">
         <v>240.2</v>
@@ -1949,45 +1949,45 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M8">
-        <v>6.894948003917681</v>
+        <v>8.226564504570625</v>
       </c>
       <c r="N8">
-        <v>89.06097036342926</v>
+        <v>87.72935386277632</v>
       </c>
       <c r="O8">
-        <v>22.26524259085732</v>
+        <v>21.93233846569408</v>
       </c>
       <c r="P8">
-        <v>66.79572777257195</v>
+        <v>65.79701539708225</v>
       </c>
       <c r="Q8">
-        <v>75.63572777257195</v>
+        <v>74.63701539708225</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1111920533359233</v>
+        <v>0.1117274393956574</v>
       </c>
       <c r="T8">
-        <v>1.011594267941651</v>
+        <v>1.019876520012567</v>
       </c>
       <c r="U8">
-        <v>0.0661309777667576</v>
+        <v>0.06763097776675758</v>
       </c>
       <c r="V8">
         <v>0.25</v>
       </c>
       <c r="W8">
-        <v>0.0495982333250682</v>
+        <v>0.05072323332506819</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y8">
-        <v>13.91684437835139</v>
+        <v>11.66415437623257</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1995,22 +1995,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1074571449707162</v>
+        <v>0.1073503658061603</v>
       </c>
       <c r="C9">
-        <v>1660.807383196328</v>
+        <v>1646.10591206086</v>
       </c>
       <c r="D9">
-        <v>1542.246383196328</v>
+        <v>1544.92191206086</v>
       </c>
       <c r="E9">
-        <v>-311.061</v>
+        <v>-293.684</v>
       </c>
       <c r="F9">
-        <v>121.639</v>
+        <v>139.016</v>
       </c>
       <c r="G9">
         <v>240.2</v>
@@ -2031,28 +2031,28 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M9">
-        <v>8.226564504570627</v>
+        <v>9.401788005223574</v>
       </c>
       <c r="N9">
-        <v>87.72935386277631</v>
+        <v>86.55413036212336</v>
       </c>
       <c r="O9">
-        <v>21.93233846569408</v>
+        <v>21.63853259053084</v>
       </c>
       <c r="P9">
-        <v>65.79701539708223</v>
+        <v>64.91559777159252</v>
       </c>
       <c r="Q9">
-        <v>74.63701539708224</v>
+        <v>73.75559777159252</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1117274393956574</v>
+        <v>0.112274464282777</v>
       </c>
       <c r="T9">
-        <v>1.019876520012567</v>
+        <v>1.028338821041546</v>
       </c>
       <c r="U9">
         <v>0.06763097776675758</v>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>11.66415437623256</v>
+        <v>10.20613507920349</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2077,22 +2077,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1073503658061603</v>
+        <v>0.1073583366416045</v>
       </c>
       <c r="C10">
-        <v>1646.10591206086</v>
+        <v>1628.528868995909</v>
       </c>
       <c r="D10">
-        <v>1544.92191206086</v>
+        <v>1544.721868995909</v>
       </c>
       <c r="E10">
-        <v>-293.684</v>
+        <v>-276.307</v>
       </c>
       <c r="F10">
-        <v>139.016</v>
+        <v>156.393</v>
       </c>
       <c r="G10">
         <v>240.2</v>
@@ -2113,45 +2113,45 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M10">
-        <v>9.401788005223574</v>
+        <v>10.84287960587652</v>
       </c>
       <c r="N10">
-        <v>86.55413036212336</v>
+        <v>85.11303876147042</v>
       </c>
       <c r="O10">
-        <v>21.63853259053084</v>
+        <v>21.27825969036761</v>
       </c>
       <c r="P10">
-        <v>64.91559777159252</v>
+        <v>63.83477907110282</v>
       </c>
       <c r="Q10">
-        <v>73.75559777159252</v>
+        <v>72.67477907110282</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.112274464282777</v>
+        <v>0.1128335116948883</v>
       </c>
       <c r="T10">
-        <v>1.028338821041546</v>
+        <v>1.036987106708525</v>
       </c>
       <c r="U10">
-        <v>0.06763097776675758</v>
+        <v>0.06933097776675759</v>
       </c>
       <c r="V10">
         <v>0.25</v>
       </c>
       <c r="W10">
-        <v>0.05072323332506819</v>
+        <v>0.05199823332506819</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y10">
-        <v>10.20613507920349</v>
+        <v>8.849671107234435</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1073583366416045</v>
+        <v>0.1072643074770487</v>
       </c>
       <c r="C11">
-        <v>1628.528868995909</v>
+        <v>1613.515011326392</v>
       </c>
       <c r="D11">
-        <v>1544.721868995909</v>
+        <v>1547.085011326392</v>
       </c>
       <c r="E11">
-        <v>-276.307</v>
+        <v>-258.93</v>
       </c>
       <c r="F11">
-        <v>156.393</v>
+        <v>173.77</v>
       </c>
       <c r="G11">
         <v>240.2</v>
@@ -2195,28 +2195,28 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M11">
-        <v>10.84287960587652</v>
+        <v>12.04764400652946</v>
       </c>
       <c r="N11">
-        <v>85.11303876147042</v>
+        <v>83.90827436081747</v>
       </c>
       <c r="O11">
-        <v>21.27825969036761</v>
+        <v>20.97706859020437</v>
       </c>
       <c r="P11">
-        <v>63.83477907110282</v>
+        <v>62.9312057706131</v>
       </c>
       <c r="Q11">
-        <v>72.67477907110282</v>
+        <v>71.77120577061311</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1128335116948883</v>
+        <v>0.1134049823828243</v>
       </c>
       <c r="T11">
-        <v>1.036987106708525</v>
+        <v>1.045827576501436</v>
       </c>
       <c r="U11">
         <v>0.06933097776675759</v>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>8.849671107234435</v>
+        <v>7.964703996510993</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2241,22 +2241,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1072643074770487</v>
+        <v>0.1072362783124928</v>
       </c>
       <c r="C12">
-        <v>1613.515011326392</v>
+        <v>1596.843840220254</v>
       </c>
       <c r="D12">
-        <v>1547.085011326392</v>
+        <v>1547.790840220254</v>
       </c>
       <c r="E12">
-        <v>-258.9299999999999</v>
+        <v>-241.553</v>
       </c>
       <c r="F12">
-        <v>173.77</v>
+        <v>191.147</v>
       </c>
       <c r="G12">
         <v>240.2</v>
@@ -2277,45 +2277,45 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M12">
-        <v>12.04764400652947</v>
+        <v>13.40532600718241</v>
       </c>
       <c r="N12">
-        <v>83.90827436081747</v>
+        <v>82.55059236016453</v>
       </c>
       <c r="O12">
-        <v>20.97706859020437</v>
+        <v>20.63764809004113</v>
       </c>
       <c r="P12">
-        <v>62.9312057706131</v>
+        <v>61.9129442701234</v>
       </c>
       <c r="Q12">
-        <v>71.77120577061311</v>
+        <v>70.75294427012339</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1134049823828243</v>
+        <v>0.1139892951086914</v>
       </c>
       <c r="T12">
-        <v>1.045827576501436</v>
+        <v>1.054866708536885</v>
       </c>
       <c r="U12">
-        <v>0.06933097776675759</v>
+        <v>0.07013097776675759</v>
       </c>
       <c r="V12">
         <v>0.25</v>
       </c>
       <c r="W12">
-        <v>0.05199823332506819</v>
+        <v>0.05259823332506819</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y12">
-        <v>7.964703996510992</v>
+        <v>7.158044371016036</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2323,22 +2323,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1072362783124928</v>
+        <v>0.107148249147937</v>
       </c>
       <c r="C13">
-        <v>1596.843840220254</v>
+        <v>1581.687779472215</v>
       </c>
       <c r="D13">
-        <v>1547.790840220254</v>
+        <v>1550.011779472215</v>
       </c>
       <c r="E13">
-        <v>-241.553</v>
+        <v>-224.176</v>
       </c>
       <c r="F13">
-        <v>191.147</v>
+        <v>208.524</v>
       </c>
       <c r="G13">
         <v>240.2</v>
@@ -2359,28 +2359,28 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M13">
-        <v>13.40532600718241</v>
+        <v>14.62399200783536</v>
       </c>
       <c r="N13">
-        <v>82.55059236016453</v>
+        <v>81.33192635951158</v>
       </c>
       <c r="O13">
-        <v>20.63764809004113</v>
+        <v>20.3329815898779</v>
       </c>
       <c r="P13">
-        <v>61.9129442701234</v>
+        <v>60.99894476963369</v>
       </c>
       <c r="Q13">
-        <v>70.75294427012339</v>
+        <v>69.83894476963368</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1139892951086914</v>
+        <v>0.1145868876692373</v>
       </c>
       <c r="T13">
-        <v>1.054866708536885</v>
+        <v>1.064111275391322</v>
       </c>
       <c r="U13">
         <v>0.07013097776675759</v>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>7.158044371016036</v>
+        <v>6.561540673431367</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2405,22 +2405,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.107148249147937</v>
+        <v>0.1071577199833812</v>
       </c>
       <c r="C14">
-        <v>1581.687779472215</v>
+        <v>1564.071528298869</v>
       </c>
       <c r="D14">
-        <v>1550.011779472215</v>
+        <v>1549.772528298869</v>
       </c>
       <c r="E14">
-        <v>-224.176</v>
+        <v>-206.799</v>
       </c>
       <c r="F14">
-        <v>208.524</v>
+        <v>225.901</v>
       </c>
       <c r="G14">
         <v>240.2</v>
@@ -2441,45 +2441,45 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M14">
-        <v>14.62399200783536</v>
+        <v>16.06855900848831</v>
       </c>
       <c r="N14">
-        <v>81.33192635951158</v>
+        <v>79.88735935885863</v>
       </c>
       <c r="O14">
-        <v>20.3329815898779</v>
+        <v>19.97183983971466</v>
       </c>
       <c r="P14">
-        <v>60.99894476963369</v>
+        <v>59.91551951914397</v>
       </c>
       <c r="Q14">
-        <v>69.83894476963368</v>
+        <v>68.75551951914397</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1145868876692373</v>
+        <v>0.1151982179897957</v>
       </c>
       <c r="T14">
-        <v>1.064111275391322</v>
+        <v>1.073568361024021</v>
       </c>
       <c r="U14">
-        <v>0.07013097776675759</v>
+        <v>0.07113097776675759</v>
       </c>
       <c r="V14">
         <v>0.25</v>
       </c>
       <c r="W14">
-        <v>0.05259823332506819</v>
+        <v>0.05334823332506819</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y14">
-        <v>6.561540673431367</v>
+        <v>5.971656718978826</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2487,22 +2487,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1071577199833812</v>
+        <v>0.1070771908188253</v>
       </c>
       <c r="C15">
-        <v>1564.071528298869</v>
+        <v>1548.731205980855</v>
       </c>
       <c r="D15">
-        <v>1549.772528298869</v>
+        <v>1551.809205980855</v>
       </c>
       <c r="E15">
-        <v>-206.799</v>
+        <v>-189.422</v>
       </c>
       <c r="F15">
-        <v>225.901</v>
+        <v>243.278</v>
       </c>
       <c r="G15">
         <v>240.2</v>
@@ -2523,28 +2523,28 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M15">
-        <v>16.06855900848831</v>
+        <v>17.30460200914125</v>
       </c>
       <c r="N15">
-        <v>79.88735935885863</v>
+        <v>78.65131635820569</v>
       </c>
       <c r="O15">
-        <v>19.97183983971466</v>
+        <v>19.66282908955142</v>
       </c>
       <c r="P15">
-        <v>59.91551951914397</v>
+        <v>58.98848726865427</v>
       </c>
       <c r="Q15">
-        <v>68.75551951914397</v>
+        <v>67.82848726865427</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1151982179897957</v>
+        <v>0.1158237652945532</v>
       </c>
       <c r="T15">
-        <v>1.073568361024021</v>
+        <v>1.083245378880736</v>
       </c>
       <c r="U15">
         <v>0.07113097776675759</v>
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>5.971656718978826</v>
+        <v>5.545109810480339</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2569,22 +2569,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1070771908188253</v>
+        <v>0.1069966616542695</v>
       </c>
       <c r="C16">
-        <v>1548.731205980855</v>
+        <v>1533.396243822947</v>
       </c>
       <c r="D16">
-        <v>1551.809205980855</v>
+        <v>1553.851243822947</v>
       </c>
       <c r="E16">
-        <v>-189.422</v>
+        <v>-172.045</v>
       </c>
       <c r="F16">
-        <v>243.278</v>
+        <v>260.655</v>
       </c>
       <c r="G16">
         <v>240.2</v>
@@ -2605,28 +2605,28 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M16">
-        <v>17.30460200914125</v>
+        <v>18.5406450097942</v>
       </c>
       <c r="N16">
-        <v>78.65131635820569</v>
+        <v>77.41527335755273</v>
       </c>
       <c r="O16">
-        <v>19.66282908955142</v>
+        <v>19.35381833938818</v>
       </c>
       <c r="P16">
-        <v>58.98848726865427</v>
+        <v>58.06145501816455</v>
       </c>
       <c r="Q16">
-        <v>67.82848726865427</v>
+        <v>66.90145501816455</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1158237652945532</v>
+        <v>0.1164640313594226</v>
       </c>
       <c r="T16">
-        <v>1.083245378880736</v>
+        <v>1.093150091275257</v>
       </c>
       <c r="U16">
         <v>0.07113097776675759</v>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>5.545109810480339</v>
+        <v>5.175435823114983</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2651,22 +2651,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1069966616542695</v>
+        <v>0.1069161324897136</v>
       </c>
       <c r="C17">
-        <v>1533.396243822947</v>
+        <v>1518.066663013456</v>
       </c>
       <c r="D17">
-        <v>1553.851243822947</v>
+        <v>1555.898663013455</v>
       </c>
       <c r="E17">
-        <v>-172.045</v>
+        <v>-154.6679999999999</v>
       </c>
       <c r="F17">
-        <v>260.655</v>
+        <v>278.032</v>
       </c>
       <c r="G17">
         <v>240.2</v>
@@ -2687,28 +2687,28 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M17">
-        <v>18.5406450097942</v>
+        <v>19.77668801044715</v>
       </c>
       <c r="N17">
-        <v>77.41527335755273</v>
+        <v>76.17923035689979</v>
       </c>
       <c r="O17">
-        <v>19.35381833938818</v>
+        <v>19.04480758922495</v>
       </c>
       <c r="P17">
-        <v>58.06145501816455</v>
+        <v>57.13442276767485</v>
       </c>
       <c r="Q17">
-        <v>66.90145501816455</v>
+        <v>65.97442276767485</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1164640313594226</v>
+        <v>0.117119541854408</v>
       </c>
       <c r="T17">
-        <v>1.093150091275257</v>
+        <v>1.103290630155361</v>
       </c>
       <c r="U17">
         <v>0.07113097776675759</v>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>5.175435823114983</v>
+        <v>4.851971084170296</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2733,22 +2733,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1069161324897136</v>
+        <v>0.1068356033251578</v>
       </c>
       <c r="C18">
-        <v>1518.066663013456</v>
+        <v>1502.742484852513</v>
       </c>
       <c r="D18">
-        <v>1555.898663013455</v>
+        <v>1557.951484852513</v>
       </c>
       <c r="E18">
-        <v>-154.6679999999999</v>
+        <v>-137.2909999999999</v>
       </c>
       <c r="F18">
-        <v>278.032</v>
+        <v>295.409</v>
       </c>
       <c r="G18">
         <v>240.2</v>
@@ -2769,28 +2769,28 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M18">
-        <v>19.77668801044715</v>
+        <v>21.01273101110009</v>
       </c>
       <c r="N18">
-        <v>76.17923035689979</v>
+        <v>74.94318735624685</v>
       </c>
       <c r="O18">
-        <v>19.04480758922495</v>
+        <v>18.73579683906171</v>
       </c>
       <c r="P18">
-        <v>57.13442276767485</v>
+        <v>56.20739051718514</v>
       </c>
       <c r="Q18">
-        <v>65.97442276767485</v>
+        <v>65.04739051718514</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.117119541854408</v>
+        <v>0.1177908477830075</v>
       </c>
       <c r="T18">
-        <v>1.103290630155361</v>
+        <v>1.113675519369926</v>
       </c>
       <c r="U18">
         <v>0.07113097776675759</v>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>4.851971084170296</v>
+        <v>4.566561020395573</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2815,22 +2815,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1068356033251578</v>
+        <v>0.107092574160602</v>
       </c>
       <c r="C19">
-        <v>1502.742484852513</v>
+        <v>1478.833729576663</v>
       </c>
       <c r="D19">
-        <v>1557.951484852513</v>
+        <v>1551.419729576663</v>
       </c>
       <c r="E19">
-        <v>-137.2909999999999</v>
+        <v>-119.9139999999999</v>
       </c>
       <c r="F19">
-        <v>295.409</v>
+        <v>312.7860000000001</v>
       </c>
       <c r="G19">
         <v>240.2</v>
@@ -2851,45 +2851,45 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M19">
-        <v>21.01273101110009</v>
+        <v>23.03073901175304</v>
       </c>
       <c r="N19">
-        <v>74.94318735624685</v>
+        <v>72.9251793555939</v>
       </c>
       <c r="O19">
-        <v>18.73579683906171</v>
+        <v>18.23129483889847</v>
       </c>
       <c r="P19">
-        <v>56.20739051718514</v>
+        <v>54.69388451669542</v>
       </c>
       <c r="Q19">
-        <v>65.04739051718514</v>
+        <v>63.53388451669542</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1177908477830075</v>
+        <v>0.1184785270269386</v>
       </c>
       <c r="T19">
-        <v>1.113675519369926</v>
+        <v>1.124313698565334</v>
       </c>
       <c r="U19">
-        <v>0.07113097776675759</v>
+        <v>0.07363097776675759</v>
       </c>
       <c r="V19">
         <v>0.25</v>
       </c>
       <c r="W19">
-        <v>0.05334823332506819</v>
+        <v>0.05522323332506819</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y19">
-        <v>4.566561020395573</v>
+        <v>4.166428108033299</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2897,22 +2897,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.107092574160602</v>
+        <v>0.1075295449960462</v>
       </c>
       <c r="C20">
-        <v>1478.833729576663</v>
+        <v>1450.474546322256</v>
       </c>
       <c r="D20">
-        <v>1551.419729576663</v>
+        <v>1540.437546322256</v>
       </c>
       <c r="E20">
-        <v>-119.914</v>
+        <v>-102.537</v>
       </c>
       <c r="F20">
-        <v>312.786</v>
+        <v>330.163</v>
       </c>
       <c r="G20">
         <v>240.2</v>
@@ -2933,45 +2933,45 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M20">
-        <v>23.03073901175304</v>
+        <v>25.46579501240599</v>
       </c>
       <c r="N20">
-        <v>72.9251793555939</v>
+        <v>70.49012335494095</v>
       </c>
       <c r="O20">
-        <v>18.23129483889847</v>
+        <v>17.62253083873524</v>
       </c>
       <c r="P20">
-        <v>54.69388451669542</v>
+        <v>52.86759251620571</v>
       </c>
       <c r="Q20">
-        <v>63.53388451669542</v>
+        <v>61.70759251620571</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1184785270269386</v>
+        <v>0.1191831860052879</v>
       </c>
       <c r="T20">
-        <v>1.124313698565334</v>
+        <v>1.135214548851987</v>
       </c>
       <c r="U20">
-        <v>0.07363097776675759</v>
+        <v>0.07713097776675759</v>
       </c>
       <c r="V20">
         <v>0.25</v>
       </c>
       <c r="W20">
-        <v>0.05522323332506819</v>
+        <v>0.05784823332506819</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y20">
-        <v>4.1664281080333</v>
+        <v>3.768031523092084</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2979,22 +2979,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1075295449960462</v>
+        <v>0.1074940158314903</v>
       </c>
       <c r="C21">
-        <v>1450.474546322256</v>
+        <v>1433.984673839142</v>
       </c>
       <c r="D21">
-        <v>1540.437546322256</v>
+        <v>1541.324673839141</v>
       </c>
       <c r="E21">
-        <v>-102.537</v>
+        <v>-85.15999999999997</v>
       </c>
       <c r="F21">
-        <v>330.163</v>
+        <v>347.54</v>
       </c>
       <c r="G21">
         <v>240.2</v>
@@ -3015,28 +3015,28 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M21">
-        <v>25.46579501240599</v>
+        <v>26.80610001305893</v>
       </c>
       <c r="N21">
-        <v>70.49012335494095</v>
+        <v>69.149818354288</v>
       </c>
       <c r="O21">
-        <v>17.62253083873524</v>
+        <v>17.287454588572</v>
       </c>
       <c r="P21">
-        <v>52.86759251620571</v>
+        <v>51.862363765716</v>
       </c>
       <c r="Q21">
-        <v>61.70759251620571</v>
+        <v>60.702363765716</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1191831860052879</v>
+        <v>0.1199054614580958</v>
       </c>
       <c r="T21">
-        <v>1.135214548851987</v>
+        <v>1.146387920395805</v>
       </c>
       <c r="U21">
         <v>0.07713097776675759</v>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>3.768031523092084</v>
+        <v>3.57962994693748</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3061,22 +3061,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1074940158314903</v>
+        <v>0.1078994866669345</v>
       </c>
       <c r="C22">
-        <v>1433.984673839142</v>
+        <v>1406.543787054631</v>
       </c>
       <c r="D22">
-        <v>1541.324673839141</v>
+        <v>1531.260787054631</v>
       </c>
       <c r="E22">
-        <v>-85.15999999999997</v>
+        <v>-67.78299999999996</v>
       </c>
       <c r="F22">
-        <v>347.54</v>
+        <v>364.917</v>
       </c>
       <c r="G22">
         <v>240.2</v>
@@ -3097,45 +3097,45 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M22">
-        <v>26.80610001305893</v>
+        <v>29.16817261371188</v>
       </c>
       <c r="N22">
-        <v>69.149818354288</v>
+        <v>66.78774575363505</v>
       </c>
       <c r="O22">
-        <v>17.287454588572</v>
+        <v>16.69693643840876</v>
       </c>
       <c r="P22">
-        <v>51.862363765716</v>
+        <v>50.09080931522629</v>
       </c>
       <c r="Q22">
-        <v>60.702363765716</v>
+        <v>58.93080931522628</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1199054614580958</v>
+        <v>0.1206460223654053</v>
       </c>
       <c r="T22">
-        <v>1.146387920395805</v>
+        <v>1.15784416210529</v>
       </c>
       <c r="U22">
-        <v>0.07713097776675759</v>
+        <v>0.07993097776675759</v>
       </c>
       <c r="V22">
         <v>0.25</v>
       </c>
       <c r="W22">
-        <v>0.05784823332506819</v>
+        <v>0.05994823332506819</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y22">
-        <v>3.57962994693748</v>
+        <v>3.289747343384765</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3143,22 +3143,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1078994866669345</v>
+        <v>0.1078849575023786</v>
       </c>
       <c r="C23">
-        <v>1406.543787054631</v>
+        <v>1389.525133759663</v>
       </c>
       <c r="D23">
-        <v>1531.260787054631</v>
+        <v>1531.619133759663</v>
       </c>
       <c r="E23">
-        <v>-67.78300000000002</v>
+        <v>-50.40599999999995</v>
       </c>
       <c r="F23">
-        <v>364.917</v>
+        <v>382.294</v>
       </c>
       <c r="G23">
         <v>240.2</v>
@@ -3179,28 +3179,28 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M23">
-        <v>29.16817261371188</v>
+        <v>30.55713321436483</v>
       </c>
       <c r="N23">
-        <v>66.78774575363506</v>
+        <v>65.39878515298211</v>
       </c>
       <c r="O23">
-        <v>16.69693643840877</v>
+        <v>16.34969628824553</v>
       </c>
       <c r="P23">
-        <v>50.09080931522629</v>
+        <v>49.04908886473659</v>
       </c>
       <c r="Q23">
-        <v>58.9308093152263</v>
+        <v>57.88908886473659</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1206460223654053</v>
+        <v>0.1214055720139277</v>
       </c>
       <c r="T23">
-        <v>1.15784416210529</v>
+        <v>1.169594153602198</v>
       </c>
       <c r="U23">
         <v>0.07993097776675759</v>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>3.289747343384766</v>
+        <v>3.140213373230913</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1078849575023786</v>
+        <v>0.1078704283378228</v>
       </c>
       <c r="C24">
-        <v>1389.525133759663</v>
+        <v>1372.50664822504</v>
       </c>
       <c r="D24">
-        <v>1531.619133759663</v>
+        <v>1531.97764822504</v>
       </c>
       <c r="E24">
-        <v>-50.40599999999995</v>
+        <v>-33.02899999999994</v>
       </c>
       <c r="F24">
-        <v>382.294</v>
+        <v>399.671</v>
       </c>
       <c r="G24">
         <v>240.2</v>
@@ -3261,28 +3261,28 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M24">
-        <v>30.55713321436483</v>
+        <v>31.94609381501778</v>
       </c>
       <c r="N24">
-        <v>65.39878515298211</v>
+        <v>64.00982455232916</v>
       </c>
       <c r="O24">
-        <v>16.34969628824553</v>
+        <v>16.00245613808229</v>
       </c>
       <c r="P24">
-        <v>49.04908886473659</v>
+        <v>48.00736841424687</v>
       </c>
       <c r="Q24">
-        <v>57.88908886473659</v>
+        <v>56.84736841424687</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1214055720139277</v>
+        <v>0.1221848502247495</v>
       </c>
       <c r="T24">
-        <v>1.169594153602198</v>
+        <v>1.181649339683441</v>
       </c>
       <c r="U24">
         <v>0.07993097776675759</v>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>3.140213373230913</v>
+        <v>3.003682357003482</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3307,22 +3307,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1078704283378228</v>
+        <v>0.109259899173267</v>
       </c>
       <c r="C25">
-        <v>1372.50664822504</v>
+        <v>1321.586603081694</v>
       </c>
       <c r="D25">
-        <v>1531.97764822504</v>
+        <v>1498.434603081694</v>
       </c>
       <c r="E25">
-        <v>-33.02899999999994</v>
+        <v>-15.65199999999993</v>
       </c>
       <c r="F25">
-        <v>399.671</v>
+        <v>417.0480000000001</v>
       </c>
       <c r="G25">
         <v>240.2</v>
@@ -3343,45 +3343,45 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M25">
-        <v>31.94609381501778</v>
+        <v>36.58802881567073</v>
       </c>
       <c r="N25">
-        <v>64.00982455232916</v>
+        <v>59.36788955167621</v>
       </c>
       <c r="O25">
-        <v>16.00245613808229</v>
+        <v>14.84197238791905</v>
       </c>
       <c r="P25">
-        <v>48.00736841424687</v>
+        <v>44.52591716375716</v>
       </c>
       <c r="Q25">
-        <v>56.84736841424687</v>
+        <v>53.36591716375716</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1221848502247495</v>
+        <v>0.1229846357569087</v>
       </c>
       <c r="T25">
-        <v>1.181649339683441</v>
+        <v>1.194021767503664</v>
       </c>
       <c r="U25">
-        <v>0.07993097776675759</v>
+        <v>0.08773097776675759</v>
       </c>
       <c r="V25">
         <v>0.25</v>
       </c>
       <c r="W25">
-        <v>0.05994823332506819</v>
+        <v>0.06579823332506819</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y25">
-        <v>3.003682357003482</v>
+        <v>2.622604208900394</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3389,22 +3389,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.109259899173267</v>
+        <v>0.1093038700087111</v>
       </c>
       <c r="C26">
-        <v>1321.586603081694</v>
+        <v>1303.172069127514</v>
       </c>
       <c r="D26">
-        <v>1498.434603081694</v>
+        <v>1497.397069127514</v>
       </c>
       <c r="E26">
-        <v>-15.65199999999999</v>
+        <v>1.725000000000023</v>
       </c>
       <c r="F26">
-        <v>417.048</v>
+        <v>434.425</v>
       </c>
       <c r="G26">
         <v>240.2</v>
@@ -3425,28 +3425,28 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M26">
-        <v>36.58802881567072</v>
+        <v>38.11253001632367</v>
       </c>
       <c r="N26">
-        <v>59.36788955167622</v>
+        <v>57.84338835102327</v>
       </c>
       <c r="O26">
-        <v>14.84197238791906</v>
+        <v>14.46084708775582</v>
       </c>
       <c r="P26">
-        <v>44.52591716375716</v>
+        <v>43.38254126326746</v>
       </c>
       <c r="Q26">
-        <v>53.36591716375716</v>
+        <v>52.22254126326746</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1229846357569087</v>
+        <v>0.1238057489032588</v>
       </c>
       <c r="T26">
-        <v>1.194021767503664</v>
+        <v>1.206724126732427</v>
       </c>
       <c r="U26">
         <v>0.08773097776675759</v>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>2.622604208900395</v>
+        <v>2.517700040544379</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3471,22 +3471,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1093038700087111</v>
+        <v>0.1101083408441553</v>
       </c>
       <c r="C27">
-        <v>1303.172069127514</v>
+        <v>1267.063249034193</v>
       </c>
       <c r="D27">
-        <v>1497.397069127514</v>
+        <v>1478.665249034193</v>
       </c>
       <c r="E27">
-        <v>1.725000000000023</v>
+        <v>19.10200000000003</v>
       </c>
       <c r="F27">
-        <v>434.425</v>
+        <v>451.802</v>
       </c>
       <c r="G27">
         <v>240.2</v>
@@ -3507,45 +3507,45 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M27">
-        <v>38.11253001632367</v>
+        <v>41.39905901697662</v>
       </c>
       <c r="N27">
-        <v>57.84338835102327</v>
+        <v>54.55685935037032</v>
       </c>
       <c r="O27">
-        <v>14.46084708775582</v>
+        <v>13.63921483759258</v>
       </c>
       <c r="P27">
-        <v>43.38254126326746</v>
+        <v>40.91764451277774</v>
       </c>
       <c r="Q27">
-        <v>52.22254126326746</v>
+        <v>49.75764451277774</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1238057489032588</v>
+        <v>0.1246490542968075</v>
       </c>
       <c r="T27">
-        <v>1.206724126732427</v>
+        <v>1.219769792967372</v>
       </c>
       <c r="U27">
-        <v>0.08773097776675759</v>
+        <v>0.09163097776675759</v>
       </c>
       <c r="V27">
         <v>0.25</v>
       </c>
       <c r="W27">
-        <v>0.06579823332506819</v>
+        <v>0.06872323332506819</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y27">
-        <v>2.517700040544379</v>
+        <v>2.317828488033944</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3553,22 +3553,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1101083408441553</v>
+        <v>0.1101815616795995</v>
       </c>
       <c r="C28">
-        <v>1267.063249034193</v>
+        <v>1248.004570273194</v>
       </c>
       <c r="D28">
-        <v>1478.665249034193</v>
+        <v>1476.983570273194</v>
       </c>
       <c r="E28">
-        <v>19.10200000000003</v>
+        <v>36.47900000000004</v>
       </c>
       <c r="F28">
-        <v>451.802</v>
+        <v>469.179</v>
       </c>
       <c r="G28">
         <v>240.2</v>
@@ -3589,28 +3589,28 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M28">
-        <v>41.39905901697662</v>
+        <v>42.99133051762956</v>
       </c>
       <c r="N28">
-        <v>54.55685935037032</v>
+        <v>52.96458784971738</v>
       </c>
       <c r="O28">
-        <v>13.63921483759258</v>
+        <v>13.24114696242934</v>
       </c>
       <c r="P28">
-        <v>40.91764451277774</v>
+        <v>39.72344088728804</v>
       </c>
       <c r="Q28">
-        <v>49.75764451277774</v>
+        <v>48.56344088728804</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1246490542968075</v>
+        <v>0.1255154639477138</v>
       </c>
       <c r="T28">
-        <v>1.219769792967372</v>
+        <v>1.233172874715603</v>
       </c>
       <c r="U28">
         <v>0.09163097776675759</v>
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>2.317828488033944</v>
+        <v>2.231982988477132</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3635,22 +3635,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1101815616795995</v>
+        <v>0.1102547825150436</v>
       </c>
       <c r="C29">
-        <v>1248.004570273194</v>
+        <v>1228.949712296907</v>
       </c>
       <c r="D29">
-        <v>1476.983570273194</v>
+        <v>1475.305712296907</v>
       </c>
       <c r="E29">
-        <v>36.47900000000004</v>
+        <v>53.85600000000005</v>
       </c>
       <c r="F29">
-        <v>469.179</v>
+        <v>486.556</v>
       </c>
       <c r="G29">
         <v>240.2</v>
@@ -3671,28 +3671,28 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M29">
-        <v>42.99133051762956</v>
+        <v>44.58360201828251</v>
       </c>
       <c r="N29">
-        <v>52.96458784971738</v>
+        <v>51.37231634906443</v>
       </c>
       <c r="O29">
-        <v>13.24114696242934</v>
+        <v>12.84307908726611</v>
       </c>
       <c r="P29">
-        <v>39.72344088728804</v>
+        <v>38.52923726179832</v>
       </c>
       <c r="Q29">
-        <v>48.56344088728804</v>
+        <v>47.36923726179832</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1255154639477138</v>
+        <v>0.1264059405333674</v>
       </c>
       <c r="T29">
-        <v>1.233172874715603</v>
+        <v>1.246948264290174</v>
       </c>
       <c r="U29">
         <v>0.09163097776675759</v>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>2.231982988477132</v>
+        <v>2.152269310317234</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3717,22 +3717,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1102547825150436</v>
+        <v>0.1103280033504878</v>
       </c>
       <c r="C30">
-        <v>1228.949712296907</v>
+        <v>1209.898662098837</v>
       </c>
       <c r="D30">
-        <v>1475.305712296907</v>
+        <v>1473.631662098837</v>
       </c>
       <c r="E30">
-        <v>53.85600000000005</v>
+        <v>71.23300000000006</v>
       </c>
       <c r="F30">
-        <v>486.556</v>
+        <v>503.933</v>
       </c>
       <c r="G30">
         <v>240.2</v>
@@ -3753,28 +3753,28 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M30">
-        <v>44.58360201828251</v>
+        <v>46.17587351893545</v>
       </c>
       <c r="N30">
-        <v>51.37231634906443</v>
+        <v>49.78004484841149</v>
       </c>
       <c r="O30">
-        <v>12.84307908726611</v>
+        <v>12.44501121210287</v>
       </c>
       <c r="P30">
-        <v>38.52923726179832</v>
+        <v>37.33503363630862</v>
       </c>
       <c r="Q30">
-        <v>47.36923726179832</v>
+        <v>46.17503363630861</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1264059405333674</v>
+        <v>0.1273215009665042</v>
       </c>
       <c r="T30">
-        <v>1.246948264290174</v>
+        <v>1.261111693007691</v>
       </c>
       <c r="U30">
         <v>0.09163097776675759</v>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>2.152269310317234</v>
+        <v>2.078053127202847</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3799,22 +3799,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1103280033504878</v>
+        <v>0.1104012241859319</v>
       </c>
       <c r="C31">
-        <v>1209.898662098838</v>
+        <v>1190.851406731458</v>
       </c>
       <c r="D31">
-        <v>1473.631662098838</v>
+        <v>1471.961406731458</v>
       </c>
       <c r="E31">
-        <v>71.233</v>
+        <v>88.60999999999996</v>
       </c>
       <c r="F31">
-        <v>503.933</v>
+        <v>521.3099999999999</v>
       </c>
       <c r="G31">
         <v>240.2</v>
@@ -3835,28 +3835,28 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M31">
-        <v>46.17587351893545</v>
+        <v>47.7681450195884</v>
       </c>
       <c r="N31">
-        <v>49.78004484841149</v>
+        <v>48.18777334775854</v>
       </c>
       <c r="O31">
-        <v>12.44501121210287</v>
+        <v>12.04694333693964</v>
       </c>
       <c r="P31">
-        <v>37.33503363630862</v>
+        <v>36.14083001081891</v>
       </c>
       <c r="Q31">
-        <v>46.17503363630861</v>
+        <v>44.98083001081891</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1273215009665042</v>
+        <v>0.1282632202691593</v>
       </c>
       <c r="T31">
-        <v>1.261111693007691</v>
+        <v>1.275679791117137</v>
       </c>
       <c r="U31">
         <v>0.09163097776675759</v>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>2.078053127202847</v>
+        <v>2.008784689629419</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3881,22 +3881,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1104012241859319</v>
+        <v>0.1137759450213761</v>
       </c>
       <c r="C32">
-        <v>1190.851406731458</v>
+        <v>1100.397690744586</v>
       </c>
       <c r="D32">
-        <v>1471.961406731458</v>
+        <v>1398.884690744586</v>
       </c>
       <c r="E32">
-        <v>88.60999999999996</v>
+        <v>105.987</v>
       </c>
       <c r="F32">
-        <v>521.3099999999999</v>
+        <v>538.687</v>
       </c>
       <c r="G32">
         <v>240.2</v>
@@ -3917,45 +3917,45 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M32">
-        <v>47.7681450195884</v>
+        <v>57.00977192024135</v>
       </c>
       <c r="N32">
-        <v>48.18777334775854</v>
+        <v>38.94614644710559</v>
       </c>
       <c r="O32">
-        <v>12.04694333693964</v>
+        <v>9.736536611776398</v>
       </c>
       <c r="P32">
-        <v>36.14083001081891</v>
+        <v>29.20960983532919</v>
       </c>
       <c r="Q32">
-        <v>44.98083001081891</v>
+        <v>38.04960983532919</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1282632202691593</v>
+        <v>0.1292322357834854</v>
       </c>
       <c r="T32">
-        <v>1.275679791117137</v>
+        <v>1.2906701529399</v>
       </c>
       <c r="U32">
-        <v>0.09163097776675759</v>
+        <v>0.1058309777667576</v>
       </c>
       <c r="V32">
         <v>0.25</v>
       </c>
       <c r="W32">
-        <v>0.06872323332506819</v>
+        <v>0.0793732333250682</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y32">
-        <v>2.008784689629419</v>
+        <v>1.683148610059212</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3963,22 +3963,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1137759450213761</v>
+        <v>0.1139556658568203</v>
       </c>
       <c r="C33">
-        <v>1100.397690744586</v>
+        <v>1079.331947891734</v>
       </c>
       <c r="D33">
-        <v>1398.884690744586</v>
+        <v>1395.195947891734</v>
       </c>
       <c r="E33">
-        <v>105.987</v>
+        <v>123.3640000000001</v>
       </c>
       <c r="F33">
-        <v>538.687</v>
+        <v>556.0640000000001</v>
       </c>
       <c r="G33">
         <v>240.2</v>
@@ -3999,28 +3999,28 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M33">
-        <v>57.00977192024135</v>
+        <v>58.8487968208943</v>
       </c>
       <c r="N33">
-        <v>38.94614644710559</v>
+        <v>37.10712154645264</v>
       </c>
       <c r="O33">
-        <v>9.736536611776398</v>
+        <v>9.27678038661316</v>
       </c>
       <c r="P33">
-        <v>29.20960983532919</v>
+        <v>27.83034115983948</v>
       </c>
       <c r="Q33">
-        <v>38.04960983532919</v>
+        <v>36.67034115983948</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1292322357834854</v>
+        <v>0.1302297517541154</v>
       </c>
       <c r="T33">
-        <v>1.2906701529399</v>
+        <v>1.30610140775745</v>
       </c>
       <c r="U33">
         <v>0.1058309777667576</v>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>1.683148610059212</v>
+        <v>1.630550215994862</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4045,22 +4045,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1139556658568203</v>
+        <v>0.1141353866922644</v>
       </c>
       <c r="C34">
-        <v>1079.331947891734</v>
+        <v>1058.28560769333</v>
       </c>
       <c r="D34">
-        <v>1395.195947891734</v>
+        <v>1391.52660769333</v>
       </c>
       <c r="E34">
-        <v>123.3640000000001</v>
+        <v>140.741</v>
       </c>
       <c r="F34">
-        <v>556.0640000000001</v>
+        <v>573.441</v>
       </c>
       <c r="G34">
         <v>240.2</v>
@@ -4081,28 +4081,28 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M34">
-        <v>58.8487968208943</v>
+        <v>60.68782172154724</v>
       </c>
       <c r="N34">
-        <v>37.10712154645264</v>
+        <v>35.26809664579969</v>
       </c>
       <c r="O34">
-        <v>9.27678038661316</v>
+        <v>8.817024161449924</v>
       </c>
       <c r="P34">
-        <v>27.83034115983948</v>
+        <v>26.45107248434977</v>
       </c>
       <c r="Q34">
-        <v>36.67034115983948</v>
+        <v>35.29107248434977</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1302297517541154</v>
+        <v>0.1312570443208835</v>
       </c>
       <c r="T34">
-        <v>1.30610140775745</v>
+        <v>1.321993297047166</v>
       </c>
       <c r="U34">
         <v>0.1058309777667576</v>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>1.630550215994862</v>
+        <v>1.581139603388957</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4127,22 +4127,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1141353866922644</v>
+        <v>0.1143151075277086</v>
       </c>
       <c r="C35">
-        <v>1058.28560769333</v>
+        <v>1037.258517465035</v>
       </c>
       <c r="D35">
-        <v>1391.52660769333</v>
+        <v>1387.876517465035</v>
       </c>
       <c r="E35">
-        <v>140.741</v>
+        <v>158.1180000000001</v>
       </c>
       <c r="F35">
-        <v>573.441</v>
+        <v>590.8180000000001</v>
       </c>
       <c r="G35">
         <v>240.2</v>
@@ -4163,28 +4163,28 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M35">
-        <v>60.68782172154724</v>
+        <v>62.5268466222002</v>
       </c>
       <c r="N35">
-        <v>35.26809664579969</v>
+        <v>33.42907174514674</v>
       </c>
       <c r="O35">
-        <v>8.817024161449924</v>
+        <v>8.357267936286686</v>
       </c>
       <c r="P35">
-        <v>26.45107248434977</v>
+        <v>25.07180380886006</v>
       </c>
       <c r="Q35">
-        <v>35.29107248434977</v>
+        <v>33.91180380886006</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1312570443208835</v>
+        <v>0.1323154669654324</v>
       </c>
       <c r="T35">
-        <v>1.321993297047166</v>
+        <v>1.338366758739601</v>
       </c>
       <c r="U35">
         <v>0.1058309777667576</v>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>1.581139603388957</v>
+        <v>1.534635497406929</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4209,22 +4209,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1143151075277086</v>
+        <v>0.1299931755360693</v>
       </c>
       <c r="C36">
-        <v>1037.258517465035</v>
+        <v>761.4375011955486</v>
       </c>
       <c r="D36">
-        <v>1387.876517465035</v>
+        <v>1129.432501195549</v>
       </c>
       <c r="E36">
-        <v>158.1180000000001</v>
+        <v>175.4950000000001</v>
       </c>
       <c r="F36">
-        <v>590.8180000000001</v>
+        <v>608.1950000000001</v>
       </c>
       <c r="G36">
         <v>240.2</v>
@@ -4245,45 +4245,45 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M36">
-        <v>62.5268466222002</v>
+        <v>98.91134752285315</v>
       </c>
       <c r="N36">
-        <v>33.42907174514674</v>
+        <v>-2.955429155506209</v>
       </c>
       <c r="O36">
-        <v>8.357267936286686</v>
+        <v>-0.7388572888765523</v>
       </c>
       <c r="P36">
-        <v>25.07180380886006</v>
+        <v>-2.216571866629657</v>
       </c>
       <c r="Q36">
-        <v>33.91180380886006</v>
+        <v>6.623428133370343</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1323154669654324</v>
+        <v>0.133657463400349</v>
       </c>
       <c r="T36">
-        <v>1.338366758739601</v>
+        <v>1.35912701678175</v>
       </c>
       <c r="U36">
-        <v>0.1058309777667576</v>
+        <v>0.1626309777667576</v>
       </c>
       <c r="V36">
-        <v>0.25</v>
+        <v>0.2425301059243395</v>
       </c>
       <c r="W36">
-        <v>0.0793732333250682</v>
+        <v>0.123188069502407</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y36">
-        <v>1.534635497406929</v>
+        <v>0.9701204236973582</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1299931755360693</v>
+        <v>0.1311614853137369</v>
       </c>
       <c r="C37">
-        <v>761.4375011955486</v>
+        <v>728.6023934844125</v>
       </c>
       <c r="D37">
-        <v>1129.432501195549</v>
+        <v>1113.974393484413</v>
       </c>
       <c r="E37">
-        <v>175.4950000000001</v>
+        <v>192.8720000000001</v>
       </c>
       <c r="F37">
-        <v>608.1950000000001</v>
+        <v>625.5720000000001</v>
       </c>
       <c r="G37">
         <v>240.2</v>
@@ -4327,37 +4327,37 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M37">
-        <v>98.91134752285315</v>
+        <v>101.7373860235061</v>
       </c>
       <c r="N37">
-        <v>-2.955429155506209</v>
+        <v>-5.78146765615918</v>
       </c>
       <c r="O37">
-        <v>-0.7388572888765523</v>
+        <v>-1.445366914039795</v>
       </c>
       <c r="P37">
-        <v>-2.216571866629657</v>
+        <v>-4.336100742119385</v>
       </c>
       <c r="Q37">
-        <v>6.623428133370343</v>
+        <v>4.503899257880615</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.133657463400349</v>
+        <v>0.1350302362659795</v>
       </c>
       <c r="T37">
-        <v>1.35912701678175</v>
+        <v>1.380363376418964</v>
       </c>
       <c r="U37">
         <v>0.1626309777667576</v>
       </c>
       <c r="V37">
-        <v>0.2425301059243395</v>
+        <v>0.2357931585375523</v>
       </c>
       <c r="W37">
-        <v>0.123188069502407</v>
+        <v>0.1242837058430834</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.9701204236973582</v>
+        <v>0.9431726341502091</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4373,22 +4373,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1311614853137369</v>
+        <v>0.1323297950914045</v>
       </c>
       <c r="C38">
-        <v>728.6023934844126</v>
+        <v>696.1847109703216</v>
       </c>
       <c r="D38">
-        <v>1113.974393484413</v>
+        <v>1098.933710970321</v>
       </c>
       <c r="E38">
-        <v>192.872</v>
+        <v>210.249</v>
       </c>
       <c r="F38">
-        <v>625.572</v>
+        <v>642.949</v>
       </c>
       <c r="G38">
         <v>240.2</v>
@@ -4409,37 +4409,37 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M38">
-        <v>101.7373860235061</v>
+        <v>104.563424524159</v>
       </c>
       <c r="N38">
-        <v>-5.781467656159151</v>
+        <v>-8.607506156812093</v>
       </c>
       <c r="O38">
-        <v>-1.445366914039788</v>
+        <v>-2.151876539203023</v>
       </c>
       <c r="P38">
-        <v>-4.336100742119363</v>
+        <v>-6.45562961760907</v>
       </c>
       <c r="Q38">
-        <v>4.503899257880636</v>
+        <v>2.38437038239093</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1350302362659795</v>
+        <v>0.1364465892225823</v>
       </c>
       <c r="T38">
-        <v>1.380363376418964</v>
+        <v>1.402273906203392</v>
       </c>
       <c r="U38">
         <v>0.1626309777667576</v>
       </c>
       <c r="V38">
-        <v>0.2357931585375524</v>
+        <v>0.2294203704689699</v>
       </c>
       <c r="W38">
-        <v>0.1242837058430834</v>
+        <v>0.1253201185977773</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.9431726341502095</v>
+        <v>0.9176814818758795</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4455,22 +4455,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1323297950914045</v>
+        <v>0.133498104869072</v>
       </c>
       <c r="C39">
-        <v>696.1847109703216</v>
+        <v>664.1677709003293</v>
       </c>
       <c r="D39">
-        <v>1098.933710970321</v>
+        <v>1084.293770900329</v>
       </c>
       <c r="E39">
-        <v>210.249</v>
+        <v>227.626</v>
       </c>
       <c r="F39">
-        <v>642.949</v>
+        <v>660.326</v>
       </c>
       <c r="G39">
         <v>240.2</v>
@@ -4491,37 +4491,37 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M39">
-        <v>104.563424524159</v>
+        <v>107.389463024812</v>
       </c>
       <c r="N39">
-        <v>-8.607506156812093</v>
+        <v>-11.43354465746505</v>
       </c>
       <c r="O39">
-        <v>-2.151876539203023</v>
+        <v>-2.858386164366262</v>
       </c>
       <c r="P39">
-        <v>-6.45562961760907</v>
+        <v>-8.575158493098787</v>
       </c>
       <c r="Q39">
-        <v>2.38437038239093</v>
+        <v>0.2648415069012131</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1364465892225823</v>
+        <v>0.1379086309842369</v>
       </c>
       <c r="T39">
-        <v>1.402273906203392</v>
+        <v>1.424891227271189</v>
       </c>
       <c r="U39">
         <v>0.1626309777667576</v>
       </c>
       <c r="V39">
-        <v>0.2294203704689699</v>
+        <v>0.2233829922987338</v>
       </c>
       <c r="W39">
-        <v>0.1253201185977773</v>
+        <v>0.1263019833127504</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.9176814818758795</v>
+        <v>0.8935319691949353</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4537,22 +4537,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.133498104869072</v>
+        <v>0.1346664146467396</v>
       </c>
       <c r="C40">
-        <v>664.1677709003293</v>
+        <v>632.5357678213524</v>
       </c>
       <c r="D40">
-        <v>1084.293770900329</v>
+        <v>1070.038767821352</v>
       </c>
       <c r="E40">
-        <v>227.626</v>
+        <v>245.0030000000001</v>
       </c>
       <c r="F40">
-        <v>660.326</v>
+        <v>677.7030000000001</v>
       </c>
       <c r="G40">
         <v>240.2</v>
@@ -4573,37 +4573,37 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M40">
-        <v>107.389463024812</v>
+        <v>110.2155015254649</v>
       </c>
       <c r="N40">
-        <v>-11.43354465746505</v>
+        <v>-14.25958315811801</v>
       </c>
       <c r="O40">
-        <v>-2.858386164366262</v>
+        <v>-3.564895789529501</v>
       </c>
       <c r="P40">
-        <v>-8.575158493098787</v>
+        <v>-10.6946873685885</v>
       </c>
       <c r="Q40">
-        <v>0.2648415069012131</v>
+        <v>-1.854687368588504</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1379086309842369</v>
+        <v>0.1394186085413555</v>
       </c>
       <c r="T40">
-        <v>1.424891227271189</v>
+        <v>1.448250099849405</v>
       </c>
       <c r="U40">
         <v>0.1626309777667576</v>
       </c>
       <c r="V40">
-        <v>0.2233829922987338</v>
+        <v>0.2176552232654329</v>
       </c>
       <c r="W40">
-        <v>0.1263019833127504</v>
+        <v>0.1272334959910583</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.8935319691949353</v>
+        <v>0.8706208930617316</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4619,22 +4619,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1346664146467396</v>
+        <v>0.1358347244244072</v>
       </c>
       <c r="C41">
-        <v>632.5357678213524</v>
+        <v>601.2737166600233</v>
       </c>
       <c r="D41">
-        <v>1070.038767821352</v>
+        <v>1056.153716660023</v>
       </c>
       <c r="E41">
-        <v>245.0030000000001</v>
+        <v>262.3800000000001</v>
       </c>
       <c r="F41">
-        <v>677.7030000000001</v>
+        <v>695.08</v>
       </c>
       <c r="G41">
         <v>240.2</v>
@@ -4655,37 +4655,37 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M41">
-        <v>110.2155015254649</v>
+        <v>113.0415400261179</v>
       </c>
       <c r="N41">
-        <v>-14.25958315811801</v>
+        <v>-17.08562165877095</v>
       </c>
       <c r="O41">
-        <v>-3.564895789529501</v>
+        <v>-4.271405414692737</v>
       </c>
       <c r="P41">
-        <v>-10.6946873685885</v>
+        <v>-12.81421624407821</v>
       </c>
       <c r="Q41">
-        <v>-1.854687368588504</v>
+        <v>-3.97421624407821</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1394186085413555</v>
+        <v>0.1409789186837115</v>
       </c>
       <c r="T41">
-        <v>1.448250099849405</v>
+        <v>1.472387601513562</v>
       </c>
       <c r="U41">
         <v>0.1626309777667576</v>
       </c>
       <c r="V41">
-        <v>0.2176552232654329</v>
+        <v>0.2122138426837971</v>
       </c>
       <c r="W41">
-        <v>0.1272334959910583</v>
+        <v>0.1281184330354508</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.8706208930617316</v>
+        <v>0.8488553707351885</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4701,22 +4701,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1358347244244072</v>
+        <v>0.1370030342020748</v>
       </c>
       <c r="C42">
-        <v>601.2737166600233</v>
+        <v>570.3674001774168</v>
       </c>
       <c r="D42">
-        <v>1056.153716660023</v>
+        <v>1042.624400177417</v>
       </c>
       <c r="E42">
-        <v>262.3800000000001</v>
+        <v>279.7570000000001</v>
       </c>
       <c r="F42">
-        <v>695.08</v>
+        <v>712.4570000000001</v>
       </c>
       <c r="G42">
         <v>240.2</v>
@@ -4737,37 +4737,37 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M42">
-        <v>113.0415400261179</v>
+        <v>115.8675785267708</v>
       </c>
       <c r="N42">
-        <v>-17.08562165877095</v>
+        <v>-19.9116601594239</v>
       </c>
       <c r="O42">
-        <v>-4.271405414692737</v>
+        <v>-4.977915039855976</v>
       </c>
       <c r="P42">
-        <v>-12.81421624407821</v>
+        <v>-14.93374511956793</v>
       </c>
       <c r="Q42">
-        <v>-3.97421624407821</v>
+        <v>-6.093745119567927</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1409789186837115</v>
+        <v>0.1425921206952998</v>
       </c>
       <c r="T42">
-        <v>1.472387601513562</v>
+        <v>1.497343323573114</v>
       </c>
       <c r="U42">
         <v>0.1626309777667576</v>
       </c>
       <c r="V42">
-        <v>0.2122138426837971</v>
+        <v>0.2070378953012655</v>
       </c>
       <c r="W42">
-        <v>0.1281184330354508</v>
+        <v>0.1289602024191412</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4775,7 +4775,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.8488553707351885</v>
+        <v>0.8281515812050618</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4783,22 +4783,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1370030342020748</v>
+        <v>0.1381713439797424</v>
       </c>
       <c r="C43">
-        <v>570.3674001774168</v>
+        <v>539.8033204113235</v>
       </c>
       <c r="D43">
-        <v>1042.624400177417</v>
+        <v>1029.437320411324</v>
       </c>
       <c r="E43">
-        <v>279.7570000000001</v>
+        <v>297.1340000000001</v>
       </c>
       <c r="F43">
-        <v>712.4570000000001</v>
+        <v>729.8340000000001</v>
       </c>
       <c r="G43">
         <v>240.2</v>
@@ -4819,37 +4819,37 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M43">
-        <v>115.8675785267708</v>
+        <v>118.6936170274238</v>
       </c>
       <c r="N43">
-        <v>-19.9116601594239</v>
+        <v>-22.73769866007684</v>
       </c>
       <c r="O43">
-        <v>-4.977915039855976</v>
+        <v>-5.684424665019211</v>
       </c>
       <c r="P43">
-        <v>-14.93374511956793</v>
+        <v>-17.05327399505763</v>
       </c>
       <c r="Q43">
-        <v>-6.093745119567927</v>
+        <v>-8.213273995057634</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1425921206952998</v>
+        <v>0.1442609503624601</v>
       </c>
       <c r="T43">
-        <v>1.497343323573114</v>
+        <v>1.523159587772651</v>
       </c>
       <c r="U43">
         <v>0.1626309777667576</v>
       </c>
       <c r="V43">
-        <v>0.2070378953012655</v>
+        <v>0.2021084216036163</v>
       </c>
       <c r="W43">
-        <v>0.1289602024191412</v>
+        <v>0.1297618875464654</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.8281515812050618</v>
+        <v>0.8084336864144651</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4865,22 +4865,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1381713439797423</v>
+        <v>0.1638801084320711</v>
       </c>
       <c r="C44">
-        <v>539.8033204113241</v>
+        <v>298.2940601998907</v>
       </c>
       <c r="D44">
-        <v>1029.437320411324</v>
+        <v>805.3050601998908</v>
       </c>
       <c r="E44">
-        <v>297.134</v>
+        <v>314.511</v>
       </c>
       <c r="F44">
-        <v>729.8339999999999</v>
+        <v>747.211</v>
       </c>
       <c r="G44">
         <v>240.2</v>
@@ -4901,45 +4901,45 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M44">
-        <v>118.6936170274238</v>
+        <v>161.8690495280767</v>
       </c>
       <c r="N44">
-        <v>-22.73769866007683</v>
+        <v>-65.91313116072978</v>
       </c>
       <c r="O44">
-        <v>-5.684424665019208</v>
+        <v>-16.47828279018244</v>
       </c>
       <c r="P44">
-        <v>-17.05327399505762</v>
+        <v>-49.43484837054733</v>
       </c>
       <c r="Q44">
-        <v>-8.213273995057623</v>
+        <v>-40.59484837054733</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1442609503624601</v>
+        <v>0.1483049226050667</v>
       </c>
       <c r="T44">
-        <v>1.52315958777265</v>
+        <v>1.585718552228483</v>
       </c>
       <c r="U44">
-        <v>0.1626309777667576</v>
+        <v>0.2166309777667576</v>
       </c>
       <c r="V44">
-        <v>0.2021084216036163</v>
+        <v>0.1481999163013295</v>
       </c>
       <c r="W44">
-        <v>0.1297618875464654</v>
+        <v>0.1845262849934489</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y44">
-        <v>0.8084336864144652</v>
+        <v>0.5927996652053181</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4947,22 +4947,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1638801084320711</v>
+        <v>0.1655884182097386</v>
       </c>
       <c r="C45">
-        <v>298.2940601998907</v>
+        <v>269.4325566985932</v>
       </c>
       <c r="D45">
-        <v>805.3050601998908</v>
+        <v>793.8205566985932</v>
       </c>
       <c r="E45">
-        <v>314.511</v>
+        <v>331.8880000000001</v>
       </c>
       <c r="F45">
-        <v>747.211</v>
+        <v>764.5880000000001</v>
       </c>
       <c r="G45">
         <v>240.2</v>
@@ -4983,37 +4983,37 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M45">
-        <v>161.8690495280767</v>
+        <v>165.6334460287297</v>
       </c>
       <c r="N45">
-        <v>-65.91313116072978</v>
+        <v>-69.67752766138274</v>
       </c>
       <c r="O45">
-        <v>-16.47828279018244</v>
+        <v>-17.41938191534569</v>
       </c>
       <c r="P45">
-        <v>-49.43484837054733</v>
+        <v>-52.25814574603706</v>
       </c>
       <c r="Q45">
-        <v>-40.59484837054733</v>
+        <v>-43.41814574603706</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1483049226050667</v>
+        <v>0.1501353676515857</v>
       </c>
       <c r="T45">
-        <v>1.585718552228483</v>
+        <v>1.614034954946849</v>
       </c>
       <c r="U45">
         <v>0.2166309777667576</v>
       </c>
       <c r="V45">
-        <v>0.1481999163013295</v>
+        <v>0.1448317363853902</v>
       </c>
       <c r="W45">
-        <v>0.1845262849934489</v>
+        <v>0.1852559371019332</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.5927996652053181</v>
+        <v>0.5793269455415608</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5029,22 +5029,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1655884182097386</v>
+        <v>0.1672967279874062</v>
       </c>
       <c r="C46">
-        <v>269.4325566985932</v>
+        <v>240.8940098718975</v>
       </c>
       <c r="D46">
-        <v>793.8205566985932</v>
+        <v>782.6590098718976</v>
       </c>
       <c r="E46">
-        <v>331.8880000000001</v>
+        <v>349.265</v>
       </c>
       <c r="F46">
-        <v>764.5880000000001</v>
+        <v>781.965</v>
       </c>
       <c r="G46">
         <v>240.2</v>
@@ -5065,37 +5065,37 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M46">
-        <v>165.6334460287297</v>
+        <v>169.3978425293826</v>
       </c>
       <c r="N46">
-        <v>-69.67752766138274</v>
+        <v>-73.44192416203568</v>
       </c>
       <c r="O46">
-        <v>-17.41938191534569</v>
+        <v>-18.36048104050892</v>
       </c>
       <c r="P46">
-        <v>-52.25814574603706</v>
+        <v>-55.08144312152676</v>
       </c>
       <c r="Q46">
-        <v>-43.41814574603706</v>
+        <v>-46.24144312152676</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1501353676515857</v>
+        <v>0.15203237433616</v>
       </c>
       <c r="T46">
-        <v>1.614034954946849</v>
+        <v>1.643381045036792</v>
       </c>
       <c r="U46">
         <v>0.2166309777667576</v>
       </c>
       <c r="V46">
-        <v>0.1448317363853902</v>
+        <v>0.1416132533546038</v>
       </c>
       <c r="W46">
-        <v>0.1852559371019332</v>
+        <v>0.1859531602278182</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.5793269455415608</v>
+        <v>0.5664530134184151</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5111,22 +5111,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1672967279874062</v>
+        <v>0.1690050377650738</v>
       </c>
       <c r="C47">
-        <v>240.8940098718975</v>
+        <v>212.6649857712823</v>
       </c>
       <c r="D47">
-        <v>782.6590098718976</v>
+        <v>771.8069857712824</v>
       </c>
       <c r="E47">
-        <v>349.265</v>
+        <v>366.6420000000001</v>
       </c>
       <c r="F47">
-        <v>781.965</v>
+        <v>799.3420000000001</v>
       </c>
       <c r="G47">
         <v>240.2</v>
@@ -5147,37 +5147,37 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M47">
-        <v>169.3978425293826</v>
+        <v>173.1622390300356</v>
       </c>
       <c r="N47">
-        <v>-73.44192416203568</v>
+        <v>-77.20632066268864</v>
       </c>
       <c r="O47">
-        <v>-18.36048104050892</v>
+        <v>-19.30158016567216</v>
       </c>
       <c r="P47">
-        <v>-55.08144312152676</v>
+        <v>-57.90474049701648</v>
       </c>
       <c r="Q47">
-        <v>-46.24144312152676</v>
+        <v>-49.06474049701647</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.15203237433616</v>
+        <v>0.1539996405275704</v>
       </c>
       <c r="T47">
-        <v>1.643381045036792</v>
+        <v>1.673814027352288</v>
       </c>
       <c r="U47">
         <v>0.2166309777667576</v>
       </c>
       <c r="V47">
-        <v>0.1416132533546038</v>
+        <v>0.1385347043686341</v>
       </c>
       <c r="W47">
-        <v>0.1859531602278182</v>
+        <v>0.1866200693047517</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.5664530134184151</v>
+        <v>0.5541388174745365</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5193,22 +5193,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1690050377650738</v>
+        <v>0.1707133475427414</v>
       </c>
       <c r="C48">
-        <v>212.6649857712823</v>
+        <v>184.7327853367246</v>
       </c>
       <c r="D48">
-        <v>771.8069857712824</v>
+        <v>761.2517853367247</v>
       </c>
       <c r="E48">
-        <v>366.6420000000001</v>
+        <v>384.0190000000001</v>
       </c>
       <c r="F48">
-        <v>799.3420000000001</v>
+        <v>816.7190000000001</v>
       </c>
       <c r="G48">
         <v>240.2</v>
@@ -5229,37 +5229,37 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M48">
-        <v>173.1622390300356</v>
+        <v>176.9266355306885</v>
       </c>
       <c r="N48">
-        <v>-77.20632066268864</v>
+        <v>-80.97071716334158</v>
       </c>
       <c r="O48">
-        <v>-19.30158016567216</v>
+        <v>-20.24267929083539</v>
       </c>
       <c r="P48">
-        <v>-57.90474049701648</v>
+        <v>-60.72803787250618</v>
       </c>
       <c r="Q48">
-        <v>-49.06474049701647</v>
+        <v>-51.88803787250617</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1539996405275704</v>
+        <v>0.156041143179034</v>
       </c>
       <c r="T48">
-        <v>1.673814027352288</v>
+        <v>1.705395424094784</v>
       </c>
       <c r="U48">
         <v>0.2166309777667576</v>
       </c>
       <c r="V48">
-        <v>0.1385347043686341</v>
+        <v>0.1355871574671738</v>
       </c>
       <c r="W48">
-        <v>0.1866200693047517</v>
+        <v>0.1872585992720284</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.5541388174745365</v>
+        <v>0.5423486298686953</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5275,22 +5275,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1707133475427414</v>
+        <v>0.172421657320409</v>
       </c>
       <c r="C49">
-        <v>184.7327853367246</v>
+        <v>157.0853948231419</v>
       </c>
       <c r="D49">
-        <v>761.2517853367247</v>
+        <v>750.9813948231421</v>
       </c>
       <c r="E49">
-        <v>384.0190000000001</v>
+        <v>401.3960000000001</v>
       </c>
       <c r="F49">
-        <v>816.7190000000001</v>
+        <v>834.0960000000001</v>
       </c>
       <c r="G49">
         <v>240.2</v>
@@ -5311,37 +5311,37 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M49">
-        <v>176.9266355306885</v>
+        <v>180.6910320313415</v>
       </c>
       <c r="N49">
-        <v>-80.97071716334158</v>
+        <v>-84.73511366399454</v>
       </c>
       <c r="O49">
-        <v>-20.24267929083539</v>
+        <v>-21.18377841599863</v>
       </c>
       <c r="P49">
-        <v>-60.72803787250618</v>
+        <v>-63.55133524799591</v>
       </c>
       <c r="Q49">
-        <v>-51.88803787250617</v>
+        <v>-54.7113352479959</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.156041143179034</v>
+        <v>0.1581611651632462</v>
       </c>
       <c r="T49">
-        <v>1.705395424094784</v>
+        <v>1.73819148994276</v>
       </c>
       <c r="U49">
         <v>0.2166309777667576</v>
       </c>
       <c r="V49">
-        <v>0.1355871574671738</v>
+        <v>0.132762425019941</v>
       </c>
       <c r="W49">
-        <v>0.1872585992720284</v>
+        <v>0.1878705238240019</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.5423486298686953</v>
+        <v>0.531049700079764</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1724216573204089</v>
+        <v>0.1741299670980765</v>
       </c>
       <c r="C50">
-        <v>157.0853948231422</v>
+        <v>129.7114401863321</v>
       </c>
       <c r="D50">
-        <v>750.9813948231423</v>
+        <v>740.984440186332</v>
       </c>
       <c r="E50">
-        <v>401.396</v>
+        <v>418.773</v>
       </c>
       <c r="F50">
-        <v>834.096</v>
+        <v>851.473</v>
       </c>
       <c r="G50">
         <v>240.2</v>
@@ -5393,37 +5393,37 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M50">
-        <v>180.6910320313415</v>
+        <v>184.4554285319944</v>
       </c>
       <c r="N50">
-        <v>-84.73511366399451</v>
+        <v>-88.49951016464745</v>
       </c>
       <c r="O50">
-        <v>-21.18377841599863</v>
+        <v>-22.12487754116186</v>
       </c>
       <c r="P50">
-        <v>-63.55133524799588</v>
+        <v>-66.37463262348558</v>
       </c>
       <c r="Q50">
-        <v>-54.71133524799588</v>
+        <v>-57.53463262348558</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1581611651632462</v>
+        <v>0.1603643252644863</v>
       </c>
       <c r="T50">
-        <v>1.73819148994276</v>
+        <v>1.772273676020069</v>
       </c>
       <c r="U50">
         <v>0.2166309777667576</v>
       </c>
       <c r="V50">
-        <v>0.132762425019941</v>
+        <v>0.1300529877746361</v>
       </c>
       <c r="W50">
-        <v>0.1878705238240019</v>
+        <v>0.18845747186365</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.5310497000797642</v>
+        <v>0.5202119510985446</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5439,22 +5439,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1741299670980765</v>
+        <v>0.1758382768757441</v>
       </c>
       <c r="C51">
-        <v>129.7114401863321</v>
+        <v>102.6001450642935</v>
       </c>
       <c r="D51">
-        <v>740.984440186332</v>
+        <v>731.2501450642936</v>
       </c>
       <c r="E51">
-        <v>418.773</v>
+        <v>436.15</v>
       </c>
       <c r="F51">
-        <v>851.473</v>
+        <v>868.85</v>
       </c>
       <c r="G51">
         <v>240.2</v>
@@ -5475,37 +5475,37 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M51">
-        <v>184.4554285319944</v>
+        <v>188.2198250326473</v>
       </c>
       <c r="N51">
-        <v>-88.49951016464745</v>
+        <v>-92.26390666530041</v>
       </c>
       <c r="O51">
-        <v>-22.12487754116186</v>
+        <v>-23.0659766663251</v>
       </c>
       <c r="P51">
-        <v>-66.37463262348558</v>
+        <v>-69.19792999897531</v>
       </c>
       <c r="Q51">
-        <v>-57.53463262348558</v>
+        <v>-60.35792999897531</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1603643252644863</v>
+        <v>0.162655611769776</v>
       </c>
       <c r="T51">
-        <v>1.772273676020069</v>
+        <v>1.807719149540471</v>
       </c>
       <c r="U51">
         <v>0.2166309777667576</v>
       </c>
       <c r="V51">
-        <v>0.1300529877746361</v>
+        <v>0.1274519280191434</v>
       </c>
       <c r="W51">
-        <v>0.18845747186365</v>
+        <v>0.1890209419817122</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.5202119510985446</v>
+        <v>0.5098077120765736</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5521,22 +5521,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1758382768757441</v>
+        <v>0.1959497290548579</v>
       </c>
       <c r="C52">
-        <v>102.6001450642935</v>
+        <v>-12.72243509760915</v>
       </c>
       <c r="D52">
-        <v>731.2501450642936</v>
+        <v>633.3045649023909</v>
       </c>
       <c r="E52">
-        <v>436.15</v>
+        <v>453.5270000000001</v>
       </c>
       <c r="F52">
-        <v>868.85</v>
+        <v>886.2270000000001</v>
       </c>
       <c r="G52">
         <v>240.2</v>
@@ -5557,45 +5557,45 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M52">
-        <v>188.2198250326473</v>
+        <v>223.0021665333003</v>
       </c>
       <c r="N52">
-        <v>-92.26390666530041</v>
+        <v>-127.0462481659533</v>
       </c>
       <c r="O52">
-        <v>-23.0659766663251</v>
+        <v>-31.76156204148834</v>
       </c>
       <c r="P52">
-        <v>-69.19792999897531</v>
+        <v>-95.28468612446501</v>
       </c>
       <c r="Q52">
-        <v>-60.35792999897531</v>
+        <v>-86.44468612446501</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.162655611769776</v>
+        <v>0.1661692822170086</v>
       </c>
       <c r="T52">
-        <v>1.807719149540471</v>
+        <v>1.862074513878049</v>
       </c>
       <c r="U52">
-        <v>0.2166309777667576</v>
+        <v>0.2516309777667576</v>
       </c>
       <c r="V52">
-        <v>0.1274519280191434</v>
+        <v>0.1075728544020873</v>
       </c>
       <c r="W52">
-        <v>0.1890209419817122</v>
+        <v>0.2245623152323993</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y52">
-        <v>0.5098077120765736</v>
+        <v>0.4302914176083492</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5603,22 +5603,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1959497290548579</v>
+        <v>0.1980080388325254</v>
       </c>
       <c r="C53">
-        <v>-12.72243509760915</v>
+        <v>-38.663614678258</v>
       </c>
       <c r="D53">
-        <v>633.3045649023909</v>
+        <v>624.7403853217421</v>
       </c>
       <c r="E53">
-        <v>453.5270000000001</v>
+        <v>470.9040000000001</v>
       </c>
       <c r="F53">
-        <v>886.2270000000001</v>
+        <v>903.604</v>
       </c>
       <c r="G53">
         <v>240.2</v>
@@ -5639,37 +5639,37 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M53">
-        <v>223.0021665333003</v>
+        <v>227.3747580339532</v>
       </c>
       <c r="N53">
-        <v>-127.0462481659533</v>
+        <v>-131.4188396666063</v>
       </c>
       <c r="O53">
-        <v>-31.76156204148834</v>
+        <v>-32.85470991665157</v>
       </c>
       <c r="P53">
-        <v>-95.28468612446501</v>
+        <v>-98.56412974995472</v>
       </c>
       <c r="Q53">
-        <v>-86.44468612446501</v>
+        <v>-89.72412974995471</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1661692822170086</v>
+        <v>0.1686769755965296</v>
       </c>
       <c r="T53">
-        <v>1.862074513878049</v>
+        <v>1.900867732917175</v>
       </c>
       <c r="U53">
         <v>0.2516309777667576</v>
       </c>
       <c r="V53">
-        <v>0.1075728544020873</v>
+        <v>0.1055041456635856</v>
       </c>
       <c r="W53">
-        <v>0.2245623152323993</v>
+        <v>0.2250828664349831</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.4302914176083492</v>
+        <v>0.4220165826543424</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5685,22 +5685,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1980080388325254</v>
+        <v>0.200066348610193</v>
       </c>
       <c r="C54">
-        <v>-38.663614678258</v>
+        <v>-64.37625790308641</v>
       </c>
       <c r="D54">
-        <v>624.7403853217421</v>
+        <v>616.4047420969137</v>
       </c>
       <c r="E54">
-        <v>470.9040000000001</v>
+        <v>488.2810000000001</v>
       </c>
       <c r="F54">
-        <v>903.604</v>
+        <v>920.9810000000001</v>
       </c>
       <c r="G54">
         <v>240.2</v>
@@ -5721,37 +5721,37 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M54">
-        <v>227.3747580339532</v>
+        <v>231.7473495346062</v>
       </c>
       <c r="N54">
-        <v>-131.4188396666063</v>
+        <v>-135.7914311672592</v>
       </c>
       <c r="O54">
-        <v>-32.85470991665157</v>
+        <v>-33.94785779181481</v>
       </c>
       <c r="P54">
-        <v>-98.56412974995472</v>
+        <v>-101.8435733754444</v>
       </c>
       <c r="Q54">
-        <v>-89.72412974995471</v>
+        <v>-93.00357337544443</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1686769755965296</v>
+        <v>0.171291379332626</v>
       </c>
       <c r="T54">
-        <v>1.900867732917175</v>
+        <v>1.941311727234562</v>
       </c>
       <c r="U54">
         <v>0.2516309777667576</v>
       </c>
       <c r="V54">
-        <v>0.1055041456635856</v>
+        <v>0.1035135014057821</v>
       </c>
       <c r="W54">
-        <v>0.2250828664349831</v>
+        <v>0.22558377419596</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.4220165826543424</v>
+        <v>0.4140540056231284</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5767,22 +5767,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.200066348610193</v>
+        <v>0.2021246583878606</v>
       </c>
       <c r="C55">
-        <v>-64.37625790308641</v>
+        <v>-89.86939211212973</v>
       </c>
       <c r="D55">
-        <v>616.4047420969137</v>
+        <v>608.2886078878703</v>
       </c>
       <c r="E55">
-        <v>488.2810000000001</v>
+        <v>505.6580000000001</v>
       </c>
       <c r="F55">
-        <v>920.9810000000001</v>
+        <v>938.3580000000001</v>
       </c>
       <c r="G55">
         <v>240.2</v>
@@ -5803,37 +5803,37 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M55">
-        <v>231.7473495346062</v>
+        <v>236.1199410352591</v>
       </c>
       <c r="N55">
-        <v>-135.7914311672592</v>
+        <v>-140.1640226679122</v>
       </c>
       <c r="O55">
-        <v>-33.94785779181481</v>
+        <v>-35.04100566697805</v>
       </c>
       <c r="P55">
-        <v>-101.8435733754444</v>
+        <v>-105.1230170009342</v>
       </c>
       <c r="Q55">
-        <v>-93.00357337544443</v>
+        <v>-96.28301700093415</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.171291379332626</v>
+        <v>0.1740194527963788</v>
       </c>
       <c r="T55">
-        <v>1.941311727234562</v>
+        <v>1.983514156087488</v>
       </c>
       <c r="U55">
         <v>0.2516309777667576</v>
       </c>
       <c r="V55">
-        <v>0.1035135014057821</v>
+        <v>0.1015965847130824</v>
       </c>
       <c r="W55">
-        <v>0.22558377419596</v>
+        <v>0.2260661298176414</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5841,7 +5841,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.4140540056231284</v>
+        <v>0.4063863388523297</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5849,22 +5849,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.2021246583878606</v>
+        <v>0.2041829681655282</v>
       </c>
       <c r="C56">
-        <v>-89.86939211212973</v>
+        <v>-115.1515753762221</v>
       </c>
       <c r="D56">
-        <v>608.2886078878703</v>
+        <v>600.3834246237781</v>
       </c>
       <c r="E56">
-        <v>505.6580000000001</v>
+        <v>523.0350000000001</v>
       </c>
       <c r="F56">
-        <v>938.3580000000001</v>
+        <v>955.7350000000001</v>
       </c>
       <c r="G56">
         <v>240.2</v>
@@ -5885,37 +5885,37 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M56">
-        <v>236.1199410352591</v>
+        <v>240.4925325359121</v>
       </c>
       <c r="N56">
-        <v>-140.1640226679122</v>
+        <v>-144.5366141685652</v>
       </c>
       <c r="O56">
-        <v>-35.04100566697805</v>
+        <v>-36.13415354214129</v>
       </c>
       <c r="P56">
-        <v>-105.1230170009342</v>
+        <v>-108.4024606264239</v>
       </c>
       <c r="Q56">
-        <v>-96.28301700093415</v>
+        <v>-99.56246062642387</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1740194527963788</v>
+        <v>0.1768687739696316</v>
       </c>
       <c r="T56">
-        <v>1.983514156087488</v>
+        <v>2.027592248444987</v>
       </c>
       <c r="U56">
         <v>0.2516309777667576</v>
       </c>
       <c r="V56">
-        <v>0.1015965847130824</v>
+        <v>0.09974937408193547</v>
       </c>
       <c r="W56">
-        <v>0.2260661298176414</v>
+        <v>0.2265309452348981</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.4063863388523297</v>
+        <v>0.3989974963277418</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5931,22 +5931,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.2041829681655282</v>
+        <v>0.2062412779431957</v>
       </c>
       <c r="C57">
-        <v>-115.1515753762221</v>
+        <v>-140.2309265983943</v>
       </c>
       <c r="D57">
-        <v>600.3834246237781</v>
+        <v>592.6810734016058</v>
       </c>
       <c r="E57">
-        <v>523.0350000000001</v>
+        <v>540.412</v>
       </c>
       <c r="F57">
-        <v>955.7350000000001</v>
+        <v>973.1120000000001</v>
       </c>
       <c r="G57">
         <v>240.2</v>
@@ -5967,37 +5967,37 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M57">
-        <v>240.4925325359121</v>
+        <v>244.865124036565</v>
       </c>
       <c r="N57">
-        <v>-144.5366141685652</v>
+        <v>-148.9092056692181</v>
       </c>
       <c r="O57">
-        <v>-36.13415354214129</v>
+        <v>-37.22730141730452</v>
       </c>
       <c r="P57">
-        <v>-108.4024606264239</v>
+        <v>-111.6819042519136</v>
       </c>
       <c r="Q57">
-        <v>-99.56246062642387</v>
+        <v>-102.8419042519135</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1768687739696316</v>
+        <v>0.1798476097416687</v>
       </c>
       <c r="T57">
-        <v>2.027592248444987</v>
+        <v>2.073673890455101</v>
       </c>
       <c r="U57">
         <v>0.2516309777667576</v>
       </c>
       <c r="V57">
-        <v>0.09974937408193547</v>
+        <v>0.09796813525904378</v>
       </c>
       <c r="W57">
-        <v>0.2265309452348981</v>
+        <v>0.2269791601015384</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.3989974963277418</v>
+        <v>0.3918725410361752</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6013,22 +6013,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.2062412779431957</v>
+        <v>0.2082995877208633</v>
       </c>
       <c r="C58">
-        <v>-140.2309265983943</v>
+        <v>-165.1151533275882</v>
       </c>
       <c r="D58">
-        <v>592.6810734016058</v>
+        <v>585.1738466724119</v>
       </c>
       <c r="E58">
-        <v>540.412</v>
+        <v>557.7890000000002</v>
       </c>
       <c r="F58">
-        <v>973.1120000000001</v>
+        <v>990.4890000000001</v>
       </c>
       <c r="G58">
         <v>240.2</v>
@@ -6049,37 +6049,37 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M58">
-        <v>244.865124036565</v>
+        <v>249.237715537218</v>
       </c>
       <c r="N58">
-        <v>-148.9092056692181</v>
+        <v>-153.281797169871</v>
       </c>
       <c r="O58">
-        <v>-37.22730141730452</v>
+        <v>-38.32044929246776</v>
       </c>
       <c r="P58">
-        <v>-111.6819042519136</v>
+        <v>-114.9613478774033</v>
       </c>
       <c r="Q58">
-        <v>-102.8419042519135</v>
+        <v>-106.1213478774033</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1798476097416687</v>
+        <v>0.1829649960147308</v>
       </c>
       <c r="T58">
-        <v>2.073673890455101</v>
+        <v>2.121898864651731</v>
       </c>
       <c r="U58">
         <v>0.2516309777667576</v>
       </c>
       <c r="V58">
-        <v>0.09796813525904378</v>
+        <v>0.09624939604397284</v>
       </c>
       <c r="W58">
-        <v>0.2269791601015384</v>
+        <v>0.2274116481307528</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.3918725410361752</v>
+        <v>0.3849975841758914</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6095,22 +6095,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.2082995877208633</v>
+        <v>0.2103578974985309</v>
       </c>
       <c r="C59">
-        <v>-165.1151533275882</v>
+        <v>-189.8115774849849</v>
       </c>
       <c r="D59">
-        <v>585.1738466724119</v>
+        <v>577.8544225150151</v>
       </c>
       <c r="E59">
-        <v>557.7890000000002</v>
+        <v>575.1660000000002</v>
       </c>
       <c r="F59">
-        <v>990.4890000000001</v>
+        <v>1007.866</v>
       </c>
       <c r="G59">
         <v>240.2</v>
@@ -6131,37 +6131,37 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M59">
-        <v>249.237715537218</v>
+        <v>253.6103070378709</v>
       </c>
       <c r="N59">
-        <v>-153.281797169871</v>
+        <v>-157.654388670524</v>
       </c>
       <c r="O59">
-        <v>-38.32044929246776</v>
+        <v>-39.413597167631</v>
       </c>
       <c r="P59">
-        <v>-114.9613478774033</v>
+        <v>-118.240791502893</v>
       </c>
       <c r="Q59">
-        <v>-106.1213478774033</v>
+        <v>-109.400791502893</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1829649960147308</v>
+        <v>0.1862308292531767</v>
       </c>
       <c r="T59">
-        <v>2.121898864651731</v>
+        <v>2.172420266191058</v>
       </c>
       <c r="U59">
         <v>0.2516309777667576</v>
       </c>
       <c r="V59">
-        <v>0.09624939604397284</v>
+        <v>0.0945899236983871</v>
       </c>
       <c r="W59">
-        <v>0.2274116481307528</v>
+        <v>0.2278292227796494</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.3849975841758914</v>
+        <v>0.3783596947935484</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6177,22 +6177,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.2103578974985309</v>
+        <v>0.2124162072761985</v>
       </c>
       <c r="C60">
-        <v>-189.8115774849848</v>
+        <v>-214.3271591834593</v>
       </c>
       <c r="D60">
-        <v>577.8544225150151</v>
+        <v>570.7158408165407</v>
       </c>
       <c r="E60">
-        <v>575.1659999999999</v>
+        <v>592.5429999999999</v>
       </c>
       <c r="F60">
-        <v>1007.866</v>
+        <v>1025.243</v>
       </c>
       <c r="G60">
         <v>240.2</v>
@@ -6213,37 +6213,37 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M60">
-        <v>253.6103070378709</v>
+        <v>257.9828985385238</v>
       </c>
       <c r="N60">
-        <v>-157.6543886705239</v>
+        <v>-162.0269801711769</v>
       </c>
       <c r="O60">
-        <v>-39.41359716763098</v>
+        <v>-40.50674504279422</v>
       </c>
       <c r="P60">
-        <v>-118.2407915028929</v>
+        <v>-121.5202351283827</v>
       </c>
       <c r="Q60">
-        <v>-109.4007915028929</v>
+        <v>-112.6802351283827</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1862308292531767</v>
+        <v>0.1896559714300835</v>
       </c>
       <c r="T60">
-        <v>2.172420266191057</v>
+        <v>2.225406126342059</v>
       </c>
       <c r="U60">
         <v>0.2516309777667576</v>
       </c>
       <c r="V60">
-        <v>0.09458992369838712</v>
+        <v>0.09298670465265173</v>
       </c>
       <c r="W60">
-        <v>0.2278292227796494</v>
+        <v>0.2282326423557021</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.3783596947935485</v>
+        <v>0.371946818610607</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6259,22 +6259,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.2124162072761985</v>
+        <v>0.2144745170538661</v>
       </c>
       <c r="C61">
-        <v>-214.3271591834593</v>
+        <v>-238.6685188030413</v>
       </c>
       <c r="D61">
-        <v>570.7158408165407</v>
+        <v>563.7514811969586</v>
       </c>
       <c r="E61">
-        <v>592.5429999999999</v>
+        <v>609.9199999999998</v>
       </c>
       <c r="F61">
-        <v>1025.243</v>
+        <v>1042.62</v>
       </c>
       <c r="G61">
         <v>240.2</v>
@@ -6295,37 +6295,37 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M61">
-        <v>257.9828985385238</v>
+        <v>262.3554900391767</v>
       </c>
       <c r="N61">
-        <v>-162.0269801711769</v>
+        <v>-166.3995716718298</v>
       </c>
       <c r="O61">
-        <v>-40.50674504279422</v>
+        <v>-41.59989291795745</v>
       </c>
       <c r="P61">
-        <v>-121.5202351283827</v>
+        <v>-124.7996787538723</v>
       </c>
       <c r="Q61">
-        <v>-112.6802351283827</v>
+        <v>-115.9596787538723</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1896559714300835</v>
+        <v>0.1932523707158356</v>
       </c>
       <c r="T61">
-        <v>2.225406126342059</v>
+        <v>2.28104127950061</v>
       </c>
       <c r="U61">
         <v>0.2516309777667576</v>
       </c>
       <c r="V61">
-        <v>0.09298670465265173</v>
+        <v>0.09143692624177421</v>
       </c>
       <c r="W61">
-        <v>0.2282326423557021</v>
+        <v>0.228622614612553</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.371946818610607</v>
+        <v>0.365747704967097</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6341,22 +6341,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.2144745170538661</v>
+        <v>0.2165328268315336</v>
       </c>
       <c r="C62">
-        <v>-238.6685188030413</v>
+        <v>-262.8419574695624</v>
       </c>
       <c r="D62">
-        <v>563.7514811969586</v>
+        <v>556.9550425304376</v>
       </c>
       <c r="E62">
-        <v>609.9199999999998</v>
+        <v>627.297</v>
       </c>
       <c r="F62">
-        <v>1042.62</v>
+        <v>1059.997</v>
       </c>
       <c r="G62">
         <v>240.2</v>
@@ -6377,37 +6377,37 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M62">
-        <v>262.3554900391767</v>
+        <v>266.7280815398298</v>
       </c>
       <c r="N62">
-        <v>-166.3995716718298</v>
+        <v>-170.7721631724828</v>
       </c>
       <c r="O62">
-        <v>-41.59989291795745</v>
+        <v>-42.6930407931207</v>
       </c>
       <c r="P62">
-        <v>-124.7996787538723</v>
+        <v>-128.0791223793621</v>
       </c>
       <c r="Q62">
-        <v>-115.9596787538723</v>
+        <v>-119.2391223793621</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1932523707158356</v>
+        <v>0.1970332007341903</v>
       </c>
       <c r="T62">
-        <v>2.28104127950061</v>
+        <v>2.339529517436524</v>
       </c>
       <c r="U62">
         <v>0.2516309777667576</v>
       </c>
       <c r="V62">
-        <v>0.09143692624177421</v>
+        <v>0.08993796023781069</v>
       </c>
       <c r="W62">
-        <v>0.228622614612553</v>
+        <v>0.2289998008937695</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.365747704967097</v>
+        <v>0.3597518409512428</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.2165328268315336</v>
+        <v>0.2185911366092012</v>
       </c>
       <c r="C63">
-        <v>-262.8419574695624</v>
+        <v>-286.8534760696366</v>
       </c>
       <c r="D63">
-        <v>556.9550425304376</v>
+        <v>550.3205239303635</v>
       </c>
       <c r="E63">
-        <v>627.297</v>
+        <v>644.674</v>
       </c>
       <c r="F63">
-        <v>1059.997</v>
+        <v>1077.374</v>
       </c>
       <c r="G63">
         <v>240.2</v>
@@ -6459,37 +6459,37 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M63">
-        <v>266.7280815398298</v>
+        <v>271.1006730404827</v>
       </c>
       <c r="N63">
-        <v>-170.7721631724828</v>
+        <v>-175.1447546731357</v>
       </c>
       <c r="O63">
-        <v>-42.6930407931207</v>
+        <v>-43.78618866828393</v>
       </c>
       <c r="P63">
-        <v>-128.0791223793621</v>
+        <v>-131.3585660048518</v>
       </c>
       <c r="Q63">
-        <v>-119.2391223793621</v>
+        <v>-122.5185660048518</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1970332007341903</v>
+        <v>0.2010130218061427</v>
       </c>
       <c r="T63">
-        <v>2.339529517436524</v>
+        <v>2.401096083684853</v>
       </c>
       <c r="U63">
         <v>0.2516309777667576</v>
       </c>
       <c r="V63">
-        <v>0.08993796023781069</v>
+        <v>0.08848734797591053</v>
       </c>
       <c r="W63">
-        <v>0.2289998008937695</v>
+        <v>0.2293648198755919</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.3597518409512428</v>
+        <v>0.3539493919036422</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6505,22 +6505,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.2185911366092012</v>
+        <v>0.2206494463868688</v>
       </c>
       <c r="C64">
-        <v>-286.8534760696366</v>
+        <v>-310.7087929225863</v>
       </c>
       <c r="D64">
-        <v>550.3205239303635</v>
+        <v>543.8422070774136</v>
       </c>
       <c r="E64">
-        <v>644.674</v>
+        <v>662.0509999999999</v>
       </c>
       <c r="F64">
-        <v>1077.374</v>
+        <v>1094.751</v>
       </c>
       <c r="G64">
         <v>240.2</v>
@@ -6541,37 +6541,37 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M64">
-        <v>271.1006730404827</v>
+        <v>275.4732645411356</v>
       </c>
       <c r="N64">
-        <v>-175.1447546731357</v>
+        <v>-179.5173461737887</v>
       </c>
       <c r="O64">
-        <v>-43.78618866828393</v>
+        <v>-44.87933654344717</v>
       </c>
       <c r="P64">
-        <v>-131.3585660048518</v>
+        <v>-134.6380096303415</v>
       </c>
       <c r="Q64">
-        <v>-122.5185660048518</v>
+        <v>-125.7980096303415</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2010130218061427</v>
+        <v>0.2052079683414439</v>
       </c>
       <c r="T64">
-        <v>2.401096083684853</v>
+        <v>2.465990572433093</v>
       </c>
       <c r="U64">
         <v>0.2516309777667576</v>
       </c>
       <c r="V64">
-        <v>0.08848734797591053</v>
+        <v>0.08708278689692782</v>
       </c>
       <c r="W64">
-        <v>0.2293648198755919</v>
+        <v>0.2297182509532295</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.3539493919036422</v>
+        <v>0.3483311475877113</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6587,22 +6587,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.2206494463868688</v>
+        <v>0.2227077561645364</v>
       </c>
       <c r="C65">
-        <v>-310.7087929225863</v>
+        <v>-334.4133602187012</v>
       </c>
       <c r="D65">
-        <v>543.8422070774136</v>
+        <v>537.514639781299</v>
       </c>
       <c r="E65">
-        <v>662.0509999999999</v>
+        <v>679.4280000000001</v>
       </c>
       <c r="F65">
-        <v>1094.751</v>
+        <v>1112.128</v>
       </c>
       <c r="G65">
         <v>240.2</v>
@@ -6623,37 +6623,37 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M65">
-        <v>275.4732645411356</v>
+        <v>279.8458560417886</v>
       </c>
       <c r="N65">
-        <v>-179.5173461737887</v>
+        <v>-183.8899376744417</v>
       </c>
       <c r="O65">
-        <v>-44.87933654344717</v>
+        <v>-45.97248441861042</v>
       </c>
       <c r="P65">
-        <v>-134.6380096303415</v>
+        <v>-137.9174532558313</v>
       </c>
       <c r="Q65">
-        <v>-125.7980096303415</v>
+        <v>-129.0774532558313</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2052079683414439</v>
+        <v>0.2096359674620395</v>
       </c>
       <c r="T65">
-        <v>2.465990572433093</v>
+        <v>2.534490310556234</v>
       </c>
       <c r="U65">
         <v>0.2516309777667576</v>
       </c>
       <c r="V65">
-        <v>0.08708278689692782</v>
+        <v>0.0857221183516633</v>
       </c>
       <c r="W65">
-        <v>0.2297182509532295</v>
+        <v>0.2300606373096908</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.3483311475877113</v>
+        <v>0.3428884734066533</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6669,22 +6669,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2227077561645364</v>
+        <v>0.2247660659422039</v>
       </c>
       <c r="C66">
-        <v>-334.4133602187012</v>
+        <v>-357.9723793231419</v>
       </c>
       <c r="D66">
-        <v>537.514639781299</v>
+        <v>531.3326206768583</v>
       </c>
       <c r="E66">
-        <v>679.4280000000001</v>
+        <v>696.8050000000001</v>
       </c>
       <c r="F66">
-        <v>1112.128</v>
+        <v>1129.505</v>
       </c>
       <c r="G66">
         <v>240.2</v>
@@ -6705,37 +6705,37 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M66">
-        <v>279.8458560417886</v>
+        <v>284.2184475424415</v>
       </c>
       <c r="N66">
-        <v>-183.8899376744417</v>
+        <v>-188.2625291750946</v>
       </c>
       <c r="O66">
-        <v>-45.97248441861042</v>
+        <v>-47.06563229377365</v>
       </c>
       <c r="P66">
-        <v>-137.9174532558313</v>
+        <v>-141.1968968813209</v>
       </c>
       <c r="Q66">
-        <v>-129.0774532558313</v>
+        <v>-132.3568968813209</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2096359674620395</v>
+        <v>0.2143169951038121</v>
       </c>
       <c r="T66">
-        <v>2.534490310556234</v>
+        <v>2.606904319429269</v>
       </c>
       <c r="U66">
         <v>0.2516309777667576</v>
       </c>
       <c r="V66">
-        <v>0.0857221183516633</v>
+        <v>0.08440331653086849</v>
       </c>
       <c r="W66">
-        <v>0.2300606373096908</v>
+        <v>0.230392488701338</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.3428884734066533</v>
+        <v>0.337613266123474</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6751,22 +6751,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2247660659422039</v>
+        <v>0.2268243757198715</v>
       </c>
       <c r="C67">
-        <v>-357.9723793231419</v>
+        <v>-381.390815035785</v>
       </c>
       <c r="D67">
-        <v>531.3326206768583</v>
+        <v>525.2911849642152</v>
       </c>
       <c r="E67">
-        <v>696.8050000000001</v>
+        <v>714.182</v>
       </c>
       <c r="F67">
-        <v>1129.505</v>
+        <v>1146.882</v>
       </c>
       <c r="G67">
         <v>240.2</v>
@@ -6787,37 +6787,37 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M67">
-        <v>284.2184475424415</v>
+        <v>288.5910390430945</v>
       </c>
       <c r="N67">
-        <v>-188.2625291750946</v>
+        <v>-192.6351206757475</v>
       </c>
       <c r="O67">
-        <v>-47.06563229377365</v>
+        <v>-48.15878016893689</v>
       </c>
       <c r="P67">
-        <v>-141.1968968813209</v>
+        <v>-144.4763405068107</v>
       </c>
       <c r="Q67">
-        <v>-132.3568968813209</v>
+        <v>-135.6363405068107</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2143169951038121</v>
+        <v>0.2192733773127477</v>
       </c>
       <c r="T67">
-        <v>2.606904319429269</v>
+        <v>2.683577975883071</v>
       </c>
       <c r="U67">
         <v>0.2516309777667576</v>
       </c>
       <c r="V67">
-        <v>0.08440331653086849</v>
+        <v>0.0831244784016129</v>
       </c>
       <c r="W67">
-        <v>0.230392488701338</v>
+        <v>0.230714283990208</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.337613266123474</v>
+        <v>0.3324979136064516</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6833,22 +6833,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2268243757198715</v>
+        <v>0.2288826854975391</v>
       </c>
       <c r="C68">
-        <v>-381.390815035785</v>
+        <v>-404.673408889164</v>
       </c>
       <c r="D68">
-        <v>525.2911849642152</v>
+        <v>519.3855911108361</v>
       </c>
       <c r="E68">
-        <v>714.182</v>
+        <v>731.559</v>
       </c>
       <c r="F68">
-        <v>1146.882</v>
+        <v>1164.259</v>
       </c>
       <c r="G68">
         <v>240.2</v>
@@ -6869,37 +6869,37 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M68">
-        <v>288.5910390430945</v>
+        <v>292.9636305437474</v>
       </c>
       <c r="N68">
-        <v>-192.6351206757475</v>
+        <v>-197.0077121764004</v>
       </c>
       <c r="O68">
-        <v>-48.15878016893689</v>
+        <v>-49.25192804410011</v>
       </c>
       <c r="P68">
-        <v>-144.4763405068107</v>
+        <v>-147.7557841323003</v>
       </c>
       <c r="Q68">
-        <v>-135.6363405068107</v>
+        <v>-138.9157841323003</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2192733773127477</v>
+        <v>0.224530146322225</v>
       </c>
       <c r="T68">
-        <v>2.683577975883071</v>
+        <v>2.764898520606801</v>
       </c>
       <c r="U68">
         <v>0.2516309777667576</v>
       </c>
       <c r="V68">
-        <v>0.0831244784016129</v>
+        <v>0.08188381454487242</v>
       </c>
       <c r="W68">
-        <v>0.230714283990208</v>
+        <v>0.2310264734495595</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.3324979136064516</v>
+        <v>0.3275352581794897</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6915,22 +6915,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2288826854975391</v>
+        <v>0.2309409952752067</v>
       </c>
       <c r="C69">
-        <v>-404.673408889164</v>
+        <v>-427.8246915593743</v>
       </c>
       <c r="D69">
-        <v>519.3855911108361</v>
+        <v>513.611308440626</v>
       </c>
       <c r="E69">
-        <v>731.559</v>
+        <v>748.9360000000001</v>
       </c>
       <c r="F69">
-        <v>1164.259</v>
+        <v>1181.636</v>
       </c>
       <c r="G69">
         <v>240.2</v>
@@ -6951,37 +6951,37 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M69">
-        <v>292.9636305437474</v>
+        <v>297.3362220444004</v>
       </c>
       <c r="N69">
-        <v>-197.0077121764004</v>
+        <v>-201.3803036770535</v>
       </c>
       <c r="O69">
-        <v>-49.25192804410011</v>
+        <v>-50.34507591926337</v>
       </c>
       <c r="P69">
-        <v>-147.7557841323003</v>
+        <v>-151.0352277577901</v>
       </c>
       <c r="Q69">
-        <v>-138.9157841323003</v>
+        <v>-142.1952277577901</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.224530146322225</v>
+        <v>0.2301154633947945</v>
       </c>
       <c r="T69">
-        <v>2.764898520606801</v>
+        <v>2.851301599375764</v>
       </c>
       <c r="U69">
         <v>0.2516309777667576</v>
       </c>
       <c r="V69">
-        <v>0.08188381454487242</v>
+        <v>0.08067964080156546</v>
       </c>
       <c r="W69">
-        <v>0.2310264734495595</v>
+        <v>0.2313294808659889</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.3275352581794897</v>
+        <v>0.3227185632062619</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6997,22 +6997,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2309409952752067</v>
+        <v>0.2329993050528743</v>
       </c>
       <c r="C70">
-        <v>-427.8246915593743</v>
+        <v>-450.8489944582038</v>
       </c>
       <c r="D70">
-        <v>513.611308440626</v>
+        <v>507.9640055417963</v>
       </c>
       <c r="E70">
-        <v>748.9360000000001</v>
+        <v>766.3130000000001</v>
       </c>
       <c r="F70">
-        <v>1181.636</v>
+        <v>1199.013</v>
       </c>
       <c r="G70">
         <v>240.2</v>
@@ -7033,37 +7033,37 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M70">
-        <v>297.3362220444004</v>
+        <v>301.7088135450533</v>
       </c>
       <c r="N70">
-        <v>-201.3803036770535</v>
+        <v>-205.7528951777064</v>
       </c>
       <c r="O70">
-        <v>-50.34507591926337</v>
+        <v>-51.43822379442659</v>
       </c>
       <c r="P70">
-        <v>-151.0352277577901</v>
+        <v>-154.3146713832798</v>
       </c>
       <c r="Q70">
-        <v>-142.1952277577901</v>
+        <v>-145.4746713832798</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2301154633947945</v>
+        <v>0.236061123504304</v>
       </c>
       <c r="T70">
-        <v>2.851301599375764</v>
+        <v>2.943279070323369</v>
       </c>
       <c r="U70">
         <v>0.2516309777667576</v>
       </c>
       <c r="V70">
-        <v>0.08067964080156546</v>
+        <v>0.07951037064502105</v>
       </c>
       <c r="W70">
-        <v>0.2313294808659889</v>
+        <v>0.2316237054587536</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.3227185632062619</v>
+        <v>0.3180414825800842</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7079,22 +7079,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2329993050528743</v>
+        <v>0.2350576148305418</v>
       </c>
       <c r="C71">
-        <v>-450.8489944582038</v>
+        <v>-473.7504605688332</v>
       </c>
       <c r="D71">
-        <v>507.9640055417963</v>
+        <v>502.439539431167</v>
       </c>
       <c r="E71">
-        <v>766.3130000000001</v>
+        <v>783.6900000000001</v>
       </c>
       <c r="F71">
-        <v>1199.013</v>
+        <v>1216.39</v>
       </c>
       <c r="G71">
         <v>240.2</v>
@@ -7115,37 +7115,37 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M71">
-        <v>301.7088135450533</v>
+        <v>306.0814050457063</v>
       </c>
       <c r="N71">
-        <v>-205.7528951777064</v>
+        <v>-210.1254866783593</v>
       </c>
       <c r="O71">
-        <v>-51.43822379442659</v>
+        <v>-52.53137166958983</v>
       </c>
       <c r="P71">
-        <v>-154.3146713832798</v>
+        <v>-157.5941150087695</v>
       </c>
       <c r="Q71">
-        <v>-145.4746713832798</v>
+        <v>-148.7541150087695</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.236061123504304</v>
+        <v>0.2424031609544475</v>
       </c>
       <c r="T71">
-        <v>2.943279070323369</v>
+        <v>3.041388372667481</v>
       </c>
       <c r="U71">
         <v>0.2516309777667576</v>
       </c>
       <c r="V71">
-        <v>0.07951037064502105</v>
+        <v>0.07837450820723503</v>
       </c>
       <c r="W71">
-        <v>0.2316237054587536</v>
+        <v>0.2319095236345823</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.3180414825800842</v>
+        <v>0.3134980328289402</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7161,22 +7161,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2350576148305418</v>
+        <v>0.2371159246082094</v>
       </c>
       <c r="C72">
-        <v>-473.7504605688332</v>
+        <v>-496.5330545820644</v>
       </c>
       <c r="D72">
-        <v>502.439539431167</v>
+        <v>497.0339454179356</v>
       </c>
       <c r="E72">
-        <v>783.6900000000001</v>
+        <v>801.067</v>
       </c>
       <c r="F72">
-        <v>1216.39</v>
+        <v>1233.767</v>
       </c>
       <c r="G72">
         <v>240.2</v>
@@ -7197,37 +7197,37 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M72">
-        <v>306.0814050457063</v>
+        <v>310.4539965463592</v>
       </c>
       <c r="N72">
-        <v>-210.1254866783593</v>
+        <v>-214.4980781790123</v>
       </c>
       <c r="O72">
-        <v>-52.53137166958983</v>
+        <v>-53.62451954475307</v>
       </c>
       <c r="P72">
-        <v>-157.5941150087695</v>
+        <v>-160.8735586342592</v>
       </c>
       <c r="Q72">
-        <v>-148.7541150087695</v>
+        <v>-152.0335586342592</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2424031609544475</v>
+        <v>0.2491825802977043</v>
       </c>
       <c r="T72">
-        <v>3.041388372667481</v>
+        <v>3.146263833793947</v>
       </c>
       <c r="U72">
         <v>0.2516309777667576</v>
       </c>
       <c r="V72">
-        <v>0.07837450820723503</v>
+        <v>0.07727064189445706</v>
       </c>
       <c r="W72">
-        <v>0.2319095236345823</v>
+        <v>0.2321872905941904</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.3134980328289402</v>
+        <v>0.3090825675778283</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7243,22 +7243,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2371159246082094</v>
+        <v>0.2391742343858769</v>
       </c>
       <c r="C73">
-        <v>-496.5330545820644</v>
+        <v>-519.200572385201</v>
       </c>
       <c r="D73">
-        <v>497.0339454179356</v>
+        <v>491.743427614799</v>
       </c>
       <c r="E73">
-        <v>801.067</v>
+        <v>818.444</v>
       </c>
       <c r="F73">
-        <v>1233.767</v>
+        <v>1251.144</v>
       </c>
       <c r="G73">
         <v>240.2</v>
@@ -7279,37 +7279,37 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M73">
-        <v>310.4539965463592</v>
+        <v>314.8265880470121</v>
       </c>
       <c r="N73">
-        <v>-214.4980781790123</v>
+        <v>-218.8706696796652</v>
       </c>
       <c r="O73">
-        <v>-53.62451954475307</v>
+        <v>-54.7176674199163</v>
       </c>
       <c r="P73">
-        <v>-160.8735586342592</v>
+        <v>-164.1530022597489</v>
       </c>
       <c r="Q73">
-        <v>-152.0335586342592</v>
+        <v>-155.3130022597489</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2491825802977042</v>
+        <v>0.2564462438797651</v>
       </c>
       <c r="T73">
-        <v>3.146263833793945</v>
+        <v>3.258630399286586</v>
       </c>
       <c r="U73">
         <v>0.2516309777667576</v>
       </c>
       <c r="V73">
-        <v>0.07727064189445706</v>
+        <v>0.07619743853481184</v>
       </c>
       <c r="W73">
-        <v>0.2321872905941904</v>
+        <v>0.2324573418049204</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.3090825675778283</v>
+        <v>0.3047897541392474</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7325,22 +7325,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2391742343858769</v>
+        <v>0.2412325441635445</v>
       </c>
       <c r="C74">
-        <v>-519.200572385201</v>
+        <v>-541.7566499513014</v>
       </c>
       <c r="D74">
-        <v>491.743427614799</v>
+        <v>486.5643500486987</v>
       </c>
       <c r="E74">
-        <v>818.444</v>
+        <v>835.8209999999999</v>
       </c>
       <c r="F74">
-        <v>1251.144</v>
+        <v>1268.521</v>
       </c>
       <c r="G74">
         <v>240.2</v>
@@ -7361,37 +7361,37 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M74">
-        <v>314.8265880470121</v>
+        <v>319.1991795476651</v>
       </c>
       <c r="N74">
-        <v>-218.8706696796652</v>
+        <v>-223.2432611803181</v>
       </c>
       <c r="O74">
-        <v>-54.7176674199163</v>
+        <v>-55.81081529507954</v>
       </c>
       <c r="P74">
-        <v>-164.1530022597489</v>
+        <v>-167.4324458852386</v>
       </c>
       <c r="Q74">
-        <v>-155.3130022597489</v>
+        <v>-158.5924458852386</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2564462438797651</v>
+        <v>0.2642479566160527</v>
       </c>
       <c r="T74">
-        <v>3.258630399286586</v>
+        <v>3.379320414074978</v>
       </c>
       <c r="U74">
         <v>0.2516309777667576</v>
       </c>
       <c r="V74">
-        <v>0.07619743853481184</v>
+        <v>0.0751536380069377</v>
       </c>
       <c r="W74">
-        <v>0.2324573418049204</v>
+        <v>0.2327199943523429</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.3047897541392474</v>
+        <v>0.3006145520277509</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7407,22 +7407,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2412325441635445</v>
+        <v>0.2432908539412121</v>
       </c>
       <c r="C75">
-        <v>-541.7566499513014</v>
+        <v>-564.2047716725524</v>
       </c>
       <c r="D75">
-        <v>486.5643500486987</v>
+        <v>481.4932283274475</v>
       </c>
       <c r="E75">
-        <v>835.8209999999999</v>
+        <v>853.1979999999999</v>
       </c>
       <c r="F75">
-        <v>1268.521</v>
+        <v>1285.898</v>
       </c>
       <c r="G75">
         <v>240.2</v>
@@ -7443,37 +7443,37 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M75">
-        <v>319.1991795476651</v>
+        <v>323.571771048318</v>
       </c>
       <c r="N75">
-        <v>-223.2432611803181</v>
+        <v>-227.615852680971</v>
       </c>
       <c r="O75">
-        <v>-55.81081529507954</v>
+        <v>-56.90396317024276</v>
       </c>
       <c r="P75">
-        <v>-167.4324458852386</v>
+        <v>-170.7118895107283</v>
       </c>
       <c r="Q75">
-        <v>-158.5924458852386</v>
+        <v>-161.8718895107283</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2642479566160527</v>
+        <v>0.2726498011012854</v>
       </c>
       <c r="T75">
-        <v>3.379320414074978</v>
+        <v>3.509294276154785</v>
       </c>
       <c r="U75">
         <v>0.2516309777667576</v>
       </c>
       <c r="V75">
-        <v>0.0751536380069377</v>
+        <v>0.07413804830414125</v>
       </c>
       <c r="W75">
-        <v>0.2327199943523429</v>
+        <v>0.2329755481822674</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.3006145520277509</v>
+        <v>0.2965521932165651</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7489,22 +7489,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2432908539412121</v>
+        <v>0.2453491637188797</v>
       </c>
       <c r="C76">
-        <v>-564.2047716725524</v>
+        <v>-586.5482781779034</v>
       </c>
       <c r="D76">
-        <v>481.4932283274475</v>
+        <v>476.5267218220967</v>
       </c>
       <c r="E76">
-        <v>853.1979999999999</v>
+        <v>870.575</v>
       </c>
       <c r="F76">
-        <v>1285.898</v>
+        <v>1303.275</v>
       </c>
       <c r="G76">
         <v>240.2</v>
@@ -7525,37 +7525,37 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M76">
-        <v>323.571771048318</v>
+        <v>327.944362548971</v>
       </c>
       <c r="N76">
-        <v>-227.615852680971</v>
+        <v>-231.9884441816241</v>
       </c>
       <c r="O76">
-        <v>-56.90396317024276</v>
+        <v>-57.99711104540602</v>
       </c>
       <c r="P76">
-        <v>-170.7118895107283</v>
+        <v>-173.991333136218</v>
       </c>
       <c r="Q76">
-        <v>-161.8718895107283</v>
+        <v>-165.151333136218</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2726498011012854</v>
+        <v>0.2817237931453369</v>
       </c>
       <c r="T76">
-        <v>3.509294276154785</v>
+        <v>3.649666047200977</v>
       </c>
       <c r="U76">
         <v>0.2516309777667576</v>
       </c>
       <c r="V76">
-        <v>0.07413804830414125</v>
+        <v>0.07314954099341936</v>
       </c>
       <c r="W76">
-        <v>0.2329755481822674</v>
+        <v>0.233224287243394</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.2965521932165651</v>
+        <v>0.2925981639736774</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7571,22 +7571,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2453491637188797</v>
+        <v>0.2474074734965473</v>
       </c>
       <c r="C77">
-        <v>-586.5482781779034</v>
+        <v>-608.7903736718117</v>
       </c>
       <c r="D77">
-        <v>476.5267218220967</v>
+        <v>471.6616263281883</v>
       </c>
       <c r="E77">
-        <v>870.575</v>
+        <v>887.952</v>
       </c>
       <c r="F77">
-        <v>1303.275</v>
+        <v>1320.652</v>
       </c>
       <c r="G77">
         <v>240.2</v>
@@ -7607,37 +7607,37 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M77">
-        <v>327.944362548971</v>
+        <v>332.3169540496239</v>
       </c>
       <c r="N77">
-        <v>-231.9884441816241</v>
+        <v>-236.361035682277</v>
       </c>
       <c r="O77">
-        <v>-57.99711104540602</v>
+        <v>-59.09025892056924</v>
       </c>
       <c r="P77">
-        <v>-173.991333136218</v>
+        <v>-177.2707767617077</v>
       </c>
       <c r="Q77">
-        <v>-165.151333136218</v>
+        <v>-168.4307767617077</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2817237931453369</v>
+        <v>0.2915539511930593</v>
       </c>
       <c r="T77">
-        <v>3.649666047200977</v>
+        <v>3.801735465834351</v>
       </c>
       <c r="U77">
         <v>0.2516309777667576</v>
       </c>
       <c r="V77">
-        <v>0.07314954099341936</v>
+        <v>0.07218704703297964</v>
       </c>
       <c r="W77">
-        <v>0.233224287243394</v>
+        <v>0.233466480539754</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.2925981639736774</v>
+        <v>0.2887481881319186</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7653,22 +7653,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2474074734965473</v>
+        <v>0.2494657832742148</v>
       </c>
       <c r="C78">
-        <v>-608.7903736718117</v>
+        <v>-630.9341328279864</v>
       </c>
       <c r="D78">
-        <v>471.6616263281883</v>
+        <v>466.8948671720136</v>
       </c>
       <c r="E78">
-        <v>887.952</v>
+        <v>905.329</v>
       </c>
       <c r="F78">
-        <v>1320.652</v>
+        <v>1338.029</v>
       </c>
       <c r="G78">
         <v>240.2</v>
@@ -7689,37 +7689,37 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M78">
-        <v>332.3169540496239</v>
+        <v>336.6895455502769</v>
       </c>
       <c r="N78">
-        <v>-236.361035682277</v>
+        <v>-240.7336271829299</v>
       </c>
       <c r="O78">
-        <v>-59.09025892056924</v>
+        <v>-60.18340679573248</v>
       </c>
       <c r="P78">
-        <v>-177.2707767617077</v>
+        <v>-180.5502203871974</v>
       </c>
       <c r="Q78">
-        <v>-168.4307767617077</v>
+        <v>-171.7102203871974</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2915539511930593</v>
+        <v>0.3022389055927575</v>
       </c>
       <c r="T78">
-        <v>3.801735465834351</v>
+        <v>3.967028312174975</v>
       </c>
       <c r="U78">
         <v>0.2516309777667576</v>
       </c>
       <c r="V78">
-        <v>0.07218704703297964</v>
+        <v>0.07124955291566822</v>
       </c>
       <c r="W78">
-        <v>0.233466480539754</v>
+        <v>0.2337023831011436</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.2887481881319186</v>
+        <v>0.2849982116626729</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7735,22 +7735,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2494657832742148</v>
+        <v>0.2515240930518824</v>
       </c>
       <c r="C79">
-        <v>-630.9341328279864</v>
+        <v>-652.9825072692904</v>
       </c>
       <c r="D79">
-        <v>466.8948671720136</v>
+        <v>462.2234927307097</v>
       </c>
       <c r="E79">
-        <v>905.329</v>
+        <v>922.7060000000001</v>
       </c>
       <c r="F79">
-        <v>1338.029</v>
+        <v>1355.406</v>
       </c>
       <c r="G79">
         <v>240.2</v>
@@ -7771,37 +7771,37 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M79">
-        <v>336.6895455502769</v>
+        <v>341.0621370509299</v>
       </c>
       <c r="N79">
-        <v>-240.7336271829299</v>
+        <v>-245.1062186835829</v>
       </c>
       <c r="O79">
-        <v>-60.18340679573248</v>
+        <v>-61.27655467089573</v>
       </c>
       <c r="P79">
-        <v>-180.5502203871974</v>
+        <v>-183.8296640126872</v>
       </c>
       <c r="Q79">
-        <v>-171.7102203871974</v>
+        <v>-174.9896640126872</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.3022389055927575</v>
+        <v>0.3138952194833374</v>
       </c>
       <c r="T79">
-        <v>3.967028312174975</v>
+        <v>4.147347780910201</v>
       </c>
       <c r="U79">
         <v>0.2516309777667576</v>
       </c>
       <c r="V79">
-        <v>0.07124955291566822</v>
+        <v>0.07033609710905707</v>
       </c>
       <c r="W79">
-        <v>0.2337023831011436</v>
+        <v>0.2339322368789079</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.2849982116626729</v>
+        <v>0.2813443884362283</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7817,22 +7817,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2515240930518824</v>
+        <v>0.25358240282955</v>
       </c>
       <c r="C80">
-        <v>-652.9825072692904</v>
+        <v>-674.9383316624983</v>
       </c>
       <c r="D80">
-        <v>462.2234927307097</v>
+        <v>457.6446683375018</v>
       </c>
       <c r="E80">
-        <v>922.7060000000001</v>
+        <v>940.0830000000001</v>
       </c>
       <c r="F80">
-        <v>1355.406</v>
+        <v>1372.783</v>
       </c>
       <c r="G80">
         <v>240.2</v>
@@ -7853,37 +7853,37 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M80">
-        <v>341.0621370509299</v>
+        <v>345.4347285515828</v>
       </c>
       <c r="N80">
-        <v>-245.1062186835829</v>
+        <v>-249.4788101842358</v>
       </c>
       <c r="O80">
-        <v>-61.27655467089573</v>
+        <v>-62.36970254605896</v>
       </c>
       <c r="P80">
-        <v>-183.8296640126872</v>
+        <v>-187.1091076381769</v>
       </c>
       <c r="Q80">
-        <v>-174.9896640126872</v>
+        <v>-178.2691076381769</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.3138952194833374</v>
+        <v>0.3266616585063535</v>
       </c>
       <c r="T80">
-        <v>4.147347780910201</v>
+        <v>4.344840532382117</v>
       </c>
       <c r="U80">
         <v>0.2516309777667576</v>
       </c>
       <c r="V80">
-        <v>0.07033609710905707</v>
+        <v>0.06944576676590446</v>
       </c>
       <c r="W80">
-        <v>0.2339322368789079</v>
+        <v>0.2341562715736908</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.2813443884362283</v>
+        <v>0.2777830670636179</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7899,22 +7899,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.25358240282955</v>
+        <v>0.2556407126072175</v>
       </c>
       <c r="C81">
-        <v>-674.9383316624983</v>
+        <v>-696.80432945436</v>
       </c>
       <c r="D81">
-        <v>457.6446683375018</v>
+        <v>453.1556705456402</v>
       </c>
       <c r="E81">
-        <v>940.0830000000001</v>
+        <v>957.46</v>
       </c>
       <c r="F81">
-        <v>1372.783</v>
+        <v>1390.16</v>
       </c>
       <c r="G81">
         <v>240.2</v>
@@ -7935,37 +7935,37 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M81">
-        <v>345.4347285515828</v>
+        <v>349.8073200522358</v>
       </c>
       <c r="N81">
-        <v>-249.4788101842358</v>
+        <v>-253.8514016848888</v>
       </c>
       <c r="O81">
-        <v>-62.36970254605896</v>
+        <v>-63.4628504212222</v>
       </c>
       <c r="P81">
-        <v>-187.1091076381769</v>
+        <v>-190.3885512636666</v>
       </c>
       <c r="Q81">
-        <v>-178.2691076381769</v>
+        <v>-181.5485512636666</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3266616585063535</v>
+        <v>0.3407047414316712</v>
       </c>
       <c r="T81">
-        <v>4.344840532382117</v>
+        <v>4.562082559001222</v>
       </c>
       <c r="U81">
         <v>0.2516309777667576</v>
       </c>
       <c r="V81">
-        <v>0.06944576676590446</v>
+        <v>0.06857769468133064</v>
       </c>
       <c r="W81">
-        <v>0.2341562715736908</v>
+        <v>0.2343747054011042</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.2777830670636179</v>
+        <v>0.2743107787253226</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7981,22 +7981,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2556407126072175</v>
+        <v>0.2576990223848851</v>
       </c>
       <c r="C82">
-        <v>-696.80432945436</v>
+        <v>-718.5831182733541</v>
       </c>
       <c r="D82">
-        <v>453.1556705456402</v>
+        <v>448.7538817266459</v>
       </c>
       <c r="E82">
-        <v>957.46</v>
+        <v>974.837</v>
       </c>
       <c r="F82">
-        <v>1390.16</v>
+        <v>1407.537</v>
       </c>
       <c r="G82">
         <v>240.2</v>
@@ -8017,37 +8017,37 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M82">
-        <v>349.8073200522358</v>
+        <v>354.1799115528887</v>
       </c>
       <c r="N82">
-        <v>-253.8514016848888</v>
+        <v>-258.2239931855417</v>
       </c>
       <c r="O82">
-        <v>-63.4628504212222</v>
+        <v>-64.55599829638543</v>
       </c>
       <c r="P82">
-        <v>-190.3885512636666</v>
+        <v>-193.6679948891563</v>
       </c>
       <c r="Q82">
-        <v>-181.5485512636666</v>
+        <v>-184.8279948891563</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3407047414316712</v>
+        <v>0.3562260436122855</v>
       </c>
       <c r="T82">
-        <v>4.562082559001222</v>
+        <v>4.802192167369707</v>
       </c>
       <c r="U82">
         <v>0.2516309777667576</v>
       </c>
       <c r="V82">
-        <v>0.06857769468133064</v>
+        <v>0.0677310564753883</v>
       </c>
       <c r="W82">
-        <v>0.2343747054011042</v>
+        <v>0.2345877458006801</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.2743107787253226</v>
+        <v>0.2709242259015533</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8063,22 +8063,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2576990223848851</v>
+        <v>0.2597573321625527</v>
       </c>
       <c r="C83">
-        <v>-718.5831182733541</v>
+        <v>-740.2772150196461</v>
       </c>
       <c r="D83">
-        <v>448.7538817266459</v>
+        <v>444.4367849803541</v>
       </c>
       <c r="E83">
-        <v>974.837</v>
+        <v>992.2140000000002</v>
       </c>
       <c r="F83">
-        <v>1407.537</v>
+        <v>1424.914</v>
       </c>
       <c r="G83">
         <v>240.2</v>
@@ -8099,37 +8099,37 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M83">
-        <v>354.1799115528887</v>
+        <v>358.5525030535417</v>
       </c>
       <c r="N83">
-        <v>-258.2239931855417</v>
+        <v>-262.5965846861947</v>
       </c>
       <c r="O83">
-        <v>-64.55599829638543</v>
+        <v>-65.64914617154868</v>
       </c>
       <c r="P83">
-        <v>-193.6679948891563</v>
+        <v>-196.947438514646</v>
       </c>
       <c r="Q83">
-        <v>-184.8279948891563</v>
+        <v>-188.107438514646</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3562260436122855</v>
+        <v>0.3734719349240791</v>
       </c>
       <c r="T83">
-        <v>4.802192167369707</v>
+        <v>5.068980621112469</v>
       </c>
       <c r="U83">
         <v>0.2516309777667576</v>
       </c>
       <c r="V83">
-        <v>0.0677310564753883</v>
+        <v>0.066905067981786</v>
       </c>
       <c r="W83">
-        <v>0.2345877458006801</v>
+        <v>0.2347955900929494</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.2709242259015533</v>
+        <v>0.267620271927144</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8145,22 +8145,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2597573321625527</v>
+        <v>0.2618156419402203</v>
       </c>
       <c r="C84">
-        <v>-740.2772150196461</v>
+        <v>-761.8890406640473</v>
       </c>
       <c r="D84">
-        <v>444.4367849803541</v>
+        <v>440.2019593359528</v>
       </c>
       <c r="E84">
-        <v>992.2140000000002</v>
+        <v>1009.591</v>
       </c>
       <c r="F84">
-        <v>1424.914</v>
+        <v>1442.291</v>
       </c>
       <c r="G84">
         <v>240.2</v>
@@ -8181,37 +8181,37 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M84">
-        <v>358.5525030535417</v>
+        <v>362.9250945541946</v>
       </c>
       <c r="N84">
-        <v>-262.5965846861947</v>
+        <v>-266.9691761868476</v>
       </c>
       <c r="O84">
-        <v>-65.64914617154868</v>
+        <v>-66.7422940467119</v>
       </c>
       <c r="P84">
-        <v>-196.947438514646</v>
+        <v>-200.2268821401357</v>
       </c>
       <c r="Q84">
-        <v>-188.107438514646</v>
+        <v>-191.3868821401357</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3734719349240791</v>
+        <v>0.3927467546254956</v>
       </c>
       <c r="T84">
-        <v>5.068980621112469</v>
+        <v>5.367155951766144</v>
       </c>
       <c r="U84">
         <v>0.2516309777667576</v>
       </c>
       <c r="V84">
-        <v>0.066905067981786</v>
+        <v>0.06609898282537895</v>
       </c>
       <c r="W84">
-        <v>0.2347955900929494</v>
+        <v>0.2349984260890194</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.267620271927144</v>
+        <v>0.2643959313015158</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8227,22 +8227,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2618156419402203</v>
+        <v>0.2638739517178879</v>
       </c>
       <c r="C85">
-        <v>-761.8890406640473</v>
+        <v>-783.4209247752028</v>
       </c>
       <c r="D85">
-        <v>440.2019593359528</v>
+        <v>436.0470752247973</v>
       </c>
       <c r="E85">
-        <v>1009.591</v>
+        <v>1026.968</v>
       </c>
       <c r="F85">
-        <v>1442.291</v>
+        <v>1459.668</v>
       </c>
       <c r="G85">
         <v>240.2</v>
@@ -8263,37 +8263,37 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M85">
-        <v>362.9250945541946</v>
+        <v>367.2976860548475</v>
       </c>
       <c r="N85">
-        <v>-266.9691761868476</v>
+        <v>-271.3417676875006</v>
       </c>
       <c r="O85">
-        <v>-66.7422940467119</v>
+        <v>-67.83544192187514</v>
       </c>
       <c r="P85">
-        <v>-200.2268821401357</v>
+        <v>-203.5063257656254</v>
       </c>
       <c r="Q85">
-        <v>-191.3868821401357</v>
+        <v>-194.6663257656254</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3927467546254956</v>
+        <v>0.4144309267895891</v>
       </c>
       <c r="T85">
-        <v>5.367155951766144</v>
+        <v>5.702603198751529</v>
       </c>
       <c r="U85">
         <v>0.2516309777667576</v>
       </c>
       <c r="V85">
-        <v>0.06609898282537895</v>
+        <v>0.06531209017269586</v>
       </c>
       <c r="W85">
-        <v>0.2349984260890194</v>
+        <v>0.2351964326566115</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.2643959313015158</v>
+        <v>0.2612483606907835</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8309,22 +8309,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2638739517178879</v>
+        <v>0.2659322614955555</v>
       </c>
       <c r="C86">
-        <v>-783.4209247752026</v>
+        <v>-804.875109792796</v>
       </c>
       <c r="D86">
-        <v>436.0470752247973</v>
+        <v>431.9698902072041</v>
       </c>
       <c r="E86">
-        <v>1026.968</v>
+        <v>1044.345</v>
       </c>
       <c r="F86">
-        <v>1459.668</v>
+        <v>1477.045</v>
       </c>
       <c r="G86">
         <v>240.2</v>
@@ -8345,37 +8345,37 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M86">
-        <v>367.2976860548475</v>
+        <v>371.6702775555005</v>
       </c>
       <c r="N86">
-        <v>-271.3417676875005</v>
+        <v>-275.7143591881535</v>
       </c>
       <c r="O86">
-        <v>-67.83544192187513</v>
+        <v>-68.92858979703838</v>
       </c>
       <c r="P86">
-        <v>-203.5063257656254</v>
+        <v>-206.7857693911151</v>
       </c>
       <c r="Q86">
-        <v>-194.6663257656254</v>
+        <v>-197.9457693911151</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.4144309267895889</v>
+        <v>0.4390063219088948</v>
       </c>
       <c r="T86">
-        <v>5.702603198751525</v>
+        <v>6.082776745334961</v>
       </c>
       <c r="U86">
         <v>0.2516309777667576</v>
       </c>
       <c r="V86">
-        <v>0.06531209017269586</v>
+        <v>0.06454371264125237</v>
       </c>
       <c r="W86">
-        <v>0.2351964326566115</v>
+        <v>0.2353897802461426</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.2612483606907835</v>
+        <v>0.2581748505650096</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8391,22 +8391,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2659322614955555</v>
+        <v>0.267990571273223</v>
       </c>
       <c r="C87">
-        <v>-804.875109792796</v>
+        <v>-826.2537550632343</v>
       </c>
       <c r="D87">
-        <v>431.9698902072041</v>
+        <v>427.9682449367658</v>
       </c>
       <c r="E87">
-        <v>1044.345</v>
+        <v>1061.722</v>
       </c>
       <c r="F87">
-        <v>1477.045</v>
+        <v>1494.422</v>
       </c>
       <c r="G87">
         <v>240.2</v>
@@ -8427,37 +8427,37 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M87">
-        <v>371.6702775555005</v>
+        <v>376.0428690561534</v>
       </c>
       <c r="N87">
-        <v>-275.7143591881535</v>
+        <v>-280.0869506888064</v>
       </c>
       <c r="O87">
-        <v>-68.92858979703838</v>
+        <v>-70.02173767220161</v>
       </c>
       <c r="P87">
-        <v>-206.7857693911151</v>
+        <v>-210.0652130166048</v>
       </c>
       <c r="Q87">
-        <v>-197.9457693911151</v>
+        <v>-201.2252130166048</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.4390063219088948</v>
+        <v>0.4670924877595302</v>
       </c>
       <c r="T87">
-        <v>6.082776745334961</v>
+        <v>6.517260798573172</v>
       </c>
       <c r="U87">
         <v>0.2516309777667576</v>
       </c>
       <c r="V87">
-        <v>0.06454371264125237</v>
+        <v>0.06379320435472619</v>
       </c>
       <c r="W87">
-        <v>0.2353897802461426</v>
+        <v>0.2355786313801032</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.2581748505650096</v>
+        <v>0.2551728174189047</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8473,22 +8473,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.267990571273223</v>
+        <v>0.2700488810508906</v>
       </c>
       <c r="C88">
-        <v>-826.2537550632343</v>
+        <v>-847.5589406530862</v>
       </c>
       <c r="D88">
-        <v>427.9682449367658</v>
+        <v>424.0400593469137</v>
       </c>
       <c r="E88">
-        <v>1061.722</v>
+        <v>1079.099</v>
       </c>
       <c r="F88">
-        <v>1494.422</v>
+        <v>1511.799</v>
       </c>
       <c r="G88">
         <v>240.2</v>
@@ -8509,37 +8509,37 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M88">
-        <v>376.0428690561534</v>
+        <v>380.4154605568064</v>
       </c>
       <c r="N88">
-        <v>-280.0869506888064</v>
+        <v>-284.4595421894594</v>
       </c>
       <c r="O88">
-        <v>-70.02173767220161</v>
+        <v>-71.11488554736485</v>
       </c>
       <c r="P88">
-        <v>-210.0652130166048</v>
+        <v>-213.3446566420945</v>
       </c>
       <c r="Q88">
-        <v>-201.2252130166048</v>
+        <v>-204.5046566420945</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4670924877595302</v>
+        <v>0.4994996022025709</v>
       </c>
       <c r="T88">
-        <v>6.517260798573172</v>
+        <v>7.01858855230957</v>
       </c>
       <c r="U88">
         <v>0.2516309777667576</v>
       </c>
       <c r="V88">
-        <v>0.06379320435472619</v>
+        <v>0.06305994913225807</v>
       </c>
       <c r="W88">
-        <v>0.2355786313801032</v>
+        <v>0.2357631411086855</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.2551728174189047</v>
+        <v>0.2522397965290323</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8555,22 +8555,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2700488810508906</v>
+        <v>0.2721071908285582</v>
       </c>
       <c r="C89">
-        <v>-847.5589406530862</v>
+        <v>-868.7926709544126</v>
       </c>
       <c r="D89">
-        <v>424.0400593469137</v>
+        <v>420.1833290455876</v>
       </c>
       <c r="E89">
-        <v>1079.099</v>
+        <v>1096.476</v>
       </c>
       <c r="F89">
-        <v>1511.799</v>
+        <v>1529.176</v>
       </c>
       <c r="G89">
         <v>240.2</v>
@@ -8591,37 +8591,37 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M89">
-        <v>380.4154605568064</v>
+        <v>384.7880520574593</v>
       </c>
       <c r="N89">
-        <v>-284.4595421894594</v>
+        <v>-288.8321336901124</v>
       </c>
       <c r="O89">
-        <v>-71.11488554736485</v>
+        <v>-72.20803342252809</v>
       </c>
       <c r="P89">
-        <v>-213.3446566420945</v>
+        <v>-216.6241002675843</v>
       </c>
       <c r="Q89">
-        <v>-204.5046566420945</v>
+        <v>-207.7841002675843</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4994996022025709</v>
+        <v>0.5373079023861186</v>
       </c>
       <c r="T89">
-        <v>7.01858855230957</v>
+        <v>7.603470931668703</v>
       </c>
       <c r="U89">
         <v>0.2516309777667576</v>
       </c>
       <c r="V89">
-        <v>0.06305994913225807</v>
+        <v>0.06234335880120968</v>
       </c>
       <c r="W89">
-        <v>0.2357631411086855</v>
+        <v>0.2359434574343454</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.2522397965290323</v>
+        <v>0.2493734352048388</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8637,22 +8637,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2721071908285582</v>
+        <v>0.2741655006062257</v>
       </c>
       <c r="C90">
-        <v>-868.7926709544126</v>
+        <v>-889.9568780951214</v>
       </c>
       <c r="D90">
-        <v>420.1833290455876</v>
+        <v>416.3961219048787</v>
       </c>
       <c r="E90">
-        <v>1096.476</v>
+        <v>1113.853</v>
       </c>
       <c r="F90">
-        <v>1529.176</v>
+        <v>1546.553</v>
       </c>
       <c r="G90">
         <v>240.2</v>
@@ -8673,37 +8673,37 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M90">
-        <v>384.7880520574593</v>
+        <v>389.1606435581123</v>
       </c>
       <c r="N90">
-        <v>-288.8321336901124</v>
+        <v>-293.2047251907653</v>
       </c>
       <c r="O90">
-        <v>-72.20803342252809</v>
+        <v>-73.30118129769133</v>
       </c>
       <c r="P90">
-        <v>-216.6241002675843</v>
+        <v>-219.903543893074</v>
       </c>
       <c r="Q90">
-        <v>-207.7841002675843</v>
+        <v>-211.063543893074</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.5373079023861186</v>
+        <v>0.5819904389666748</v>
       </c>
       <c r="T90">
-        <v>7.603470931668703</v>
+        <v>8.294695561820403</v>
       </c>
       <c r="U90">
         <v>0.2516309777667576</v>
       </c>
       <c r="V90">
-        <v>0.06234335880120968</v>
+        <v>0.06164287162366799</v>
       </c>
       <c r="W90">
-        <v>0.2359434574343454</v>
+        <v>0.2361197217077433</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.2493734352048388</v>
+        <v>0.246571486494672</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8719,22 +8719,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2741655006062257</v>
+        <v>0.2762238103838933</v>
       </c>
       <c r="C91">
-        <v>-889.9568780951214</v>
+        <v>-911.0534251665449</v>
       </c>
       <c r="D91">
-        <v>416.3961219048787</v>
+        <v>412.6765748334552</v>
       </c>
       <c r="E91">
-        <v>1113.853</v>
+        <v>1131.23</v>
       </c>
       <c r="F91">
-        <v>1546.553</v>
+        <v>1563.93</v>
       </c>
       <c r="G91">
         <v>240.2</v>
@@ -8755,37 +8755,37 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M91">
-        <v>389.1606435581123</v>
+        <v>393.5332350587652</v>
       </c>
       <c r="N91">
-        <v>-293.2047251907653</v>
+        <v>-297.5773166914182</v>
       </c>
       <c r="O91">
-        <v>-73.30118129769133</v>
+        <v>-74.39432917285455</v>
       </c>
       <c r="P91">
-        <v>-219.903543893074</v>
+        <v>-223.1829875185637</v>
       </c>
       <c r="Q91">
-        <v>-211.063543893074</v>
+        <v>-214.3429875185637</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.5819904389666748</v>
+        <v>0.6356094828633423</v>
       </c>
       <c r="T91">
-        <v>8.294695561820403</v>
+        <v>9.124165118002443</v>
       </c>
       <c r="U91">
         <v>0.2516309777667576</v>
       </c>
       <c r="V91">
-        <v>0.06164287162366799</v>
+        <v>0.06095795082784947</v>
       </c>
       <c r="W91">
-        <v>0.2361197217077433</v>
+        <v>0.2362920689972879</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.246571486494672</v>
+        <v>0.2438318033113979</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8801,22 +8801,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2762238103838933</v>
+        <v>0.2782821201615609</v>
       </c>
       <c r="C92">
-        <v>-911.0534251665449</v>
+        <v>-932.0841092795588</v>
       </c>
       <c r="D92">
-        <v>412.6765748334552</v>
+        <v>409.0228907204413</v>
       </c>
       <c r="E92">
-        <v>1131.23</v>
+        <v>1148.607</v>
       </c>
       <c r="F92">
-        <v>1563.93</v>
+        <v>1581.307</v>
       </c>
       <c r="G92">
         <v>240.2</v>
@@ -8837,37 +8837,37 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M92">
-        <v>393.5332350587652</v>
+        <v>397.9058265594181</v>
       </c>
       <c r="N92">
-        <v>-297.5773166914182</v>
+        <v>-301.9499081920712</v>
       </c>
       <c r="O92">
-        <v>-74.39432917285455</v>
+        <v>-75.48747704801779</v>
       </c>
       <c r="P92">
-        <v>-223.1829875185637</v>
+        <v>-226.4624311440534</v>
       </c>
       <c r="Q92">
-        <v>-214.3429875185637</v>
+        <v>-217.6224311440534</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.6356094828633423</v>
+        <v>0.7011438698481581</v>
       </c>
       <c r="T92">
-        <v>9.124165118002443</v>
+        <v>10.13796124222494</v>
       </c>
       <c r="U92">
         <v>0.2516309777667576</v>
       </c>
       <c r="V92">
-        <v>0.06095795082784947</v>
+        <v>0.06028808323633464</v>
       </c>
       <c r="W92">
-        <v>0.2362920689972879</v>
+        <v>0.236460628434315</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.2438318033113979</v>
+        <v>0.2411523329453386</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8883,22 +8883,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2782821201615609</v>
+        <v>0.2803404299392285</v>
       </c>
       <c r="C93">
-        <v>-932.0841092795588</v>
+        <v>-953.0506644597804</v>
       </c>
       <c r="D93">
-        <v>409.0228907204413</v>
+        <v>405.4333355402198</v>
       </c>
       <c r="E93">
-        <v>1148.607</v>
+        <v>1165.984</v>
       </c>
       <c r="F93">
-        <v>1581.307</v>
+        <v>1598.684</v>
       </c>
       <c r="G93">
         <v>240.2</v>
@@ -8919,37 +8919,37 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M93">
-        <v>397.9058265594181</v>
+        <v>402.2784180600711</v>
       </c>
       <c r="N93">
-        <v>-301.9499081920712</v>
+        <v>-306.3224996927242</v>
       </c>
       <c r="O93">
-        <v>-75.48747704801779</v>
+        <v>-76.58062492318105</v>
       </c>
       <c r="P93">
-        <v>-226.4624311440534</v>
+        <v>-229.7418747695431</v>
       </c>
       <c r="Q93">
-        <v>-217.6224311440534</v>
+        <v>-220.9018747695431</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.7011438698481581</v>
+        <v>0.7830618535791781</v>
       </c>
       <c r="T93">
-        <v>10.13796124222494</v>
+        <v>11.40520639750306</v>
       </c>
       <c r="U93">
         <v>0.2516309777667576</v>
       </c>
       <c r="V93">
-        <v>0.06028808323633464</v>
+        <v>0.05963277798376578</v>
       </c>
       <c r="W93">
-        <v>0.236460628434315</v>
+        <v>0.2366255235357546</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.2411523329453386</v>
+        <v>0.2385311119350632</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8965,22 +8965,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2803404299392285</v>
+        <v>0.2823987397168961</v>
       </c>
       <c r="C94">
-        <v>-953.0506644597804</v>
+        <v>-973.9547643916453</v>
       </c>
       <c r="D94">
-        <v>405.4333355402198</v>
+        <v>401.9062356083548</v>
       </c>
       <c r="E94">
-        <v>1165.984</v>
+        <v>1183.361</v>
       </c>
       <c r="F94">
-        <v>1598.684</v>
+        <v>1616.061</v>
       </c>
       <c r="G94">
         <v>240.2</v>
@@ -9001,37 +9001,37 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M94">
-        <v>402.2784180600711</v>
+        <v>406.651009560724</v>
       </c>
       <c r="N94">
-        <v>-306.3224996927242</v>
+        <v>-310.6950911933771</v>
       </c>
       <c r="O94">
-        <v>-76.58062492318105</v>
+        <v>-77.67377279834427</v>
       </c>
       <c r="P94">
-        <v>-229.7418747695431</v>
+        <v>-233.0213183950328</v>
       </c>
       <c r="Q94">
-        <v>-220.9018747695431</v>
+        <v>-224.1813183950328</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.7830618535791781</v>
+        <v>0.8883849755190609</v>
       </c>
       <c r="T94">
-        <v>11.40520639750306</v>
+        <v>13.03452159714636</v>
       </c>
       <c r="U94">
         <v>0.2516309777667576</v>
       </c>
       <c r="V94">
-        <v>0.05963277798376578</v>
+        <v>0.05899156531727368</v>
       </c>
       <c r="W94">
-        <v>0.2366255235357546</v>
+        <v>0.2367868725059805</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.2385311119350632</v>
+        <v>0.2359662612690947</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9047,22 +9047,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2823987397168961</v>
+        <v>0.2844570494945636</v>
       </c>
       <c r="C95">
-        <v>-973.9547643916453</v>
+        <v>-994.7980250204859</v>
       </c>
       <c r="D95">
-        <v>401.9062356083548</v>
+        <v>398.4399749795143</v>
       </c>
       <c r="E95">
-        <v>1183.361</v>
+        <v>1200.738</v>
       </c>
       <c r="F95">
-        <v>1616.061</v>
+        <v>1633.438</v>
       </c>
       <c r="G95">
         <v>240.2</v>
@@ -9083,37 +9083,37 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M95">
-        <v>406.651009560724</v>
+        <v>411.023601061377</v>
       </c>
       <c r="N95">
-        <v>-310.6950911933771</v>
+        <v>-315.0676826940301</v>
       </c>
       <c r="O95">
-        <v>-77.67377279834427</v>
+        <v>-78.76692067350751</v>
       </c>
       <c r="P95">
-        <v>-233.0213183950328</v>
+        <v>-236.3007620205225</v>
       </c>
       <c r="Q95">
-        <v>-224.1813183950328</v>
+        <v>-227.4607620205225</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.8883849755190609</v>
+        <v>1.028815804772238</v>
       </c>
       <c r="T95">
-        <v>13.03452159714636</v>
+        <v>15.20694186333742</v>
       </c>
       <c r="U95">
         <v>0.2516309777667576</v>
       </c>
       <c r="V95">
-        <v>0.05899156531727368</v>
+        <v>0.05836399547347289</v>
       </c>
       <c r="W95">
-        <v>0.2367868725059805</v>
+        <v>0.236944788519393</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.2359662612690947</v>
+        <v>0.2334559818938916</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9129,22 +9129,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2844570494945636</v>
+        <v>0.2865153592722312</v>
       </c>
       <c r="C96">
-        <v>-994.7980250204859</v>
+        <v>-1015.582007021109</v>
       </c>
       <c r="D96">
-        <v>398.4399749795143</v>
+        <v>395.0329929788913</v>
       </c>
       <c r="E96">
-        <v>1200.738</v>
+        <v>1218.115</v>
       </c>
       <c r="F96">
-        <v>1633.438</v>
+        <v>1650.815</v>
       </c>
       <c r="G96">
         <v>240.2</v>
@@ -9165,37 +9165,37 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M96">
-        <v>411.023601061377</v>
+        <v>415.3961925620299</v>
       </c>
       <c r="N96">
-        <v>-315.0676826940301</v>
+        <v>-319.440274194683</v>
       </c>
       <c r="O96">
-        <v>-78.76692067350751</v>
+        <v>-79.86006854867074</v>
       </c>
       <c r="P96">
-        <v>-236.3007620205225</v>
+        <v>-239.5802056460122</v>
       </c>
       <c r="Q96">
-        <v>-227.4607620205225</v>
+        <v>-230.7402056460122</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.028815804772238</v>
+        <v>1.225418965726686</v>
       </c>
       <c r="T96">
-        <v>15.20694186333742</v>
+        <v>18.24833023600491</v>
       </c>
       <c r="U96">
         <v>0.2516309777667576</v>
       </c>
       <c r="V96">
-        <v>0.05836399547347289</v>
+        <v>0.05774963762638371</v>
       </c>
       <c r="W96">
-        <v>0.236944788519393</v>
+        <v>0.2370993799851547</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.2334559818938916</v>
+        <v>0.2309985505055349</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9211,22 +9211,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2865153592722312</v>
+        <v>0.2885736690498988</v>
       </c>
       <c r="C97">
-        <v>-1015.582007021109</v>
+        <v>-1036.308218140798</v>
       </c>
       <c r="D97">
-        <v>395.0329929788913</v>
+        <v>391.6837818592019</v>
       </c>
       <c r="E97">
-        <v>1218.115</v>
+        <v>1235.492</v>
       </c>
       <c r="F97">
-        <v>1650.815</v>
+        <v>1668.192</v>
       </c>
       <c r="G97">
         <v>240.2</v>
@@ -9247,37 +9247,37 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M97">
-        <v>415.3961925620299</v>
+        <v>419.7687840626829</v>
       </c>
       <c r="N97">
-        <v>-319.440274194683</v>
+        <v>-323.812865695336</v>
       </c>
       <c r="O97">
-        <v>-79.86006854867074</v>
+        <v>-80.95321642383399</v>
       </c>
       <c r="P97">
-        <v>-239.5802056460122</v>
+        <v>-242.859649271502</v>
       </c>
       <c r="Q97">
-        <v>-230.7402056460122</v>
+        <v>-234.019649271502</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.225418965726686</v>
+        <v>1.520323707158358</v>
       </c>
       <c r="T97">
-        <v>18.24833023600491</v>
+        <v>22.81041279500615</v>
       </c>
       <c r="U97">
         <v>0.2516309777667576</v>
       </c>
       <c r="V97">
-        <v>0.05774963762638371</v>
+        <v>0.05714807890110887</v>
       </c>
       <c r="W97">
-        <v>0.2370993799851547</v>
+        <v>0.2372507507953797</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.2309985505055349</v>
+        <v>0.2285923156044355</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9293,22 +9293,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2885736690498988</v>
+        <v>0.2906319788275664</v>
       </c>
       <c r="C98">
-        <v>-1036.308218140798</v>
+        <v>-1056.978115424132</v>
       </c>
       <c r="D98">
-        <v>391.6837818592019</v>
+        <v>388.3908845758679</v>
       </c>
       <c r="E98">
-        <v>1235.492</v>
+        <v>1252.869</v>
       </c>
       <c r="F98">
-        <v>1668.192</v>
+        <v>1685.569</v>
       </c>
       <c r="G98">
         <v>240.2</v>
@@ -9329,37 +9329,37 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M98">
-        <v>419.7687840626829</v>
+        <v>424.1413755633358</v>
       </c>
       <c r="N98">
-        <v>-323.8128656953359</v>
+        <v>-328.1854571959888</v>
       </c>
       <c r="O98">
-        <v>-80.95321642383398</v>
+        <v>-82.0463642989972</v>
       </c>
       <c r="P98">
-        <v>-242.859649271502</v>
+        <v>-246.1390928969916</v>
       </c>
       <c r="Q98">
-        <v>-234.0196492715019</v>
+        <v>-237.2990928969916</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.520323707158355</v>
+        <v>2.011831609544473</v>
       </c>
       <c r="T98">
-        <v>22.81041279500609</v>
+        <v>30.41388372667478</v>
       </c>
       <c r="U98">
         <v>0.2516309777667576</v>
       </c>
       <c r="V98">
-        <v>0.05714807890110887</v>
+        <v>0.05655892344852013</v>
       </c>
       <c r="W98">
-        <v>0.2372507507953797</v>
+        <v>0.2373990005579713</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2285923156044355</v>
+        <v>0.2262356937940806</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9375,22 +9375,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2906319788275664</v>
+        <v>0.2926902886052339</v>
       </c>
       <c r="C99">
-        <v>-1056.978115424132</v>
+        <v>-1077.59310732651</v>
       </c>
       <c r="D99">
-        <v>388.3908845758679</v>
+        <v>385.1528926734899</v>
       </c>
       <c r="E99">
-        <v>1252.869</v>
+        <v>1270.246</v>
       </c>
       <c r="F99">
-        <v>1685.569</v>
+        <v>1702.946</v>
       </c>
       <c r="G99">
         <v>240.2</v>
@@ -9411,37 +9411,37 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M99">
-        <v>424.1413755633358</v>
+        <v>428.5139670639887</v>
       </c>
       <c r="N99">
-        <v>-328.1854571959888</v>
+        <v>-332.5580486966418</v>
       </c>
       <c r="O99">
-        <v>-82.0463642989972</v>
+        <v>-83.13951217416044</v>
       </c>
       <c r="P99">
-        <v>-246.1390928969916</v>
+        <v>-249.4185365224813</v>
       </c>
       <c r="Q99">
-        <v>-237.2990928969916</v>
+        <v>-240.5785365224813</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.011831609544473</v>
+        <v>2.994847414316709</v>
       </c>
       <c r="T99">
-        <v>30.41388372667478</v>
+        <v>45.62082559001217</v>
       </c>
       <c r="U99">
         <v>0.2516309777667576</v>
       </c>
       <c r="V99">
-        <v>0.05655892344852013</v>
+        <v>0.05598179157659645</v>
       </c>
       <c r="W99">
-        <v>0.2373990005579713</v>
+        <v>0.2375442248152038</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2262356937940806</v>
+        <v>0.2239271663063859</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9457,22 +9457,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2926902886052339</v>
+        <v>0.2947485983829015</v>
       </c>
       <c r="C100">
-        <v>-1077.59310732651</v>
+        <v>-1098.154555722831</v>
       </c>
       <c r="D100">
-        <v>385.1528926734899</v>
+        <v>381.9684442771691</v>
       </c>
       <c r="E100">
-        <v>1270.246</v>
+        <v>1287.623</v>
       </c>
       <c r="F100">
-        <v>1702.946</v>
+        <v>1720.323</v>
       </c>
       <c r="G100">
         <v>240.2</v>
@@ -9493,37 +9493,37 @@
         <v>95.95591836734694</v>
       </c>
       <c r="M100">
-        <v>428.5139670639887</v>
+        <v>432.8865585646417</v>
       </c>
       <c r="N100">
-        <v>-332.5580486966418</v>
+        <v>-336.9306401972948</v>
       </c>
       <c r="O100">
-        <v>-83.13951217416044</v>
+        <v>-84.2326600493237</v>
       </c>
       <c r="P100">
-        <v>-249.4185365224813</v>
+        <v>-252.6979801479711</v>
       </c>
       <c r="Q100">
-        <v>-240.5785365224813</v>
+        <v>-243.8579801479711</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.994847414316709</v>
+        <v>5.943894828633418</v>
       </c>
       <c r="T100">
-        <v>45.62082559001217</v>
+        <v>91.24165118002435</v>
       </c>
       <c r="U100">
         <v>0.2516309777667576</v>
       </c>
       <c r="V100">
-        <v>0.05598179157659645</v>
+        <v>0.05541631893440861</v>
       </c>
       <c r="W100">
-        <v>0.2375442248152038</v>
+        <v>0.2376865152490579</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9531,91 +9531,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2239271663063859</v>
+        <v>0.2216652757376344</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2947485983829015</v>
-      </c>
-      <c r="C101">
-        <v>-1098.154555722831</v>
-      </c>
-      <c r="D101">
-        <v>381.9684442771691</v>
-      </c>
-      <c r="E101">
-        <v>1287.623</v>
-      </c>
-      <c r="F101">
-        <v>1720.323</v>
-      </c>
-      <c r="G101">
-        <v>240.2</v>
-      </c>
-      <c r="H101">
-        <v>1305</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>104.7959183673469</v>
-      </c>
-      <c r="K101">
-        <v>8.84</v>
-      </c>
-      <c r="L101">
-        <v>95.95591836734694</v>
-      </c>
-      <c r="M101">
-        <v>432.8865585646417</v>
-      </c>
-      <c r="N101">
-        <v>-336.9306401972948</v>
-      </c>
-      <c r="O101">
-        <v>-84.2326600493237</v>
-      </c>
-      <c r="P101">
-        <v>-252.6979801479711</v>
-      </c>
-      <c r="Q101">
-        <v>-243.8579801479711</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>5.943894828633418</v>
-      </c>
-      <c r="T101">
-        <v>91.24165118002435</v>
-      </c>
-      <c r="U101">
-        <v>0.2516309777667576</v>
-      </c>
-      <c r="V101">
-        <v>0.05541631893440861</v>
-      </c>
-      <c r="W101">
-        <v>0.2376865152490579</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.2216652757376344</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
